--- a/Bouvet modell.xlsx
+++ b/Bouvet modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D7D322C-A70C-F046-A15C-0A4B1069CB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB88CF3-B90D-194E-9711-F60A1001EE10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22920" yWindow="500" windowWidth="28280" windowHeight="26740" activeTab="1" xr2:uid="{880FDD81-14BC-AE47-8673-E11DDB2293DC}"/>
+    <workbookView xWindow="25440" yWindow="500" windowWidth="25760" windowHeight="26740" activeTab="1" xr2:uid="{880FDD81-14BC-AE47-8673-E11DDB2293DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="142">
   <si>
     <t>Kapitalstruktur</t>
   </si>
@@ -448,6 +448,24 @@
   <si>
     <t>Nullvekst og konstante marginer</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>13.05.26: Deputy chair kjøper 5 920 aksjer</t>
+  </si>
+  <si>
+    <t>Avskrivninger</t>
+  </si>
 </sst>
 </file>
 
@@ -457,7 +475,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -518,6 +536,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -572,7 +605,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -613,10 +646,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1022,6 +1060,28 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{57676AD8-B6A7-2442-B8DB-77F28EC5BD66}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;2636cb70-354f-45f3-80e5-cb8bb6477e55&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B413DF46-F1A5-0C49-85C0-D1B5F4B7D670}">
   <dimension ref="A1:L30"/>
@@ -1050,6 +1110,11 @@
         <v>101</v>
       </c>
     </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="K30" s="1" t="s">
         <v>105</v>
@@ -1063,29 +1128,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7744B4B7-919E-FB44-9BF2-96D39848EF35}">
-  <dimension ref="A3:EK90"/>
+  <dimension ref="A3:EO90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="5"/>
     <col min="3" max="3" width="38.1640625" style="1" customWidth="1"/>
-    <col min="4" max="16" width="10.83203125" style="1"/>
-    <col min="17" max="17" width="10.83203125" style="5"/>
-    <col min="18" max="27" width="10.83203125" style="1"/>
-    <col min="28" max="28" width="10.83203125" style="5"/>
-    <col min="29" max="32" width="10.83203125" style="1"/>
-    <col min="33" max="37" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13.83203125" style="1" customWidth="1"/>
-    <col min="42" max="53" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="55" width="10.83203125" style="1"/>
-    <col min="56" max="56" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="16384" width="10.83203125" style="1"/>
+    <col min="4" max="36" width="10.83203125" style="1"/>
+    <col min="37" max="41" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="13.83203125" style="1" customWidth="1"/>
+    <col min="46" max="57" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="59" width="10.83203125" style="1"/>
+    <col min="60" max="60" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:141" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:145" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1131,7 +1192,7 @@
       <c r="P3" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="21" t="s">
         <v>95</v>
       </c>
       <c r="R3" s="21" t="s">
@@ -1140,68 +1201,80 @@
       <c r="S3" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="T3" s="21"/>
+      <c r="T3" s="21" t="s">
+        <v>136</v>
+      </c>
       <c r="U3" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="V3" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="W3" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="V3" s="21" t="s">
+      <c r="Z3" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="W3" s="21" t="s">
+      <c r="AA3" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="X3" s="21" t="s">
+      <c r="AB3" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="Y3" s="21" t="s">
+      <c r="AC3" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="21" t="s">
+      <c r="AD3" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="AA3" s="21" t="s">
+      <c r="AE3" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="AB3" s="6" t="s">
+      <c r="AF3" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="AC3" s="21" t="s">
+      <c r="AG3" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="AD3" s="21" t="s">
+      <c r="AH3" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="AE3" s="21" t="s">
+      <c r="AI3" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="AF3" s="21" t="s">
+      <c r="AJ3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="AG3" s="21" t="s">
+      <c r="AK3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="AH3" s="21" t="s">
+      <c r="AL3" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="AI3" s="21" t="s">
+      <c r="AM3" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="AJ3" s="21" t="s">
+      <c r="AN3" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="AK3" s="21" t="s">
+      <c r="AO3" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="AL3" s="21" t="s">
+      <c r="AP3" s="21" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:141" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:145" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="6">
-        <v>65.900000000000006</v>
+        <v>45</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>44</v>
@@ -1248,78 +1321,83 @@
       <c r="Q4" s="32">
         <v>968.70699999999999</v>
       </c>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="10">
+      <c r="R4" s="10">
+        <v>870.47400000000005</v>
+      </c>
+      <c r="S4" s="10">
+        <v>998.43499999999995</v>
+      </c>
+      <c r="T4" s="35">
+        <v>1037</v>
+      </c>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10">
         <v>1846.711</v>
       </c>
-      <c r="V4" s="10">
+      <c r="Z4" s="10">
         <v>2132</v>
       </c>
-      <c r="W4" s="10">
+      <c r="AA4" s="10">
         <v>2401.8440000000001</v>
       </c>
-      <c r="X4" s="10">
+      <c r="AB4" s="10">
         <v>2695</v>
       </c>
-      <c r="Y4" s="10">
+      <c r="AC4" s="10">
         <v>3102</v>
       </c>
-      <c r="Z4" s="10">
+      <c r="AD4" s="10">
         <v>3526</v>
       </c>
-      <c r="AA4" s="10">
+      <c r="AE4" s="10">
         <v>3921</v>
       </c>
-      <c r="AB4" s="11">
-        <f>AA4*1.06</f>
-        <v>4156.26</v>
-      </c>
-      <c r="AC4" s="10">
-        <f>AB4*1.075</f>
-        <v>4467.9795000000004</v>
-      </c>
-      <c r="AD4" s="10">
-        <f t="shared" ref="AD4:AL4" si="0">AC4*1.075</f>
-        <v>4803.0779625000005</v>
-      </c>
-      <c r="AE4" s="10">
-        <f t="shared" si="0"/>
-        <v>5163.3088096874999</v>
-      </c>
       <c r="AF4" s="10">
-        <f t="shared" si="0"/>
-        <v>5550.5569704140626</v>
+        <v>3912</v>
       </c>
       <c r="AG4" s="10">
-        <f t="shared" si="0"/>
-        <v>5966.8487431951171</v>
+        <f>AF4*1.01</f>
+        <v>3951.12</v>
       </c>
       <c r="AH4" s="10">
-        <f t="shared" si="0"/>
-        <v>6414.3623989347507</v>
+        <f t="shared" ref="AH4:AP4" si="0">AG4*1.05</f>
+        <v>4148.6760000000004</v>
       </c>
       <c r="AI4" s="10">
         <f t="shared" si="0"/>
-        <v>6895.4395788548563</v>
+        <v>4356.1098000000002</v>
       </c>
       <c r="AJ4" s="10">
         <f t="shared" si="0"/>
-        <v>7412.5975472689706</v>
+        <v>4573.9152900000008</v>
       </c>
       <c r="AK4" s="10">
         <f t="shared" si="0"/>
-        <v>7968.5423633141427</v>
+        <v>4802.611054500001</v>
       </c>
       <c r="AL4" s="10">
         <f t="shared" si="0"/>
-        <v>8566.1830405627024</v>
-      </c>
-      <c r="AM4" s="10"/>
-      <c r="AN4" s="10"/>
-      <c r="AO4" s="10"/>
-      <c r="AP4" s="10"/>
+        <v>5042.7416072250016</v>
+      </c>
+      <c r="AM4" s="10">
+        <f t="shared" si="0"/>
+        <v>5294.8786875862515</v>
+      </c>
+      <c r="AN4" s="10">
+        <f t="shared" si="0"/>
+        <v>5559.6226219655646</v>
+      </c>
+      <c r="AO4" s="10">
+        <f t="shared" si="0"/>
+        <v>5837.6037530638432</v>
+      </c>
+      <c r="AP4" s="10">
+        <f t="shared" si="0"/>
+        <v>6129.4839407170357</v>
+      </c>
       <c r="AQ4" s="10"/>
       <c r="AR4" s="10"/>
       <c r="AS4" s="10"/>
@@ -1334,13 +1412,17 @@
       <c r="BB4" s="10"/>
       <c r="BC4" s="10"/>
       <c r="BD4" s="10"/>
+      <c r="BE4" s="10"/>
+      <c r="BF4" s="10"/>
+      <c r="BG4" s="10"/>
+      <c r="BH4" s="10"/>
     </row>
-    <row r="5" spans="1:141" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:145" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="7">
-        <v>103.80063699999999</v>
+        <v>102.482005</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>34</v>
@@ -1387,49 +1469,45 @@
       <c r="Q5" s="33">
         <v>-79.430000000000007</v>
       </c>
-      <c r="U5" s="12">
+      <c r="R5" s="12">
+        <v>-63.588999999999999</v>
+      </c>
+      <c r="S5" s="12">
+        <v>-71.727999999999994</v>
+      </c>
+      <c r="T5" s="36">
+        <v>-66.938999999999993</v>
+      </c>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="12"/>
+      <c r="Y5" s="12">
         <v>-258.51400000000001</v>
       </c>
-      <c r="V5" s="12">
+      <c r="Z5" s="12">
         <v>-286.63900000000001</v>
       </c>
-      <c r="W5" s="12">
+      <c r="AA5" s="12">
         <v>-308.822</v>
       </c>
-      <c r="X5" s="12">
+      <c r="AB5" s="12">
         <v>-326.64699999999999</v>
       </c>
-      <c r="Y5" s="12">
+      <c r="AC5" s="12">
         <v>-342</v>
       </c>
-      <c r="Z5" s="12">
+      <c r="AD5" s="12">
         <v>-347</v>
       </c>
-      <c r="AA5" s="12">
+      <c r="AE5" s="12">
         <v>-325</v>
       </c>
-      <c r="AB5" s="13">
-        <f>-350</f>
-        <v>-350</v>
-      </c>
-      <c r="AC5" s="12">
-        <f t="shared" ref="AC5:AL5" si="1">-350</f>
-        <v>-350</v>
-      </c>
-      <c r="AD5" s="12">
-        <f t="shared" si="1"/>
-        <v>-350</v>
-      </c>
-      <c r="AE5" s="12">
-        <f t="shared" si="1"/>
-        <v>-350</v>
-      </c>
       <c r="AF5" s="12">
-        <f t="shared" si="1"/>
-        <v>-350</v>
+        <v>-302</v>
       </c>
       <c r="AG5" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="AG5:AP5" si="1">-350</f>
         <v>-350</v>
       </c>
       <c r="AH5" s="12">
@@ -1452,14 +1530,30 @@
         <f t="shared" si="1"/>
         <v>-350</v>
       </c>
+      <c r="AM5" s="12">
+        <f t="shared" si="1"/>
+        <v>-350</v>
+      </c>
+      <c r="AN5" s="12">
+        <f t="shared" si="1"/>
+        <v>-350</v>
+      </c>
+      <c r="AO5" s="12">
+        <f t="shared" si="1"/>
+        <v>-350</v>
+      </c>
+      <c r="AP5" s="12">
+        <f t="shared" si="1"/>
+        <v>-350</v>
+      </c>
     </row>
-    <row r="6" spans="1:141" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:145" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="7">
         <f>B4*B5</f>
-        <v>6840.4619782999998</v>
+        <v>4611.6902250000003</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>35</v>
@@ -1506,75 +1600,83 @@
       <c r="Q6" s="33">
         <v>-670</v>
       </c>
-      <c r="U6" s="12">
+      <c r="R6" s="12">
+        <v>-608.63599999999997</v>
+      </c>
+      <c r="S6" s="12">
+        <v>-711.69200000000001</v>
+      </c>
+      <c r="T6" s="36">
+        <v>-748.60400000000004</v>
+      </c>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12">
         <v>-1178.9680000000001</v>
       </c>
-      <c r="V6" s="12">
+      <c r="Z6" s="12">
         <v>-1377.9380000000001</v>
       </c>
-      <c r="W6" s="12">
+      <c r="AA6" s="12">
         <v>-1579.6679999999999</v>
       </c>
-      <c r="X6" s="12">
+      <c r="AB6" s="12">
         <v>-1790</v>
       </c>
-      <c r="Y6" s="12">
+      <c r="AC6" s="12">
         <v>-2021</v>
       </c>
-      <c r="Z6" s="12">
+      <c r="AD6" s="12">
         <v>-2361</v>
       </c>
-      <c r="AA6" s="12">
+      <c r="AE6" s="12">
         <v>-2671</v>
       </c>
-      <c r="AB6" s="13">
-        <f>AA6*1.06</f>
-        <v>-2831.26</v>
-      </c>
-      <c r="AC6" s="12">
-        <f>AB6*1.075</f>
-        <v>-3043.6044999999999</v>
-      </c>
-      <c r="AD6" s="12">
-        <f t="shared" ref="AD6:AL6" si="2">AC6*1.075</f>
-        <v>-3271.8748374999996</v>
-      </c>
-      <c r="AE6" s="12">
-        <f t="shared" si="2"/>
-        <v>-3517.2654503124995</v>
-      </c>
       <c r="AF6" s="12">
-        <f t="shared" si="2"/>
-        <v>-3781.0603590859369</v>
+        <v>-2731</v>
       </c>
       <c r="AG6" s="12">
-        <f t="shared" si="2"/>
-        <v>-4064.6398860173817</v>
+        <f>AF6*1.01</f>
+        <v>-2758.31</v>
       </c>
       <c r="AH6" s="12">
-        <f t="shared" si="2"/>
-        <v>-4369.4878774686849</v>
+        <f t="shared" ref="AH6:AP6" si="2">AG6*1.05</f>
+        <v>-2896.2255</v>
       </c>
       <c r="AI6" s="12">
-        <f t="shared" si="2"/>
-        <v>-4697.1994682788363</v>
+        <f>AH6*1.06</f>
+        <v>-3069.9990299999999</v>
       </c>
       <c r="AJ6" s="12">
         <f t="shared" si="2"/>
-        <v>-5049.4894283997492</v>
+        <v>-3223.4989814999999</v>
       </c>
       <c r="AK6" s="12">
         <f t="shared" si="2"/>
-        <v>-5428.20113552973</v>
+        <v>-3384.6739305750002</v>
       </c>
       <c r="AL6" s="12">
         <f t="shared" si="2"/>
-        <v>-5835.3162206944598</v>
-      </c>
-      <c r="AM6" s="12"/>
-      <c r="AN6" s="12"/>
-      <c r="AO6" s="12"/>
-      <c r="AP6" s="12"/>
+        <v>-3553.9076271037502</v>
+      </c>
+      <c r="AM6" s="12">
+        <f t="shared" si="2"/>
+        <v>-3731.6030084589379</v>
+      </c>
+      <c r="AN6" s="12">
+        <f t="shared" si="2"/>
+        <v>-3918.183158881885</v>
+      </c>
+      <c r="AO6" s="12">
+        <f t="shared" si="2"/>
+        <v>-4114.0923168259797</v>
+      </c>
+      <c r="AP6" s="12">
+        <f t="shared" si="2"/>
+        <v>-4319.7969326672792</v>
+      </c>
       <c r="AQ6" s="12"/>
       <c r="AR6" s="12"/>
       <c r="AS6" s="12"/>
@@ -1589,16 +1691,21 @@
       <c r="BB6" s="12"/>
       <c r="BC6" s="12"/>
       <c r="BD6" s="12"/>
+      <c r="BE6" s="12"/>
+      <c r="BF6" s="12"/>
+      <c r="BG6" s="12"/>
+      <c r="BH6" s="12"/>
     </row>
-    <row r="7" spans="1:141" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:145" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="7">
-        <v>383</v>
+        <f>R40</f>
+        <v>373.41899999999998</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="D7" s="12">
         <v>-16.963999999999999</v>
@@ -1642,73 +1749,86 @@
       <c r="Q7" s="33">
         <v>-22.582999999999998</v>
       </c>
-      <c r="U7" s="12">
+      <c r="R7" s="12">
+        <v>-22.358000000000001</v>
+      </c>
+      <c r="S7" s="12">
+        <v>-23.245000000000001</v>
+      </c>
+      <c r="T7" s="36">
+        <f>-5.426-17.849</f>
+        <v>-23.274999999999999</v>
+      </c>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12">
         <v>-17.388000000000002</v>
       </c>
-      <c r="V7" s="12">
+      <c r="Z7" s="12">
         <v>-53.850999999999999</v>
       </c>
-      <c r="W7" s="12">
+      <c r="AA7" s="12">
         <v>-58</v>
       </c>
-      <c r="X7" s="12">
+      <c r="AB7" s="12">
         <v>-60</v>
       </c>
-      <c r="Y7" s="12">
+      <c r="AC7" s="12">
         <v>-71</v>
       </c>
-      <c r="Z7" s="12">
+      <c r="AD7" s="12">
         <v>-79</v>
       </c>
-      <c r="AA7" s="12">
+      <c r="AE7" s="12">
         <v>-93</v>
       </c>
-      <c r="AB7" s="13">
-        <f>AA7*1.02</f>
-        <v>-94.86</v>
-      </c>
-      <c r="AC7" s="12">
-        <f t="shared" ref="AC7:AL7" si="3">AB7*1.02</f>
-        <v>-96.757199999999997</v>
-      </c>
-      <c r="AD7" s="12">
-        <f t="shared" si="3"/>
-        <v>-98.692344000000006</v>
-      </c>
-      <c r="AE7" s="12">
-        <f t="shared" si="3"/>
-        <v>-100.66619088</v>
-      </c>
       <c r="AF7" s="12">
-        <f t="shared" si="3"/>
-        <v>-102.6795146976</v>
+        <v>-90</v>
       </c>
       <c r="AG7" s="12">
-        <f t="shared" si="3"/>
-        <v>-104.733104991552</v>
+        <f>AF7*1.01</f>
+        <v>-90.9</v>
       </c>
       <c r="AH7" s="12">
-        <f t="shared" si="3"/>
-        <v>-106.82776709138304</v>
+        <f t="shared" ref="AH7:AP7" si="3">AG7*1.02</f>
+        <v>-92.718000000000004</v>
       </c>
       <c r="AI7" s="12">
         <f t="shared" si="3"/>
-        <v>-108.9643224332107</v>
+        <v>-94.572360000000003</v>
       </c>
       <c r="AJ7" s="12">
         <f t="shared" si="3"/>
-        <v>-111.14360888187491</v>
+        <v>-96.463807200000005</v>
       </c>
       <c r="AK7" s="12">
         <f t="shared" si="3"/>
-        <v>-113.36648105951241</v>
+        <v>-98.393083344000004</v>
       </c>
       <c r="AL7" s="12">
         <f t="shared" si="3"/>
-        <v>-115.63381068070267</v>
+        <v>-100.36094501088</v>
+      </c>
+      <c r="AM7" s="12">
+        <f t="shared" si="3"/>
+        <v>-102.36816391109761</v>
+      </c>
+      <c r="AN7" s="12">
+        <f t="shared" si="3"/>
+        <v>-104.41552718931956</v>
+      </c>
+      <c r="AO7" s="12">
+        <f t="shared" si="3"/>
+        <v>-106.50383773310595</v>
+      </c>
+      <c r="AP7" s="12">
+        <f t="shared" si="3"/>
+        <v>-108.63391448776808</v>
       </c>
     </row>
-    <row r="8" spans="1:141" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:145" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -1760,79 +1880,91 @@
       <c r="Q8" s="33">
         <v>-2</v>
       </c>
-      <c r="U8" s="12">
+      <c r="R8" s="12">
+        <v>-2.1960000000000002</v>
+      </c>
+      <c r="S8" s="12">
+        <v>-2</v>
+      </c>
+      <c r="T8" s="36">
+        <v>-2</v>
+      </c>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="12">
         <v>-7.4</v>
       </c>
-      <c r="V8" s="12">
+      <c r="Z8" s="12">
         <v>-6.8</v>
       </c>
-      <c r="W8" s="12">
+      <c r="AA8" s="12">
         <v>-8.9</v>
       </c>
-      <c r="X8" s="12">
+      <c r="AB8" s="12">
         <v>-9.5</v>
       </c>
-      <c r="Y8" s="12">
+      <c r="AC8" s="12">
         <v>-8</v>
       </c>
-      <c r="Z8" s="12">
+      <c r="AD8" s="12">
         <v>-18</v>
       </c>
-      <c r="AA8" s="12">
+      <c r="AE8" s="12">
         <v>-27</v>
       </c>
-      <c r="AB8" s="13">
-        <f>AA8*1.1</f>
-        <v>-29.700000000000003</v>
-      </c>
-      <c r="AC8" s="12">
-        <f t="shared" ref="AC8:AL9" si="4">AB8*1.1</f>
-        <v>-32.670000000000009</v>
-      </c>
-      <c r="AD8" s="12">
-        <f t="shared" si="4"/>
-        <v>-35.937000000000012</v>
-      </c>
-      <c r="AE8" s="12">
-        <f t="shared" si="4"/>
-        <v>-39.530700000000017</v>
-      </c>
       <c r="AF8" s="12">
-        <f t="shared" si="4"/>
-        <v>-43.483770000000021</v>
+        <v>-8</v>
       </c>
       <c r="AG8" s="12">
-        <f t="shared" si="4"/>
-        <v>-47.832147000000028</v>
+        <f t="shared" ref="AG8:AG9" si="4">AF8*1.01</f>
+        <v>-8.08</v>
       </c>
       <c r="AH8" s="12">
-        <f t="shared" si="4"/>
-        <v>-52.615361700000037</v>
+        <f t="shared" ref="AH8:AP8" si="5">AG8*1.1</f>
+        <v>-8.8880000000000017</v>
       </c>
       <c r="AI8" s="12">
-        <f t="shared" si="4"/>
-        <v>-57.876897870000043</v>
+        <f t="shared" si="5"/>
+        <v>-9.7768000000000033</v>
       </c>
       <c r="AJ8" s="12">
-        <f t="shared" si="4"/>
-        <v>-63.664587657000055</v>
+        <f t="shared" si="5"/>
+        <v>-10.754480000000004</v>
       </c>
       <c r="AK8" s="12">
-        <f t="shared" si="4"/>
-        <v>-70.031046422700072</v>
+        <f t="shared" si="5"/>
+        <v>-11.829928000000006</v>
       </c>
       <c r="AL8" s="12">
-        <f t="shared" si="4"/>
-        <v>-77.034151064970089</v>
+        <f t="shared" si="5"/>
+        <v>-13.012920800000007</v>
+      </c>
+      <c r="AM8" s="12">
+        <f t="shared" si="5"/>
+        <v>-14.314212880000008</v>
+      </c>
+      <c r="AN8" s="12">
+        <f t="shared" si="5"/>
+        <v>-15.745634168000011</v>
+      </c>
+      <c r="AO8" s="12">
+        <f t="shared" si="5"/>
+        <v>-17.320197584800013</v>
+      </c>
+      <c r="AP8" s="12">
+        <f t="shared" si="5"/>
+        <v>-19.052217343280017</v>
       </c>
     </row>
-    <row r="9" spans="1:141" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:145" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="8">
         <f>B6-B7+B8</f>
-        <v>6457.4619782999998</v>
+        <v>4238.2712250000004</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>38</v>
@@ -1879,216 +2011,235 @@
       <c r="Q9" s="33">
         <v>-71.245000000000005</v>
       </c>
-      <c r="U9" s="12">
+      <c r="R9" s="12">
+        <v>-82.1</v>
+      </c>
+      <c r="S9" s="12">
+        <v>-86.212000000000003</v>
+      </c>
+      <c r="T9" s="36">
+        <v>-68.965000000000003</v>
+      </c>
+      <c r="U9" s="12"/>
+      <c r="V9" s="12"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="12"/>
+      <c r="Y9" s="12">
         <v>-192</v>
       </c>
-      <c r="V9" s="12">
+      <c r="Z9" s="12">
         <v>-174</v>
       </c>
-      <c r="W9" s="12">
+      <c r="AA9" s="12">
         <v>-131.827</v>
       </c>
-      <c r="X9" s="12">
+      <c r="AB9" s="12">
         <v>-168.66</v>
       </c>
-      <c r="Y9" s="12">
+      <c r="AC9" s="12">
         <v>-259</v>
       </c>
-      <c r="Z9" s="12">
+      <c r="AD9" s="12">
         <v>-313</v>
       </c>
-      <c r="AA9" s="12">
+      <c r="AE9" s="12">
         <v>-315</v>
       </c>
-      <c r="AB9" s="13">
-        <f>AA9*1.1</f>
-        <v>-346.5</v>
-      </c>
-      <c r="AC9" s="12">
-        <f t="shared" si="4"/>
-        <v>-381.15000000000003</v>
-      </c>
-      <c r="AD9" s="12">
-        <f t="shared" si="4"/>
-        <v>-419.26500000000004</v>
-      </c>
-      <c r="AE9" s="12">
-        <f t="shared" si="4"/>
-        <v>-461.19150000000008</v>
-      </c>
       <c r="AF9" s="12">
-        <f t="shared" si="4"/>
-        <v>-507.31065000000012</v>
+        <v>-307</v>
       </c>
       <c r="AG9" s="12">
         <f t="shared" si="4"/>
-        <v>-558.04171500000018</v>
+        <v>-310.07</v>
       </c>
       <c r="AH9" s="12">
-        <f t="shared" si="4"/>
-        <v>-613.84588650000023</v>
+        <f t="shared" ref="AH9:AP9" si="6">AG9*1.04</f>
+        <v>-322.47280000000001</v>
       </c>
       <c r="AI9" s="12">
-        <f t="shared" si="4"/>
-        <v>-675.2304751500003</v>
+        <f t="shared" si="6"/>
+        <v>-335.371712</v>
       </c>
       <c r="AJ9" s="12">
-        <f t="shared" si="4"/>
-        <v>-742.75352266500045</v>
+        <f t="shared" si="6"/>
+        <v>-348.78658048</v>
       </c>
       <c r="AK9" s="12">
-        <f t="shared" si="4"/>
-        <v>-817.02887493150058</v>
+        <f t="shared" si="6"/>
+        <v>-362.73804369920003</v>
       </c>
       <c r="AL9" s="12">
-        <f t="shared" si="4"/>
-        <v>-898.7317624246507</v>
+        <f t="shared" si="6"/>
+        <v>-377.24756544716803</v>
+      </c>
+      <c r="AM9" s="12">
+        <f t="shared" si="6"/>
+        <v>-392.33746806505474</v>
+      </c>
+      <c r="AN9" s="12">
+        <f t="shared" si="6"/>
+        <v>-408.03096678765695</v>
+      </c>
+      <c r="AO9" s="12">
+        <f t="shared" si="6"/>
+        <v>-424.35220545916326</v>
+      </c>
+      <c r="AP9" s="12">
+        <f t="shared" si="6"/>
+        <v>-441.3262936775298</v>
       </c>
     </row>
-    <row r="10" spans="1:141" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:145" x14ac:dyDescent="0.25">
       <c r="B10" s="6"/>
       <c r="C10" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D10" s="10">
-        <f t="shared" ref="D10:S10" si="5">SUM(D4:D9)</f>
+        <f t="shared" ref="D10:T10" si="7">SUM(D4:D9)</f>
         <v>122.78</v>
       </c>
       <c r="E10" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>89.204000000000079</v>
       </c>
       <c r="F10" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>73.395999999999987</v>
       </c>
       <c r="G10" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>116.312</v>
       </c>
       <c r="H10" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>131.63600000000008</v>
       </c>
       <c r="I10" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>89.026999999999944</v>
       </c>
       <c r="J10" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>80.011999999999972</v>
       </c>
       <c r="K10" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>106.31700000000006</v>
       </c>
       <c r="L10" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>134.96499999999986</v>
       </c>
       <c r="M10" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>135.55000000000001</v>
       </c>
       <c r="N10" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>100.95000000000006</v>
       </c>
       <c r="O10" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>119.7529999999999</v>
       </c>
       <c r="P10" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>155.20700000000011</v>
       </c>
       <c r="Q10" s="32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>123.44900000000004</v>
       </c>
       <c r="R10" s="10">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>91.595000000000027</v>
       </c>
       <c r="S10" s="10">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T10" s="4"/>
-      <c r="U10" s="10">
-        <f t="shared" ref="U10:AA10" si="6">SUM(U4:U9)</f>
+        <f t="shared" si="7"/>
+        <v>103.55799999999998</v>
+      </c>
+      <c r="T10" s="10">
+        <f t="shared" si="7"/>
+        <v>127.21699999999998</v>
+      </c>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10">
+        <f t="shared" ref="Y10:AE10" si="8">SUM(Y4:Y9)</f>
         <v>192.44100000000009</v>
       </c>
-      <c r="V10" s="10">
-        <f t="shared" si="6"/>
+      <c r="Z10" s="10">
+        <f t="shared" si="8"/>
         <v>232.77199999999976</v>
       </c>
-      <c r="W10" s="10">
-        <f t="shared" si="6"/>
+      <c r="AA10" s="10">
+        <f t="shared" si="8"/>
         <v>314.62700000000007</v>
       </c>
-      <c r="X10" s="10">
-        <f t="shared" si="6"/>
+      <c r="AB10" s="10">
+        <f t="shared" si="8"/>
         <v>340.1930000000001</v>
       </c>
-      <c r="Y10" s="10">
-        <f t="shared" si="6"/>
+      <c r="AC10" s="10">
+        <f t="shared" si="8"/>
         <v>401</v>
       </c>
-      <c r="Z10" s="10">
-        <f t="shared" si="6"/>
+      <c r="AD10" s="10">
+        <f t="shared" si="8"/>
         <v>408</v>
       </c>
-      <c r="AA10" s="10">
-        <f t="shared" si="6"/>
+      <c r="AE10" s="10">
+        <f t="shared" si="8"/>
         <v>490</v>
       </c>
-      <c r="AB10" s="11">
-        <f t="shared" ref="AB10:AL10" si="7">SUM(AB4:AB9)</f>
-        <v>503.93999999999994</v>
-      </c>
-      <c r="AC10" s="10">
-        <f t="shared" si="7"/>
-        <v>563.79780000000051</v>
-      </c>
-      <c r="AD10" s="10">
-        <f t="shared" si="7"/>
-        <v>627.30878100000086</v>
-      </c>
-      <c r="AE10" s="10">
-        <f t="shared" si="7"/>
-        <v>694.65496849500028</v>
-      </c>
       <c r="AF10" s="10">
-        <f t="shared" si="7"/>
-        <v>766.02267663052544</v>
+        <f t="shared" ref="AF10:AP10" si="9">SUM(AF4:AF9)</f>
+        <v>474</v>
       </c>
       <c r="AG10" s="10">
-        <f t="shared" si="7"/>
-        <v>841.60189018618314</v>
+        <f t="shared" si="9"/>
+        <v>433.75999999999993</v>
       </c>
       <c r="AH10" s="10">
-        <f t="shared" si="7"/>
-        <v>921.58550617468245</v>
+        <f t="shared" si="9"/>
+        <v>478.37170000000037</v>
       </c>
       <c r="AI10" s="10">
-        <f t="shared" si="7"/>
-        <v>1006.1684151228089</v>
+        <f t="shared" si="9"/>
+        <v>496.38989800000024</v>
       </c>
       <c r="AJ10" s="10">
-        <f t="shared" si="7"/>
-        <v>1095.5463996653459</v>
+        <f t="shared" si="9"/>
+        <v>544.41144082000085</v>
       </c>
       <c r="AK10" s="10">
-        <f t="shared" si="7"/>
-        <v>1189.9148253706999</v>
+        <f t="shared" si="9"/>
+        <v>594.97606888180076</v>
       </c>
       <c r="AL10" s="10">
-        <f t="shared" si="7"/>
-        <v>1289.4670956979194</v>
+        <f t="shared" si="9"/>
+        <v>648.21254886320344</v>
+      </c>
+      <c r="AM10" s="10">
+        <f t="shared" si="9"/>
+        <v>704.25583427116135</v>
+      </c>
+      <c r="AN10" s="10">
+        <f t="shared" si="9"/>
+        <v>763.24733493870303</v>
+      </c>
+      <c r="AO10" s="10">
+        <f t="shared" si="9"/>
+        <v>825.33519546079424</v>
+      </c>
+      <c r="AP10" s="10">
+        <f t="shared" si="9"/>
+        <v>890.67458254117855</v>
       </c>
     </row>
-    <row r="11" spans="1:141" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:145" x14ac:dyDescent="0.25">
       <c r="C11" s="1" t="s">
         <v>40</v>
       </c>
@@ -2134,41 +2285,42 @@
       <c r="Q11" s="33">
         <v>0</v>
       </c>
-      <c r="U11" s="12">
+      <c r="R11" s="12">
+        <v>-1.19</v>
+      </c>
+      <c r="S11" s="12">
+        <v>-1.2410000000000001</v>
+      </c>
+      <c r="T11" s="36">
+        <v>-1.377</v>
+      </c>
+      <c r="U11" s="12"/>
+      <c r="V11" s="12"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="12"/>
+      <c r="Y11" s="12">
         <v>0</v>
       </c>
-      <c r="V11" s="12">
+      <c r="Z11" s="12">
         <v>-3.8</v>
       </c>
-      <c r="W11" s="12">
+      <c r="AA11" s="12">
         <v>-2.8</v>
       </c>
-      <c r="X11" s="12">
+      <c r="AB11" s="12">
         <v>-5</v>
       </c>
-      <c r="Y11" s="12">
+      <c r="AC11" s="12">
         <v>-1</v>
       </c>
-      <c r="Z11" s="12">
+      <c r="AD11" s="12">
         <v>11</v>
       </c>
-      <c r="AA11" s="12">
+      <c r="AE11" s="12">
         <v>1</v>
       </c>
-      <c r="AB11" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="12">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="12">
-        <v>0</v>
-      </c>
       <c r="AF11" s="12">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AG11" s="12">
         <v>0</v>
@@ -2188,149 +2340,169 @@
       <c r="AL11" s="12">
         <v>0</v>
       </c>
+      <c r="AM11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:141" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:145" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="12">
-        <f t="shared" ref="D12:S12" si="8">SUM(D10:D11)</f>
+        <f t="shared" ref="D12:T12" si="10">SUM(D10:D11)</f>
         <v>121.89100000000001</v>
       </c>
       <c r="E12" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>88.753000000000085</v>
       </c>
       <c r="F12" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>73.35799999999999</v>
       </c>
       <c r="G12" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>116.982</v>
       </c>
       <c r="H12" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>133.71400000000008</v>
       </c>
       <c r="I12" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>90.53199999999994</v>
       </c>
       <c r="J12" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>81.785999999999973</v>
       </c>
       <c r="K12" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>112.38600000000007</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>134.87399999999985</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>135.87400000000002</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>100.72500000000007</v>
       </c>
       <c r="O12" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>120.5709999999999</v>
       </c>
       <c r="P12" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>156.9070000000001</v>
       </c>
       <c r="Q12" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>123.44900000000004</v>
       </c>
       <c r="R12" s="12">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>90.40500000000003</v>
       </c>
       <c r="S12" s="12">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="12">
-        <f t="shared" ref="U12:AB12" si="9">SUM(U10:U11)</f>
+        <f t="shared" si="10"/>
+        <v>102.31699999999998</v>
+      </c>
+      <c r="T12" s="12">
+        <f t="shared" si="10"/>
+        <v>125.83999999999999</v>
+      </c>
+      <c r="U12" s="12"/>
+      <c r="V12" s="12"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="12"/>
+      <c r="Y12" s="12">
+        <f t="shared" ref="Y12:AF12" si="11">SUM(Y10:Y11)</f>
         <v>192.44100000000009</v>
       </c>
-      <c r="V12" s="12">
-        <f t="shared" si="9"/>
+      <c r="Z12" s="12">
+        <f t="shared" si="11"/>
         <v>228.97199999999975</v>
       </c>
-      <c r="W12" s="12">
-        <f t="shared" si="9"/>
+      <c r="AA12" s="12">
+        <f t="shared" si="11"/>
         <v>311.82700000000006</v>
       </c>
-      <c r="X12" s="12">
-        <f t="shared" si="9"/>
+      <c r="AB12" s="12">
+        <f t="shared" si="11"/>
         <v>335.1930000000001</v>
       </c>
-      <c r="Y12" s="12">
-        <f t="shared" si="9"/>
+      <c r="AC12" s="12">
+        <f t="shared" si="11"/>
         <v>400</v>
       </c>
-      <c r="Z12" s="12">
-        <f t="shared" si="9"/>
+      <c r="AD12" s="12">
+        <f t="shared" si="11"/>
         <v>419</v>
       </c>
-      <c r="AA12" s="12">
-        <f t="shared" si="9"/>
+      <c r="AE12" s="12">
+        <f t="shared" si="11"/>
         <v>491</v>
       </c>
-      <c r="AB12" s="13">
-        <f t="shared" si="9"/>
-        <v>503.93999999999994</v>
-      </c>
-      <c r="AC12" s="12">
-        <f t="shared" ref="AC12:AL12" si="10">SUM(AC10:AC11)</f>
-        <v>563.79780000000051</v>
-      </c>
-      <c r="AD12" s="12">
-        <f t="shared" si="10"/>
-        <v>627.30878100000086</v>
-      </c>
-      <c r="AE12" s="12">
-        <f t="shared" si="10"/>
-        <v>694.65496849500028</v>
-      </c>
       <c r="AF12" s="12">
-        <f t="shared" si="10"/>
-        <v>766.02267663052544</v>
+        <f t="shared" si="11"/>
+        <v>473</v>
       </c>
       <c r="AG12" s="12">
-        <f t="shared" si="10"/>
-        <v>841.60189018618314</v>
+        <f t="shared" ref="AG12:AP12" si="12">SUM(AG10:AG11)</f>
+        <v>433.75999999999993</v>
       </c>
       <c r="AH12" s="12">
-        <f t="shared" si="10"/>
-        <v>921.58550617468245</v>
+        <f t="shared" si="12"/>
+        <v>478.37170000000037</v>
       </c>
       <c r="AI12" s="12">
-        <f t="shared" si="10"/>
-        <v>1006.1684151228089</v>
+        <f t="shared" si="12"/>
+        <v>496.38989800000024</v>
       </c>
       <c r="AJ12" s="12">
-        <f t="shared" si="10"/>
-        <v>1095.5463996653459</v>
+        <f t="shared" si="12"/>
+        <v>544.41144082000085</v>
       </c>
       <c r="AK12" s="12">
-        <f t="shared" si="10"/>
-        <v>1189.9148253706999</v>
+        <f t="shared" si="12"/>
+        <v>594.97606888180076</v>
       </c>
       <c r="AL12" s="12">
-        <f t="shared" si="10"/>
-        <v>1289.4670956979194</v>
+        <f t="shared" si="12"/>
+        <v>648.21254886320344</v>
+      </c>
+      <c r="AM12" s="12">
+        <f t="shared" si="12"/>
+        <v>704.25583427116135</v>
+      </c>
+      <c r="AN12" s="12">
+        <f t="shared" si="12"/>
+        <v>763.24733493870303</v>
+      </c>
+      <c r="AO12" s="12">
+        <f t="shared" si="12"/>
+        <v>825.33519546079424</v>
+      </c>
+      <c r="AP12" s="12">
+        <f t="shared" si="12"/>
+        <v>890.67458254117855</v>
       </c>
     </row>
-    <row r="13" spans="1:141" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:145" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
         <v>42</v>
       </c>
@@ -2376,627 +2548,647 @@
       <c r="Q13" s="33">
         <v>-27.263000000000002</v>
       </c>
-      <c r="U13" s="12">
+      <c r="R13" s="12">
+        <v>-20.315999999999999</v>
+      </c>
+      <c r="S13" s="12">
+        <v>-30.268000000000001</v>
+      </c>
+      <c r="T13" s="36">
+        <v>-28.431999999999999</v>
+      </c>
+      <c r="U13" s="12"/>
+      <c r="V13" s="12"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12">
         <v>-41</v>
       </c>
-      <c r="V13" s="12">
+      <c r="Z13" s="12">
         <v>-48</v>
       </c>
-      <c r="W13" s="12">
+      <c r="AA13" s="12">
         <v>-70.5</v>
       </c>
-      <c r="X13" s="12">
+      <c r="AB13" s="12">
         <v>-69.256</v>
       </c>
-      <c r="Y13" s="12">
+      <c r="AC13" s="12">
         <v>-85</v>
       </c>
-      <c r="Z13" s="12">
+      <c r="AD13" s="12">
         <v>-93</v>
       </c>
-      <c r="AA13" s="12">
+      <c r="AE13" s="12">
         <v>-108</v>
       </c>
-      <c r="AB13" s="13">
-        <f>AB12*-0.22</f>
-        <v>-110.86679999999998</v>
-      </c>
-      <c r="AC13" s="12">
-        <f t="shared" ref="AC13:AL13" si="11">AC12*-0.22</f>
-        <v>-124.03551600000011</v>
-      </c>
-      <c r="AD13" s="12">
-        <f t="shared" si="11"/>
-        <v>-138.00793182000018</v>
-      </c>
-      <c r="AE13" s="12">
-        <f t="shared" si="11"/>
-        <v>-152.82409306890005</v>
-      </c>
       <c r="AF13" s="12">
-        <f t="shared" si="11"/>
-        <v>-168.5249888587156</v>
+        <v>-114</v>
       </c>
       <c r="AG13" s="12">
-        <f t="shared" si="11"/>
-        <v>-185.15241584096029</v>
+        <f t="shared" ref="AG13:AP13" si="13">AG12*-0.22</f>
+        <v>-95.427199999999985</v>
       </c>
       <c r="AH13" s="12">
-        <f t="shared" si="11"/>
-        <v>-202.74881135843015</v>
+        <f t="shared" si="13"/>
+        <v>-105.24177400000008</v>
       </c>
       <c r="AI13" s="12">
-        <f t="shared" si="11"/>
-        <v>-221.35705132701796</v>
+        <f t="shared" si="13"/>
+        <v>-109.20577756000006</v>
       </c>
       <c r="AJ13" s="12">
-        <f t="shared" si="11"/>
-        <v>-241.02020792637612</v>
+        <f t="shared" si="13"/>
+        <v>-119.77051698040019</v>
       </c>
       <c r="AK13" s="12">
-        <f t="shared" si="11"/>
-        <v>-261.78126158155396</v>
+        <f t="shared" si="13"/>
+        <v>-130.89473515399618</v>
       </c>
       <c r="AL13" s="12">
-        <f t="shared" si="11"/>
-        <v>-283.68276105354227</v>
+        <f t="shared" si="13"/>
+        <v>-142.60676074990477</v>
+      </c>
+      <c r="AM13" s="12">
+        <f t="shared" si="13"/>
+        <v>-154.93628353965551</v>
+      </c>
+      <c r="AN13" s="12">
+        <f t="shared" si="13"/>
+        <v>-167.91441368651468</v>
+      </c>
+      <c r="AO13" s="12">
+        <f t="shared" si="13"/>
+        <v>-181.57374300137474</v>
+      </c>
+      <c r="AP13" s="12">
+        <f t="shared" si="13"/>
+        <v>-195.94840815905928</v>
       </c>
     </row>
-    <row r="14" spans="1:141" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:145" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="9"/>
       <c r="C14" s="4" t="s">
         <v>43</v>
       </c>
       <c r="D14" s="10">
-        <f t="shared" ref="D14:S14" si="12">SUM(D12:D13)</f>
+        <f t="shared" ref="D14:T14" si="14">SUM(D12:D13)</f>
         <v>95.5</v>
       </c>
       <c r="E14" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>69.779000000000082</v>
       </c>
       <c r="F14" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>56.751999999999988</v>
       </c>
       <c r="G14" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>94.283999999999992</v>
       </c>
       <c r="H14" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>104.68900000000008</v>
       </c>
       <c r="I14" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>69.389999999999944</v>
       </c>
       <c r="J14" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>62.895999999999972</v>
       </c>
       <c r="K14" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>88.317000000000064</v>
       </c>
       <c r="L14" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>105.15099999999985</v>
       </c>
       <c r="M14" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>103.98400000000002</v>
       </c>
       <c r="N14" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>77.895000000000067</v>
       </c>
       <c r="O14" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>97.268999999999892</v>
       </c>
       <c r="P14" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>120.8830000000001</v>
       </c>
       <c r="Q14" s="32">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>96.186000000000035</v>
       </c>
       <c r="R14" s="10">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>70.089000000000027</v>
       </c>
       <c r="S14" s="10">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="10">
-        <f t="shared" ref="U14:AA14" si="13">SUM(U12:U13)</f>
+        <f t="shared" si="14"/>
+        <v>72.048999999999978</v>
+      </c>
+      <c r="T14" s="10">
+        <f t="shared" si="14"/>
+        <v>97.407999999999987</v>
+      </c>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10">
+        <f t="shared" ref="Y14:AE14" si="15">SUM(Y12:Y13)</f>
         <v>151.44100000000009</v>
       </c>
-      <c r="V14" s="10">
-        <f t="shared" si="13"/>
+      <c r="Z14" s="10">
+        <f t="shared" si="15"/>
         <v>180.97199999999975</v>
       </c>
-      <c r="W14" s="10">
-        <f t="shared" si="13"/>
+      <c r="AA14" s="10">
+        <f t="shared" si="15"/>
         <v>241.32700000000006</v>
       </c>
-      <c r="X14" s="10">
-        <f t="shared" si="13"/>
+      <c r="AB14" s="10">
+        <f t="shared" si="15"/>
         <v>265.93700000000013</v>
       </c>
-      <c r="Y14" s="10">
-        <f t="shared" si="13"/>
+      <c r="AC14" s="10">
+        <f t="shared" si="15"/>
         <v>315</v>
       </c>
-      <c r="Z14" s="10">
-        <f t="shared" si="13"/>
+      <c r="AD14" s="10">
+        <f t="shared" si="15"/>
         <v>326</v>
       </c>
-      <c r="AA14" s="10">
-        <f t="shared" si="13"/>
+      <c r="AE14" s="10">
+        <f t="shared" si="15"/>
         <v>383</v>
       </c>
-      <c r="AB14" s="11">
-        <f t="shared" ref="AB14:AL14" si="14">SUM(AB12:AB13)</f>
-        <v>393.07319999999993</v>
-      </c>
-      <c r="AC14" s="10">
-        <f t="shared" si="14"/>
-        <v>439.76228400000036</v>
-      </c>
-      <c r="AD14" s="10">
-        <f t="shared" si="14"/>
-        <v>489.30084918000068</v>
-      </c>
-      <c r="AE14" s="10">
-        <f t="shared" si="14"/>
-        <v>541.83087542610019</v>
-      </c>
       <c r="AF14" s="10">
-        <f t="shared" si="14"/>
-        <v>597.49768777180986</v>
+        <f t="shared" ref="AF14:AP14" si="16">SUM(AF12:AF13)</f>
+        <v>359</v>
       </c>
       <c r="AG14" s="10">
-        <f t="shared" si="14"/>
-        <v>656.44947434522282</v>
+        <f t="shared" si="16"/>
+        <v>338.33279999999996</v>
       </c>
       <c r="AH14" s="10">
-        <f t="shared" si="14"/>
-        <v>718.83669481625225</v>
+        <f t="shared" si="16"/>
+        <v>373.1299260000003</v>
       </c>
       <c r="AI14" s="10">
-        <f t="shared" si="14"/>
-        <v>784.81136379579095</v>
+        <f t="shared" si="16"/>
+        <v>387.18412044000019</v>
       </c>
       <c r="AJ14" s="10">
-        <f t="shared" si="14"/>
-        <v>854.52619173896983</v>
+        <f t="shared" si="16"/>
+        <v>424.64092383960065</v>
       </c>
       <c r="AK14" s="10">
-        <f t="shared" si="14"/>
-        <v>928.13356378914591</v>
+        <f t="shared" si="16"/>
+        <v>464.08133372780458</v>
       </c>
       <c r="AL14" s="10">
-        <f t="shared" si="14"/>
-        <v>1005.7843346443772</v>
+        <f t="shared" si="16"/>
+        <v>505.60578811329867</v>
       </c>
       <c r="AM14" s="10">
-        <f>AL14*(1+$AO$18)</f>
-        <v>995.72649129793342</v>
+        <f t="shared" si="16"/>
+        <v>549.31955073150584</v>
       </c>
       <c r="AN14" s="10">
-        <f t="shared" ref="AN14:CY14" si="15">AM14*(1+$AO$18)</f>
-        <v>985.7692263849541</v>
+        <f t="shared" si="16"/>
+        <v>595.33292125218838</v>
       </c>
       <c r="AO14" s="10">
-        <f>AN14*(1+$AO$18)</f>
-        <v>975.91153412110452</v>
+        <f t="shared" si="16"/>
+        <v>643.7614524594195</v>
       </c>
       <c r="AP14" s="10">
-        <f t="shared" si="15"/>
-        <v>966.15241877989342</v>
+        <f t="shared" si="16"/>
+        <v>694.72617438211932</v>
       </c>
       <c r="AQ14" s="10">
-        <f t="shared" si="15"/>
-        <v>956.49089459209449</v>
+        <f>AP14*(1+$AS$18)</f>
+        <v>687.77891263829815</v>
       </c>
       <c r="AR14" s="10">
-        <f t="shared" si="15"/>
-        <v>946.92598564617356</v>
+        <f t="shared" ref="AR14:DC14" si="17">AQ14*(1+$AS$18)</f>
+        <v>680.90112351191522</v>
       </c>
       <c r="AS14" s="10">
-        <f t="shared" si="15"/>
-        <v>937.45672578971187</v>
+        <f>AR14*(1+$AS$18)</f>
+        <v>674.092112276796</v>
       </c>
       <c r="AT14" s="10">
-        <f t="shared" si="15"/>
-        <v>928.08215853181468</v>
+        <f t="shared" si="17"/>
+        <v>667.35119115402802</v>
       </c>
       <c r="AU14" s="10">
-        <f t="shared" si="15"/>
-        <v>918.80133694649658</v>
+        <f t="shared" si="17"/>
+        <v>660.67767924248778</v>
       </c>
       <c r="AV14" s="10">
-        <f t="shared" si="15"/>
-        <v>909.61332357703157</v>
+        <f t="shared" si="17"/>
+        <v>654.07090245006293</v>
       </c>
       <c r="AW14" s="10">
-        <f t="shared" si="15"/>
-        <v>900.5171903412612</v>
+        <f t="shared" si="17"/>
+        <v>647.53019342556229</v>
       </c>
       <c r="AX14" s="10">
-        <f t="shared" si="15"/>
-        <v>891.51201843784861</v>
+        <f t="shared" si="17"/>
+        <v>641.05489149130665</v>
       </c>
       <c r="AY14" s="10">
-        <f t="shared" si="15"/>
-        <v>882.59689825347016</v>
+        <f t="shared" si="17"/>
+        <v>634.64434257639357</v>
       </c>
       <c r="AZ14" s="10">
-        <f t="shared" si="15"/>
-        <v>873.77092927093543</v>
+        <f t="shared" si="17"/>
+        <v>628.29789915062963</v>
       </c>
       <c r="BA14" s="10">
-        <f t="shared" si="15"/>
-        <v>865.03321997822604</v>
+        <f t="shared" si="17"/>
+        <v>622.01492015912333</v>
       </c>
       <c r="BB14" s="10">
-        <f t="shared" si="15"/>
-        <v>856.38288777844377</v>
+        <f t="shared" si="17"/>
+        <v>615.79477095753214</v>
       </c>
       <c r="BC14" s="10">
-        <f t="shared" si="15"/>
-        <v>847.81905890065934</v>
+        <f t="shared" si="17"/>
+        <v>609.63682324795684</v>
       </c>
       <c r="BD14" s="10">
-        <f t="shared" si="15"/>
-        <v>839.3408683116528</v>
+        <f t="shared" si="17"/>
+        <v>603.54045501547728</v>
       </c>
       <c r="BE14" s="10">
-        <f t="shared" si="15"/>
-        <v>830.94745962853631</v>
+        <f t="shared" si="17"/>
+        <v>597.50505046532248</v>
       </c>
       <c r="BF14" s="10">
-        <f t="shared" si="15"/>
-        <v>822.63798503225098</v>
+        <f t="shared" si="17"/>
+        <v>591.52999996066922</v>
       </c>
       <c r="BG14" s="10">
-        <f t="shared" si="15"/>
-        <v>814.41160518192851</v>
+        <f t="shared" si="17"/>
+        <v>585.61469996106257</v>
       </c>
       <c r="BH14" s="10">
-        <f t="shared" si="15"/>
-        <v>806.2674891301092</v>
+        <f t="shared" si="17"/>
+        <v>579.75855296145198</v>
       </c>
       <c r="BI14" s="10">
-        <f t="shared" si="15"/>
-        <v>798.20481423880813</v>
+        <f t="shared" si="17"/>
+        <v>573.9609674318375</v>
       </c>
       <c r="BJ14" s="10">
-        <f t="shared" si="15"/>
-        <v>790.22276609642006</v>
+        <f t="shared" si="17"/>
+        <v>568.22135775751917</v>
       </c>
       <c r="BK14" s="10">
-        <f t="shared" si="15"/>
-        <v>782.32053843545589</v>
+        <f t="shared" si="17"/>
+        <v>562.53914417994395</v>
       </c>
       <c r="BL14" s="10">
-        <f t="shared" si="15"/>
-        <v>774.49733305110135</v>
+        <f t="shared" si="17"/>
+        <v>556.91375273814447</v>
       </c>
       <c r="BM14" s="10">
-        <f t="shared" si="15"/>
-        <v>766.75235972059033</v>
+        <f t="shared" si="17"/>
+        <v>551.34461521076298</v>
       </c>
       <c r="BN14" s="10">
-        <f t="shared" si="15"/>
-        <v>759.08483612338443</v>
+        <f t="shared" si="17"/>
+        <v>545.83116905865529</v>
       </c>
       <c r="BO14" s="10">
-        <f t="shared" si="15"/>
-        <v>751.4939877621506</v>
+        <f t="shared" si="17"/>
+        <v>540.37285736806871</v>
       </c>
       <c r="BP14" s="10">
-        <f t="shared" si="15"/>
-        <v>743.97904788452911</v>
+        <f t="shared" si="17"/>
+        <v>534.96912879438798</v>
       </c>
       <c r="BQ14" s="10">
-        <f t="shared" si="15"/>
-        <v>736.53925740568377</v>
+        <f t="shared" si="17"/>
+        <v>529.61943750644411</v>
       </c>
       <c r="BR14" s="10">
-        <f t="shared" si="15"/>
-        <v>729.17386483162693</v>
+        <f t="shared" si="17"/>
+        <v>524.32324313137963</v>
       </c>
       <c r="BS14" s="10">
-        <f t="shared" si="15"/>
-        <v>721.88212618331067</v>
+        <f t="shared" si="17"/>
+        <v>519.08001070006583</v>
       </c>
       <c r="BT14" s="10">
-        <f t="shared" si="15"/>
-        <v>714.66330492147756</v>
+        <f t="shared" si="17"/>
+        <v>513.88921059306517</v>
       </c>
       <c r="BU14" s="10">
-        <f t="shared" si="15"/>
-        <v>707.5166718722628</v>
+        <f t="shared" si="17"/>
+        <v>508.75031848713451</v>
       </c>
       <c r="BV14" s="10">
-        <f t="shared" si="15"/>
-        <v>700.44150515354022</v>
+        <f t="shared" si="17"/>
+        <v>503.66281530226314</v>
       </c>
       <c r="BW14" s="10">
-        <f t="shared" si="15"/>
-        <v>693.43709010200484</v>
+        <f t="shared" si="17"/>
+        <v>498.62618714924048</v>
       </c>
       <c r="BX14" s="10">
-        <f t="shared" si="15"/>
-        <v>686.50271920098476</v>
+        <f t="shared" si="17"/>
+        <v>493.63992527774809</v>
       </c>
       <c r="BY14" s="10">
-        <f t="shared" si="15"/>
-        <v>679.63769200897491</v>
+        <f t="shared" si="17"/>
+        <v>488.70352602497059</v>
       </c>
       <c r="BZ14" s="10">
-        <f t="shared" si="15"/>
-        <v>672.84131508888515</v>
+        <f t="shared" si="17"/>
+        <v>483.81649076472087</v>
       </c>
       <c r="CA14" s="10">
-        <f t="shared" si="15"/>
-        <v>666.1129019379963</v>
+        <f t="shared" si="17"/>
+        <v>478.97832585707363</v>
       </c>
       <c r="CB14" s="10">
-        <f t="shared" si="15"/>
-        <v>659.45177291861637</v>
+        <f t="shared" si="17"/>
+        <v>474.18854259850286</v>
       </c>
       <c r="CC14" s="10">
-        <f t="shared" si="15"/>
-        <v>652.85725518943025</v>
+        <f t="shared" si="17"/>
+        <v>469.4466571725178</v>
       </c>
       <c r="CD14" s="10">
-        <f t="shared" si="15"/>
-        <v>646.32868263753596</v>
+        <f t="shared" si="17"/>
+        <v>464.75219060079263</v>
       </c>
       <c r="CE14" s="10">
-        <f t="shared" si="15"/>
-        <v>639.86539581116062</v>
+        <f t="shared" si="17"/>
+        <v>460.10466869478472</v>
       </c>
       <c r="CF14" s="10">
-        <f t="shared" si="15"/>
-        <v>633.46674185304903</v>
+        <f t="shared" si="17"/>
+        <v>455.5036220078369</v>
       </c>
       <c r="CG14" s="10">
-        <f t="shared" si="15"/>
-        <v>627.13207443451859</v>
+        <f t="shared" si="17"/>
+        <v>450.94858578775853</v>
       </c>
       <c r="CH14" s="10">
-        <f t="shared" si="15"/>
-        <v>620.8607536901734</v>
+        <f t="shared" si="17"/>
+        <v>446.43909992988097</v>
       </c>
       <c r="CI14" s="10">
-        <f t="shared" si="15"/>
-        <v>614.6521461532717</v>
+        <f t="shared" si="17"/>
+        <v>441.97470893058215</v>
       </c>
       <c r="CJ14" s="10">
-        <f t="shared" si="15"/>
-        <v>608.50562469173894</v>
+        <f t="shared" si="17"/>
+        <v>437.55496184127634</v>
       </c>
       <c r="CK14" s="10">
-        <f t="shared" si="15"/>
-        <v>602.42056844482158</v>
+        <f t="shared" si="17"/>
+        <v>433.17941222286356</v>
       </c>
       <c r="CL14" s="10">
-        <f t="shared" si="15"/>
-        <v>596.39636276037334</v>
+        <f t="shared" si="17"/>
+        <v>428.84761810063492</v>
       </c>
       <c r="CM14" s="10">
-        <f t="shared" si="15"/>
-        <v>590.43239913276955</v>
+        <f t="shared" si="17"/>
+        <v>424.55914191962859</v>
       </c>
       <c r="CN14" s="10">
-        <f t="shared" si="15"/>
-        <v>584.52807514144183</v>
+        <f t="shared" si="17"/>
+        <v>420.31355050043231</v>
       </c>
       <c r="CO14" s="10">
-        <f t="shared" si="15"/>
-        <v>578.68279439002742</v>
+        <f t="shared" si="17"/>
+        <v>416.11041499542796</v>
       </c>
       <c r="CP14" s="10">
-        <f t="shared" si="15"/>
-        <v>572.89596644612709</v>
+        <f t="shared" si="17"/>
+        <v>411.94931084547369</v>
       </c>
       <c r="CQ14" s="10">
-        <f t="shared" si="15"/>
-        <v>567.1670067816658</v>
+        <f t="shared" si="17"/>
+        <v>407.82981773701897</v>
       </c>
       <c r="CR14" s="10">
-        <f t="shared" si="15"/>
-        <v>561.49533671384916</v>
+        <f t="shared" si="17"/>
+        <v>403.75151955964878</v>
       </c>
       <c r="CS14" s="10">
-        <f t="shared" si="15"/>
-        <v>555.88038334671069</v>
+        <f t="shared" si="17"/>
+        <v>399.7140043640523</v>
       </c>
       <c r="CT14" s="10">
-        <f t="shared" si="15"/>
-        <v>550.32157951324359</v>
+        <f t="shared" si="17"/>
+        <v>395.71686432041179</v>
       </c>
       <c r="CU14" s="10">
-        <f t="shared" si="15"/>
-        <v>544.81836371811119</v>
+        <f t="shared" si="17"/>
+        <v>391.75969567720767</v>
       </c>
       <c r="CV14" s="10">
-        <f t="shared" si="15"/>
-        <v>539.37018008093003</v>
+        <f t="shared" si="17"/>
+        <v>387.84209872043562</v>
       </c>
       <c r="CW14" s="10">
-        <f t="shared" si="15"/>
-        <v>533.97647828012077</v>
+        <f t="shared" si="17"/>
+        <v>383.96367773323124</v>
       </c>
       <c r="CX14" s="10">
-        <f t="shared" si="15"/>
-        <v>528.63671349731953</v>
+        <f t="shared" si="17"/>
+        <v>380.12404095589892</v>
       </c>
       <c r="CY14" s="10">
-        <f t="shared" si="15"/>
-        <v>523.35034636234639</v>
+        <f t="shared" si="17"/>
+        <v>376.32280054633992</v>
       </c>
       <c r="CZ14" s="10">
-        <f t="shared" ref="CZ14:EK14" si="16">CY14*(1+$AO$18)</f>
-        <v>518.11684289872289</v>
+        <f t="shared" si="17"/>
+        <v>372.5595725408765</v>
       </c>
       <c r="DA14" s="10">
-        <f t="shared" si="16"/>
-        <v>512.93567446973566</v>
+        <f t="shared" si="17"/>
+        <v>368.83397681546774</v>
       </c>
       <c r="DB14" s="10">
-        <f t="shared" si="16"/>
-        <v>507.8063177250383</v>
+        <f t="shared" si="17"/>
+        <v>365.14563704731307</v>
       </c>
       <c r="DC14" s="10">
-        <f t="shared" si="16"/>
-        <v>502.72825454778791</v>
+        <f t="shared" si="17"/>
+        <v>361.49418067683996</v>
       </c>
       <c r="DD14" s="10">
-        <f t="shared" si="16"/>
-        <v>497.70097200231004</v>
+        <f t="shared" ref="DD14:EO14" si="18">DC14*(1+$AS$18)</f>
+        <v>357.87923887007156</v>
       </c>
       <c r="DE14" s="10">
-        <f t="shared" si="16"/>
-        <v>492.72396228228695</v>
+        <f t="shared" si="18"/>
+        <v>354.30044648137084</v>
       </c>
       <c r="DF14" s="10">
-        <f t="shared" si="16"/>
-        <v>487.79672265946408</v>
+        <f t="shared" si="18"/>
+        <v>350.75744201655715</v>
       </c>
       <c r="DG14" s="10">
-        <f t="shared" si="16"/>
-        <v>482.91875543286943</v>
+        <f t="shared" si="18"/>
+        <v>347.2498675963916</v>
       </c>
       <c r="DH14" s="10">
-        <f t="shared" si="16"/>
-        <v>478.08956787854072</v>
+        <f t="shared" si="18"/>
+        <v>343.7773689204277</v>
       </c>
       <c r="DI14" s="10">
-        <f t="shared" si="16"/>
-        <v>473.30867219975534</v>
+        <f t="shared" si="18"/>
+        <v>340.33959523122343</v>
       </c>
       <c r="DJ14" s="10">
-        <f t="shared" si="16"/>
-        <v>468.57558547775778</v>
+        <f t="shared" si="18"/>
+        <v>336.9361992789112</v>
       </c>
       <c r="DK14" s="10">
-        <f t="shared" si="16"/>
-        <v>463.88982962298019</v>
+        <f t="shared" si="18"/>
+        <v>333.56683728612211</v>
       </c>
       <c r="DL14" s="10">
-        <f t="shared" si="16"/>
-        <v>459.25093132675039</v>
+        <f t="shared" si="18"/>
+        <v>330.23116891326089</v>
       </c>
       <c r="DM14" s="10">
-        <f t="shared" si="16"/>
-        <v>454.65842201348289</v>
+        <f t="shared" si="18"/>
+        <v>326.92885722412825</v>
       </c>
       <c r="DN14" s="10">
-        <f t="shared" si="16"/>
-        <v>450.11183779334806</v>
+        <f t="shared" si="18"/>
+        <v>323.65956865188696</v>
       </c>
       <c r="DO14" s="10">
-        <f t="shared" si="16"/>
-        <v>445.61071941541456</v>
+        <f t="shared" si="18"/>
+        <v>320.4229729653681</v>
       </c>
       <c r="DP14" s="10">
-        <f t="shared" si="16"/>
-        <v>441.15461222126044</v>
+        <f t="shared" si="18"/>
+        <v>317.21874323571444</v>
       </c>
       <c r="DQ14" s="10">
-        <f t="shared" si="16"/>
-        <v>436.74306609904784</v>
+        <f t="shared" si="18"/>
+        <v>314.04655580335731</v>
       </c>
       <c r="DR14" s="10">
-        <f t="shared" si="16"/>
-        <v>432.37563543805737</v>
+        <f t="shared" si="18"/>
+        <v>310.90609024532375</v>
       </c>
       <c r="DS14" s="10">
-        <f t="shared" si="16"/>
-        <v>428.05187908367679</v>
+        <f t="shared" si="18"/>
+        <v>307.79702934287053</v>
       </c>
       <c r="DT14" s="10">
-        <f t="shared" si="16"/>
-        <v>423.77136029284003</v>
+        <f t="shared" si="18"/>
+        <v>304.7190590494418</v>
       </c>
       <c r="DU14" s="10">
-        <f t="shared" si="16"/>
-        <v>419.53364668991162</v>
+        <f t="shared" si="18"/>
+        <v>301.67186845894736</v>
       </c>
       <c r="DV14" s="10">
-        <f t="shared" si="16"/>
-        <v>415.33831022301251</v>
+        <f t="shared" si="18"/>
+        <v>298.65514977435788</v>
       </c>
       <c r="DW14" s="10">
-        <f t="shared" si="16"/>
-        <v>411.18492712078239</v>
+        <f t="shared" si="18"/>
+        <v>295.66859827661432</v>
       </c>
       <c r="DX14" s="10">
-        <f t="shared" si="16"/>
-        <v>407.07307784957459</v>
+        <f t="shared" si="18"/>
+        <v>292.71191229384817</v>
       </c>
       <c r="DY14" s="10">
-        <f t="shared" si="16"/>
-        <v>403.00234707107882</v>
+        <f t="shared" si="18"/>
+        <v>289.78479317090967</v>
       </c>
       <c r="DZ14" s="10">
-        <f t="shared" si="16"/>
-        <v>398.97232360036804</v>
+        <f t="shared" si="18"/>
+        <v>286.88694523920054</v>
       </c>
       <c r="EA14" s="10">
-        <f t="shared" si="16"/>
-        <v>394.98260036436437</v>
+        <f t="shared" si="18"/>
+        <v>284.01807578680854</v>
       </c>
       <c r="EB14" s="10">
-        <f t="shared" si="16"/>
-        <v>391.03277436072074</v>
+        <f t="shared" si="18"/>
+        <v>281.17789502894044</v>
       </c>
       <c r="EC14" s="10">
-        <f t="shared" si="16"/>
-        <v>387.12244661711355</v>
+        <f t="shared" si="18"/>
+        <v>278.36611607865103</v>
       </c>
       <c r="ED14" s="10">
-        <f t="shared" si="16"/>
-        <v>383.2512221509424</v>
+        <f t="shared" si="18"/>
+        <v>275.58245491786454</v>
       </c>
       <c r="EE14" s="10">
-        <f t="shared" si="16"/>
-        <v>379.41870992943296</v>
+        <f t="shared" si="18"/>
+        <v>272.82663036868587</v>
       </c>
       <c r="EF14" s="10">
-        <f t="shared" si="16"/>
-        <v>375.62452283013863</v>
+        <f t="shared" si="18"/>
+        <v>270.09836406499903</v>
       </c>
       <c r="EG14" s="10">
-        <f t="shared" si="16"/>
-        <v>371.86827760183724</v>
+        <f t="shared" si="18"/>
+        <v>267.39738042434902</v>
       </c>
       <c r="EH14" s="10">
-        <f t="shared" si="16"/>
-        <v>368.14959482581884</v>
+        <f t="shared" si="18"/>
+        <v>264.72340662010555</v>
       </c>
       <c r="EI14" s="10">
-        <f t="shared" si="16"/>
-        <v>364.46809887756064</v>
+        <f t="shared" si="18"/>
+        <v>262.07617255390448</v>
       </c>
       <c r="EJ14" s="10">
-        <f t="shared" si="16"/>
-        <v>360.823417888785</v>
+        <f t="shared" si="18"/>
+        <v>259.45541082836542</v>
       </c>
       <c r="EK14" s="10">
-        <f t="shared" si="16"/>
-        <v>357.21518370989713</v>
+        <f t="shared" si="18"/>
+        <v>256.86085672008176</v>
+      </c>
+      <c r="EL14" s="10">
+        <f t="shared" si="18"/>
+        <v>254.29224815288094</v>
+      </c>
+      <c r="EM14" s="10">
+        <f t="shared" si="18"/>
+        <v>251.74932567135212</v>
+      </c>
+      <c r="EN14" s="10">
+        <f t="shared" si="18"/>
+        <v>249.2318324146386</v>
+      </c>
+      <c r="EO14" s="10">
+        <f t="shared" si="18"/>
+        <v>246.73951409049221</v>
       </c>
     </row>
-    <row r="15" spans="1:141" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:145" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
         <v>93</v>
       </c>
@@ -3039,37 +3231,31 @@
       <c r="P15" s="25">
         <v>104.29419</v>
       </c>
-      <c r="Q15" s="28">
+      <c r="Q15" s="25">
         <v>104.29419</v>
       </c>
       <c r="R15" s="25">
-        <v>104.29419</v>
+        <v>103.80063699999999</v>
       </c>
       <c r="S15" s="25">
         <v>104.29419</v>
       </c>
-      <c r="U15" s="25">
+      <c r="T15" s="37">
+        <v>104.3</v>
+      </c>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="10"/>
+      <c r="Y15" s="25">
         <v>10.199999999999999</v>
       </c>
-      <c r="V15" s="25">
+      <c r="Z15" s="25">
         <v>10.199999999999999</v>
-      </c>
-      <c r="W15" s="25">
-        <v>103.80063699999999</v>
-      </c>
-      <c r="X15" s="25">
-        <v>103.80063699999999</v>
-      </c>
-      <c r="Y15" s="25">
-        <v>103.80063699999999</v>
-      </c>
-      <c r="Z15" s="25">
-        <v>103.80063699999999</v>
       </c>
       <c r="AA15" s="25">
         <v>103.80063699999999</v>
       </c>
-      <c r="AB15" s="28">
+      <c r="AB15" s="25">
         <v>103.80063699999999</v>
       </c>
       <c r="AC15" s="25">
@@ -3102,150 +3288,169 @@
       <c r="AL15" s="25">
         <v>103.80063699999999</v>
       </c>
+      <c r="AM15" s="25">
+        <v>103.80063699999999</v>
+      </c>
+      <c r="AN15" s="25">
+        <v>103.80063699999999</v>
+      </c>
+      <c r="AO15" s="25">
+        <v>103.80063699999999</v>
+      </c>
+      <c r="AP15" s="25">
+        <v>103.80063699999999</v>
+      </c>
     </row>
-    <row r="16" spans="1:141" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:145" x14ac:dyDescent="0.25">
       <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D16" s="15">
-        <f t="shared" ref="D16:O16" si="17">D14/D15</f>
+        <f t="shared" ref="D16:O16" si="19">D14/D15</f>
         <v>0.9200328895862171</v>
       </c>
       <c r="E16" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.6722405759417458</v>
       </c>
       <c r="F16" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.54674038272038727</v>
       </c>
       <c r="G16" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.9083181252538941</v>
       </c>
       <c r="H16" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1.0085583578836812</v>
       </c>
       <c r="I16" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.6684930074176707</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.60593077092580827</v>
       </c>
       <c r="K16" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.85083292889618845</v>
       </c>
       <c r="L16" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1.0130091976217821</v>
       </c>
       <c r="M16" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1.0017664920495626</v>
       </c>
       <c r="N16" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.75042892077820367</v>
       </c>
       <c r="O16" s="15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.93707517421111686</v>
       </c>
       <c r="P16" s="15">
-        <f t="shared" ref="P16:S16" si="18">P14/P15</f>
+        <f t="shared" ref="P16:T16" si="20">P14/P15</f>
         <v>1.1590578535582863</v>
       </c>
-      <c r="Q16" s="14">
-        <f t="shared" si="18"/>
+      <c r="Q16" s="15">
+        <f t="shared" si="20"/>
         <v>0.92225655139562457</v>
       </c>
       <c r="R16" s="15">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>0.67522707013830785</v>
       </c>
       <c r="S16" s="15">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15">
-        <f t="shared" ref="U16:AB16" si="19">U14/U15</f>
+        <f t="shared" si="20"/>
+        <v>0.69082467585202956</v>
+      </c>
+      <c r="T16" s="15">
+        <f t="shared" si="20"/>
+        <v>0.93392138063278995</v>
+      </c>
+      <c r="U16" s="15"/>
+      <c r="V16" s="15"/>
+      <c r="W16" s="34"/>
+      <c r="X16" s="15"/>
+      <c r="Y16" s="15">
+        <f t="shared" ref="Y16:AF16" si="21">Y14/Y15</f>
         <v>14.847156862745107</v>
       </c>
-      <c r="V16" s="15">
-        <f t="shared" si="19"/>
+      <c r="Z16" s="15">
+        <f t="shared" si="21"/>
         <v>17.742352941176449</v>
       </c>
-      <c r="W16" s="15">
-        <f t="shared" si="19"/>
+      <c r="AA16" s="15">
+        <f t="shared" si="21"/>
         <v>2.3249086612060008</v>
       </c>
-      <c r="X16" s="15">
-        <f t="shared" si="19"/>
+      <c r="AB16" s="15">
+        <f t="shared" si="21"/>
         <v>2.561997765004083</v>
       </c>
-      <c r="Y16" s="15">
-        <f t="shared" si="19"/>
+      <c r="AC16" s="15">
+        <f t="shared" si="21"/>
         <v>3.0346634577974703</v>
       </c>
-      <c r="Z16" s="15">
-        <f t="shared" si="19"/>
+      <c r="AD16" s="15">
+        <f t="shared" si="21"/>
         <v>3.140635832514207</v>
       </c>
-      <c r="AA16" s="15">
-        <f t="shared" si="19"/>
+      <c r="AE16" s="15">
+        <f t="shared" si="21"/>
         <v>3.6897654105918445</v>
       </c>
-      <c r="AB16" s="14">
-        <f t="shared" si="19"/>
-        <v>3.7868091310460836</v>
-      </c>
-      <c r="AC16" s="15">
-        <f t="shared" ref="AC16:AL16" si="20">AC14/AC15</f>
-        <v>4.2366048678487438</v>
-      </c>
-      <c r="AD16" s="15">
-        <f t="shared" si="20"/>
-        <v>4.7138520853200614</v>
-      </c>
-      <c r="AE16" s="15">
-        <f t="shared" si="20"/>
-        <v>5.2199185967047601</v>
-      </c>
       <c r="AF16" s="15">
-        <f t="shared" si="20"/>
-        <v>5.7562044419034724</v>
+        <f t="shared" si="21"/>
+        <v>3.4585529566644184</v>
       </c>
       <c r="AG16" s="15">
-        <f t="shared" si="20"/>
-        <v>6.3241372434470016</v>
+        <f t="shared" ref="AG16:AP16" si="22">AG14/AG15</f>
+        <v>3.2594482055057137</v>
       </c>
       <c r="AH16" s="15">
-        <f t="shared" si="20"/>
-        <v>6.9251665075644215</v>
+        <f t="shared" si="22"/>
+        <v>3.5946785760091271</v>
       </c>
       <c r="AI16" s="15">
-        <f t="shared" si="20"/>
-        <v>7.560756720556455</v>
+        <f t="shared" si="22"/>
+        <v>3.730074608694359</v>
       </c>
       <c r="AJ16" s="15">
-        <f t="shared" si="20"/>
-        <v>8.2323790723844006</v>
+        <f t="shared" si="22"/>
+        <v>4.0909279182901415</v>
       </c>
       <c r="AK16" s="15">
-        <f t="shared" si="20"/>
-        <v>8.9415016190039953</v>
+        <f t="shared" si="22"/>
+        <v>4.4708909997132738</v>
       </c>
       <c r="AL16" s="15">
-        <f t="shared" si="20"/>
-        <v>9.6895776722870899</v>
+        <f t="shared" si="22"/>
+        <v>4.8709314578994221</v>
+      </c>
+      <c r="AM16" s="15">
+        <f t="shared" si="22"/>
+        <v>5.2920633881226173</v>
+      </c>
+      <c r="AN16" s="15">
+        <f t="shared" si="22"/>
+        <v>5.7353494011042381</v>
+      </c>
+      <c r="AO16" s="15">
+        <f t="shared" si="22"/>
+        <v>6.2019027152927739</v>
+      </c>
+      <c r="AP16" s="15">
+        <f t="shared" si="22"/>
+        <v>6.6928893161042868</v>
       </c>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:45" x14ac:dyDescent="0.25">
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
@@ -3257,14 +3462,15 @@
       <c r="L17" s="12"/>
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
-      <c r="AN17" s="1" t="s">
+      <c r="T17" s="38"/>
+      <c r="AR17" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AO17" s="22">
+      <c r="AS17" s="22">
         <v>0.08</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C18" s="4" t="s">
         <v>47</v>
       </c>
@@ -3273,11 +3479,11 @@
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
       <c r="H18" s="17">
-        <f t="shared" ref="H18:L18" si="21">(H4-D4)/D4</f>
+        <f t="shared" ref="H18:L18" si="23">(H4-D4)/D4</f>
         <v>0.15749018993077837</v>
       </c>
       <c r="I18" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.13354959770200958</v>
       </c>
       <c r="J18" s="17">
@@ -3285,11 +3491,11 @@
         <v>0.11229625393194177</v>
       </c>
       <c r="K18" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.13853628638824544</v>
       </c>
       <c r="L18" s="17">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>7.470003174267266E-2</v>
       </c>
       <c r="M18" s="17">
@@ -3308,96 +3514,102 @@
         <f>(P4-L4)/L4</f>
         <v>5.8089059849423988E-2</v>
       </c>
-      <c r="Q18" s="16">
-        <f t="shared" ref="Q18:S18" si="22">(Q4-M4)/M4</f>
+      <c r="Q18" s="17">
+        <f t="shared" ref="Q18:S18" si="24">(Q4-M4)/M4</f>
         <v>-3.2475315164868519E-2</v>
       </c>
       <c r="R18" s="17">
-        <f t="shared" si="22"/>
-        <v>-1</v>
+        <f t="shared" si="24"/>
+        <v>-9.1608405936333993E-3</v>
       </c>
       <c r="S18" s="17">
-        <f t="shared" si="22"/>
-        <v>-1</v>
-      </c>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="17">
-        <f t="shared" ref="V18:Y18" si="23">(V4-U4)/U4</f>
+        <f t="shared" si="24"/>
+        <v>-2.6824737123229418E-2</v>
+      </c>
+      <c r="T18" s="39">
+        <v>-2.6800000000000001E-2</v>
+      </c>
+      <c r="U18" s="17"/>
+      <c r="V18" s="17"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="17">
+        <f t="shared" ref="Z18:AC18" si="25">(Z4-Y4)/Y4</f>
         <v>0.15448491940536443</v>
       </c>
-      <c r="W18" s="17">
-        <f t="shared" si="23"/>
+      <c r="AA18" s="17">
+        <f t="shared" si="25"/>
         <v>0.12656848030018764</v>
       </c>
-      <c r="X18" s="17">
-        <f t="shared" si="23"/>
+      <c r="AB18" s="17">
+        <f t="shared" si="25"/>
         <v>0.12205455475043339</v>
       </c>
-      <c r="Y18" s="17">
-        <f t="shared" si="23"/>
+      <c r="AC18" s="17">
+        <f t="shared" si="25"/>
         <v>0.15102040816326531</v>
-      </c>
-      <c r="Z18" s="17">
-        <f>(Z4-Y4)/Y4</f>
-        <v>0.13668600902643455</v>
-      </c>
-      <c r="AA18" s="17">
-        <f>(AA4-Z4)/Z4</f>
-        <v>0.11202495745887692</v>
-      </c>
-      <c r="AB18" s="16">
-        <f t="shared" ref="AB18:AL18" si="24">(AB4-AA4)/AA4</f>
-        <v>6.0000000000000053E-2</v>
-      </c>
-      <c r="AC18" s="17">
-        <f t="shared" si="24"/>
-        <v>7.5000000000000039E-2</v>
       </c>
       <c r="AD18" s="17">
         <f>(AD4-AC4)/AC4</f>
-        <v>7.5000000000000011E-2</v>
+        <v>0.13668600902643455</v>
       </c>
       <c r="AE18" s="17">
-        <f t="shared" si="24"/>
-        <v>7.4999999999999872E-2</v>
+        <f>(AE4-AD4)/AD4</f>
+        <v>0.11202495745887692</v>
       </c>
       <c r="AF18" s="17">
-        <f t="shared" si="24"/>
-        <v>7.5000000000000039E-2</v>
+        <f t="shared" ref="AF18:AP18" si="26">(AF4-AE4)/AE4</f>
+        <v>-2.2953328232593728E-3</v>
       </c>
       <c r="AG18" s="17">
-        <f t="shared" si="24"/>
-        <v>7.4999999999999969E-2</v>
+        <f t="shared" si="26"/>
+        <v>9.9999999999999725E-3</v>
       </c>
       <c r="AH18" s="17">
-        <f t="shared" si="24"/>
-        <v>7.4999999999999969E-2</v>
+        <f>(AH4-AG4)/AG4</f>
+        <v>5.0000000000000128E-2</v>
       </c>
       <c r="AI18" s="17">
-        <f t="shared" si="24"/>
-        <v>7.49999999999999E-2</v>
+        <f t="shared" si="26"/>
+        <v>4.9999999999999947E-2</v>
       </c>
       <c r="AJ18" s="17">
-        <f t="shared" si="24"/>
-        <v>7.5000000000000011E-2</v>
+        <f t="shared" si="26"/>
+        <v>5.0000000000000148E-2</v>
       </c>
       <c r="AK18" s="17">
-        <f t="shared" si="24"/>
-        <v>7.49999999999999E-2</v>
+        <f t="shared" si="26"/>
+        <v>5.0000000000000037E-2</v>
       </c>
       <c r="AL18" s="17">
-        <f t="shared" si="24"/>
-        <v>7.4999999999999886E-2</v>
-      </c>
-      <c r="AN18" s="1" t="s">
+        <f t="shared" si="26"/>
+        <v>5.0000000000000114E-2</v>
+      </c>
+      <c r="AM18" s="17">
+        <f t="shared" si="26"/>
+        <v>4.9999999999999961E-2</v>
+      </c>
+      <c r="AN18" s="17">
+        <f t="shared" si="26"/>
+        <v>5.0000000000000086E-2</v>
+      </c>
+      <c r="AO18" s="17">
+        <f t="shared" si="26"/>
+        <v>5.0000000000000072E-2</v>
+      </c>
+      <c r="AP18" s="17">
+        <f t="shared" si="26"/>
+        <v>5.0000000000000051E-2</v>
+      </c>
+      <c r="AR18" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AO18" s="22">
+      <c r="AS18" s="22">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C19" s="1" t="s">
         <v>100</v>
       </c>
@@ -3406,147 +3618,153 @@
         <v>0.1503720722883303</v>
       </c>
       <c r="E19" s="19">
-        <f t="shared" ref="E19:N19" si="25">E10/E4</f>
+        <f t="shared" ref="E19:N19" si="27">E10/E4</f>
         <v>0.12138200551637437</v>
       </c>
       <c r="F19" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.10494137832427794</v>
       </c>
       <c r="G19" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.13656724391587011</v>
       </c>
       <c r="H19" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.13928261559623328</v>
       </c>
       <c r="I19" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.10686886365627946</v>
       </c>
       <c r="J19" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.10285111962362131</v>
       </c>
       <c r="K19" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.10964222953741065</v>
       </c>
       <c r="L19" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.1328789336210825</v>
       </c>
       <c r="M19" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.13538456006759741</v>
       </c>
       <c r="N19" s="19">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.11490890381800348</v>
       </c>
       <c r="O19" s="19">
-        <f t="shared" ref="O19:P19" si="26">O10/O4</f>
+        <f t="shared" ref="O19:P19" si="28">O10/O4</f>
         <v>0.11672332926558246</v>
       </c>
       <c r="P19" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0.14441890760212162</v>
       </c>
-      <c r="Q19" s="20">
-        <f t="shared" ref="Q19:S19" si="27">Q10/Q4</f>
+      <c r="Q19" s="19">
+        <f t="shared" ref="Q19:S19" si="29">Q10/Q4</f>
         <v>0.12743688235968156</v>
       </c>
-      <c r="R19" s="19" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S19" s="19" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T19" s="15"/>
-      <c r="U19" s="19">
-        <f t="shared" ref="U19:Y19" si="28">U10/U4</f>
+      <c r="R19" s="19">
+        <f t="shared" si="29"/>
+        <v>0.10522428010486243</v>
+      </c>
+      <c r="S19" s="19">
+        <f t="shared" si="29"/>
+        <v>0.10372032230440638</v>
+      </c>
+      <c r="T19" s="40">
+        <v>0.1037</v>
+      </c>
+      <c r="U19" s="19"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="19"/>
+      <c r="X19" s="15"/>
+      <c r="Y19" s="19">
+        <f t="shared" ref="Y19:AC19" si="30">Y10/Y4</f>
         <v>0.10420742606720818</v>
       </c>
-      <c r="V19" s="19">
-        <f t="shared" si="28"/>
+      <c r="Z19" s="19">
+        <f t="shared" si="30"/>
         <v>0.10918011257035636</v>
       </c>
-      <c r="W19" s="19">
-        <f t="shared" si="28"/>
+      <c r="AA19" s="19">
+        <f t="shared" si="30"/>
         <v>0.13099393632558987</v>
       </c>
-      <c r="X19" s="19">
-        <f t="shared" si="28"/>
+      <c r="AB19" s="19">
+        <f t="shared" si="30"/>
         <v>0.12623116883116886</v>
       </c>
-      <c r="Y19" s="19">
-        <f t="shared" si="28"/>
+      <c r="AC19" s="19">
+        <f t="shared" si="30"/>
         <v>0.12927143778207609</v>
       </c>
-      <c r="Z19" s="19">
-        <f>Z10/Z4</f>
+      <c r="AD19" s="19">
+        <f>AD10/AD4</f>
         <v>0.11571185479296653</v>
       </c>
-      <c r="AA19" s="19">
-        <f t="shared" ref="AA19:AL19" si="29">AA10/AA4</f>
+      <c r="AE19" s="19">
+        <f t="shared" ref="AE19:AP19" si="31">AE10/AE4</f>
         <v>0.12496812037745474</v>
       </c>
-      <c r="AB19" s="20">
-        <f>AB10/AB4</f>
-        <v>0.1212484300789652</v>
-      </c>
-      <c r="AC19" s="19">
-        <f t="shared" si="29"/>
-        <v>0.12618629964618244</v>
-      </c>
-      <c r="AD19" s="19">
-        <f t="shared" si="29"/>
-        <v>0.13060557956745864</v>
-      </c>
-      <c r="AE19" s="19">
-        <f t="shared" si="29"/>
-        <v>0.1345367852474125</v>
-      </c>
       <c r="AF19" s="19">
-        <f t="shared" si="29"/>
-        <v>0.13800825407497463</v>
+        <f>AF10/AF4</f>
+        <v>0.12116564417177914</v>
       </c>
       <c r="AG19" s="19">
-        <f t="shared" si="29"/>
-        <v>0.14104629200563976</v>
+        <f t="shared" si="31"/>
+        <v>0.10978153030026928</v>
       </c>
       <c r="AH19" s="19">
-        <f t="shared" si="29"/>
-        <v>0.14367531000863507</v>
+        <f t="shared" si="31"/>
+        <v>0.11530707628168609</v>
       </c>
       <c r="AI19" s="19">
-        <f t="shared" si="29"/>
-        <v>0.14591795107715322</v>
+        <f t="shared" si="31"/>
+        <v>0.11395256795409524</v>
       </c>
       <c r="AJ19" s="19">
-        <f t="shared" si="29"/>
-        <v>0.14779520845145289</v>
+        <f t="shared" si="31"/>
+        <v>0.11902525654776627</v>
       </c>
       <c r="AK19" s="19">
-        <f t="shared" si="29"/>
-        <v>0.14932653565962978</v>
+        <f t="shared" si="31"/>
+        <v>0.12388595747813344</v>
       </c>
       <c r="AL19" s="19">
-        <f t="shared" si="29"/>
-        <v>0.15052994893898694</v>
-      </c>
-      <c r="AN19" s="23" t="s">
+        <f t="shared" si="31"/>
+        <v>0.12854367710105852</v>
+      </c>
+      <c r="AM19" s="19">
+        <f t="shared" si="31"/>
+        <v>0.13300698199607039</v>
+      </c>
+      <c r="AN19" s="19">
+        <f t="shared" si="31"/>
+        <v>0.13728401850931068</v>
+      </c>
+      <c r="AO19" s="19">
+        <f t="shared" si="31"/>
+        <v>0.14138253132162668</v>
+      </c>
+      <c r="AP19" s="19">
+        <f t="shared" si="31"/>
+        <v>0.14530988108551698</v>
+      </c>
+      <c r="AR19" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="AO19" s="24">
-        <f>NPV(AO17,AB14:EK14)</f>
-        <v>9224.5685250083989</v>
+      <c r="AS19" s="24">
+        <f>NPV(AS17,AF14:EO14)</f>
+        <v>6547.5720215258207</v>
       </c>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
         <v>91</v>
       </c>
@@ -3555,11 +3773,11 @@
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
       <c r="H20" s="19">
-        <f t="shared" ref="H20" si="30">(H6-D6)/D6</f>
+        <f t="shared" ref="H20" si="32">(H6-D6)/D6</f>
         <v>0.15764434753450854</v>
       </c>
       <c r="I20" s="19">
-        <f t="shared" ref="I20" si="31">(I6-E6)/E6</f>
+        <f t="shared" ref="I20" si="33">(I6-E6)/E6</f>
         <v>0.14227845683331503</v>
       </c>
       <c r="J20" s="19">
@@ -3567,15 +3785,15 @@
         <v>0.16435289445249363</v>
       </c>
       <c r="K20" s="19">
-        <f t="shared" ref="K20" si="32">(K6-G6)/G6</f>
+        <f t="shared" ref="K20" si="34">(K6-G6)/G6</f>
         <v>0.20458342975530372</v>
       </c>
       <c r="L20" s="19">
-        <f t="shared" ref="L20" si="33">(L6-H6)/H6</f>
+        <f t="shared" ref="L20" si="35">(L6-H6)/H6</f>
         <v>0.11459370189122506</v>
       </c>
       <c r="M20" s="19">
-        <f t="shared" ref="M20" si="34">(M6-I6)/I6</f>
+        <f t="shared" ref="M20" si="36">(M6-I6)/I6</f>
         <v>0.23642801444673264</v>
       </c>
       <c r="N20" s="19">
@@ -3590,96 +3808,102 @@
         <f>(P6-L6)/L6</f>
         <v>6.3361636999026513E-2</v>
       </c>
-      <c r="Q20" s="20">
-        <f t="shared" ref="Q20:S20" si="35">(Q6-M6)/M6</f>
+      <c r="Q20" s="19">
+        <f t="shared" ref="Q20:S20" si="37">(Q6-M6)/M6</f>
         <v>-1.5041926872008331E-2</v>
       </c>
       <c r="R20" s="19">
-        <f t="shared" si="35"/>
-        <v>-1</v>
+        <f t="shared" si="37"/>
+        <v>4.7598720786530387E-2</v>
       </c>
       <c r="S20" s="19">
-        <f t="shared" si="35"/>
-        <v>-1</v>
-      </c>
-      <c r="T20" s="15"/>
-      <c r="V20" s="19">
-        <f t="shared" ref="V20:Y20" si="36">(V6-U6)/U6</f>
+        <f t="shared" si="37"/>
+        <v>-2.4039573483299599E-3</v>
+      </c>
+      <c r="T20" s="40">
+        <v>-2.3999999999999998E-3</v>
+      </c>
+      <c r="U20" s="19"/>
+      <c r="V20" s="19"/>
+      <c r="W20" s="19"/>
+      <c r="X20" s="15"/>
+      <c r="Z20" s="19">
+        <f t="shared" ref="Z20:AC20" si="38">(Z6-Y6)/Y6</f>
         <v>0.16876624301931861</v>
       </c>
-      <c r="W20" s="19">
-        <f t="shared" si="36"/>
+      <c r="AA20" s="19">
+        <f t="shared" si="38"/>
         <v>0.1463999105910424</v>
       </c>
-      <c r="X20" s="19">
-        <f t="shared" si="36"/>
+      <c r="AB20" s="19">
+        <f t="shared" si="38"/>
         <v>0.13314949723612818</v>
       </c>
-      <c r="Y20" s="19">
-        <f t="shared" si="36"/>
+      <c r="AC20" s="19">
+        <f t="shared" si="38"/>
         <v>0.12905027932960894</v>
       </c>
-      <c r="Z20" s="19">
-        <f>(Z6-Y6)/Y6</f>
+      <c r="AD20" s="19">
+        <f>(AD6-AC6)/AC6</f>
         <v>0.1682335477486393</v>
       </c>
-      <c r="AA20" s="19">
-        <f>(AA6-Z6)/Z6</f>
+      <c r="AE20" s="19">
+        <f>(AE6-AD6)/AD6</f>
         <v>0.13130029648454045</v>
       </c>
-      <c r="AB20" s="20">
-        <f>(AB6-AA6)/AA6</f>
-        <v>6.0000000000000081E-2</v>
-      </c>
-      <c r="AC20" s="19">
-        <f t="shared" ref="AC20:AL20" si="37">(AC6-AB6)/AB6</f>
-        <v>7.4999999999999886E-2</v>
-      </c>
-      <c r="AD20" s="19">
-        <f t="shared" si="37"/>
-        <v>7.4999999999999886E-2</v>
-      </c>
-      <c r="AE20" s="19">
-        <f t="shared" si="37"/>
-        <v>7.4999999999999997E-2</v>
-      </c>
       <c r="AF20" s="19">
-        <f t="shared" si="37"/>
-        <v>7.4999999999999956E-2</v>
+        <f>(AF6-AE6)/AE6</f>
+        <v>2.2463496817671284E-2</v>
       </c>
       <c r="AG20" s="19">
-        <f t="shared" si="37"/>
-        <v>7.49999999999999E-2</v>
+        <f t="shared" ref="AG20:AP20" si="39">(AG6-AF6)/AF6</f>
+        <v>9.9999999999999794E-3</v>
       </c>
       <c r="AH20" s="19">
-        <f t="shared" si="37"/>
-        <v>7.4999999999999886E-2</v>
+        <f t="shared" si="39"/>
+        <v>5.0000000000000024E-2</v>
       </c>
       <c r="AI20" s="19">
-        <f t="shared" si="37"/>
-        <v>7.5000000000000011E-2</v>
+        <f t="shared" si="39"/>
+        <v>5.9999999999999977E-2</v>
       </c>
       <c r="AJ20" s="19">
-        <f t="shared" si="37"/>
-        <v>7.5000000000000025E-2</v>
+        <f t="shared" si="39"/>
+        <v>4.9999999999999982E-2</v>
       </c>
       <c r="AK20" s="19">
-        <f t="shared" si="37"/>
-        <v>7.4999999999999928E-2</v>
+        <f t="shared" si="39"/>
+        <v>5.00000000000001E-2</v>
       </c>
       <c r="AL20" s="19">
-        <f t="shared" si="37"/>
-        <v>7.5000000000000025E-2</v>
-      </c>
-      <c r="AN20" s="1" t="s">
+        <f t="shared" si="39"/>
+        <v>4.9999999999999996E-2</v>
+      </c>
+      <c r="AM20" s="19">
+        <f t="shared" si="39"/>
+        <v>5.0000000000000051E-2</v>
+      </c>
+      <c r="AN20" s="19">
+        <f t="shared" si="39"/>
+        <v>5.0000000000000058E-2</v>
+      </c>
+      <c r="AO20" s="19">
+        <f t="shared" si="39"/>
+        <v>5.0000000000000107E-2</v>
+      </c>
+      <c r="AP20" s="19">
+        <f t="shared" si="39"/>
+        <v>5.0000000000000135E-2</v>
+      </c>
+      <c r="AR20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AO20" s="25">
+      <c r="AS20" s="25">
         <f>B5</f>
-        <v>103.80063699999999</v>
+        <v>102.482005</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="s">
         <v>129</v>
       </c>
@@ -3696,26 +3920,26 @@
       <c r="N21" s="19"/>
       <c r="O21" s="19"/>
       <c r="P21" s="19"/>
-      <c r="Q21" s="14"/>
+      <c r="Q21" s="15"/>
       <c r="R21" s="15"/>
       <c r="S21" s="15"/>
       <c r="T21" s="15"/>
-      <c r="Y21" s="19">
-        <f>Y14/G48</f>
+      <c r="U21" s="15"/>
+      <c r="V21" s="15"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="15"/>
+      <c r="AC21" s="19">
+        <f>AC14/G48</f>
         <v>0.68932465878429394</v>
       </c>
-      <c r="Z21" s="19">
-        <f>Z14/K48</f>
+      <c r="AD21" s="19">
+        <f>AD14/K48</f>
         <v>0.71132445996072435</v>
       </c>
-      <c r="AA21" s="19">
-        <f>AA14/O48</f>
+      <c r="AE21" s="19">
+        <f>AE14/O48</f>
         <v>0.82393232998597377</v>
       </c>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="19"/>
-      <c r="AD21" s="19"/>
-      <c r="AE21" s="19"/>
       <c r="AF21" s="19"/>
       <c r="AG21" s="19"/>
       <c r="AH21" s="19"/>
@@ -3723,15 +3947,19 @@
       <c r="AJ21" s="19"/>
       <c r="AK21" s="19"/>
       <c r="AL21" s="19"/>
-      <c r="AN21" s="4" t="s">
+      <c r="AM21" s="19"/>
+      <c r="AN21" s="19"/>
+      <c r="AO21" s="19"/>
+      <c r="AP21" s="19"/>
+      <c r="AR21" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="AO21" s="26">
-        <f>AO19/AO20</f>
-        <v>88.86813021203713</v>
+      <c r="AS21" s="26">
+        <f>AS19/AS20</f>
+        <v>63.88996801463653</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:45" x14ac:dyDescent="0.25">
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
@@ -3743,15 +3971,15 @@
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
-      <c r="AN22" s="4" t="s">
+      <c r="AR22" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="AO22" s="27">
-        <f>(AO21-B4)/B4</f>
-        <v>0.34853004874107923</v>
+      <c r="AS22" s="27">
+        <f>(AS21-B4)/B4</f>
+        <v>0.41977706699192291</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C23" s="1" t="s">
         <v>33</v>
       </c>
@@ -3798,13 +4026,23 @@
       <c r="P23" s="12">
         <v>2347</v>
       </c>
-      <c r="Q23" s="13">
+      <c r="Q23" s="12">
         <v>2337</v>
       </c>
-      <c r="R23" s="12"/>
-      <c r="S23" s="12"/>
+      <c r="R23" s="12">
+        <v>2354</v>
+      </c>
+      <c r="S23" s="12">
+        <v>2367</v>
+      </c>
+      <c r="T23" s="12">
+        <v>2391</v>
+      </c>
+      <c r="U23" s="12"/>
+      <c r="V23" s="12"/>
+      <c r="W23" s="12"/>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C24" s="1" t="s">
         <v>83</v>
       </c>
@@ -3813,27 +4051,27 @@
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
       <c r="H24" s="19">
-        <f t="shared" ref="H24:M24" si="38">(H23-D23)/D23</f>
+        <f t="shared" ref="H24:M24" si="40">(H23-D23)/D23</f>
         <v>0.12346993081426291</v>
       </c>
       <c r="I24" s="19">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.12918410041841005</v>
       </c>
       <c r="J24" s="19">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.12773359840954274</v>
       </c>
       <c r="K24" s="19">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.13228809407153355</v>
       </c>
       <c r="L24" s="19">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>9.7110374230222646E-2</v>
       </c>
       <c r="M24" s="19">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>7.9666512274201018E-2</v>
       </c>
       <c r="N24" s="19">
@@ -3848,20 +4086,27 @@
         <f>(P23-L23)/L23</f>
         <v>1.3385146804835924E-2</v>
       </c>
-      <c r="Q24" s="20">
-        <f t="shared" ref="Q24:S24" si="39">(Q23-M23)/M23</f>
+      <c r="Q24" s="19">
+        <f t="shared" ref="Q24:T24" si="41">(Q23-M23)/M23</f>
         <v>2.5740025740025739E-3</v>
       </c>
       <c r="R24" s="19">
-        <f t="shared" si="39"/>
-        <v>-1</v>
+        <f t="shared" si="41"/>
+        <v>-1.4650481372959398E-2</v>
       </c>
       <c r="S24" s="19">
-        <f t="shared" si="39"/>
-        <v>-1</v>
-      </c>
+        <f t="shared" si="41"/>
+        <v>2.9661016949152543E-3</v>
+      </c>
+      <c r="T24" s="19">
+        <f t="shared" si="41"/>
+        <v>1.8747337025990626E-2</v>
+      </c>
+      <c r="U24" s="19"/>
+      <c r="V24" s="19"/>
+      <c r="W24" s="19"/>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:45" x14ac:dyDescent="0.25">
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -3874,7 +4119,7 @@
       <c r="M25" s="12"/>
       <c r="N25" s="12"/>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C26" s="4" t="s">
         <v>99</v>
       </c>
@@ -3890,7 +4135,7 @@
       <c r="M26" s="12"/>
       <c r="N26" s="12"/>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C27" s="1" t="s">
         <v>48</v>
       </c>
@@ -3933,14 +4178,24 @@
       <c r="P27" s="12">
         <v>15.577</v>
       </c>
-      <c r="Q27" s="13">
+      <c r="Q27" s="12">
         <v>17.122</v>
       </c>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="12"/>
+      <c r="R27" s="12">
+        <v>18.524999999999999</v>
+      </c>
+      <c r="S27" s="12">
+        <v>7.91</v>
+      </c>
+      <c r="T27" s="12">
+        <v>9.3740000000000006</v>
+      </c>
+      <c r="U27" s="12"/>
+      <c r="V27" s="12"/>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C28" s="1" t="s">
         <v>49</v>
       </c>
@@ -3983,14 +4238,24 @@
       <c r="P28" s="12">
         <v>54.204999999999998</v>
       </c>
-      <c r="Q28" s="13">
+      <c r="Q28" s="12">
         <v>54.287999999999997</v>
       </c>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="12"/>
+      <c r="R28" s="12">
+        <v>54.277999999999999</v>
+      </c>
+      <c r="S28" s="12">
+        <v>54.567999999999998</v>
+      </c>
+      <c r="T28" s="12">
+        <v>53.97</v>
+      </c>
+      <c r="U28" s="12"/>
+      <c r="V28" s="12"/>
+      <c r="W28" s="12"/>
+      <c r="X28" s="12"/>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C29" s="1" t="s">
         <v>50</v>
       </c>
@@ -4033,14 +4298,24 @@
       <c r="P29" s="12">
         <v>23.884</v>
       </c>
-      <c r="Q29" s="13">
+      <c r="Q29" s="12">
         <v>21.690999999999999</v>
       </c>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="12"/>
+      <c r="R29" s="12">
+        <v>19.495000000000001</v>
+      </c>
+      <c r="S29" s="12">
+        <v>17.367999999999999</v>
+      </c>
+      <c r="T29" s="12">
+        <v>16.071999999999999</v>
+      </c>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C30" s="1" t="s">
         <v>51</v>
       </c>
@@ -4083,14 +4358,24 @@
       <c r="P30" s="12">
         <v>38.659999999999997</v>
       </c>
-      <c r="Q30" s="13">
+      <c r="Q30" s="12">
         <v>44.8</v>
       </c>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
+      <c r="R30" s="12">
+        <v>45.731999999999999</v>
+      </c>
+      <c r="S30" s="12">
+        <v>43.953000000000003</v>
+      </c>
+      <c r="T30" s="12">
+        <v>42.555999999999997</v>
+      </c>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C31" s="1" t="s">
         <v>52</v>
       </c>
@@ -4133,14 +4418,24 @@
       <c r="P31" s="12">
         <v>5.1529999999999996</v>
       </c>
-      <c r="Q31" s="13">
+      <c r="Q31" s="12">
         <v>5</v>
       </c>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="12"/>
+      <c r="R31" s="12">
+        <v>6.3330000000000002</v>
+      </c>
+      <c r="S31" s="12">
+        <v>6.2889999999999997</v>
+      </c>
+      <c r="T31" s="12">
+        <v>6.0990000000000002</v>
+      </c>
+      <c r="U31" s="12"/>
+      <c r="V31" s="12"/>
+      <c r="W31" s="12"/>
+      <c r="X31" s="12"/>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C32" s="1" t="s">
         <v>53</v>
       </c>
@@ -4183,14 +4478,24 @@
       <c r="P32" s="12">
         <v>22</v>
       </c>
-      <c r="Q32" s="13">
+      <c r="Q32" s="12">
         <v>22.2</v>
       </c>
-      <c r="R32" s="12"/>
-      <c r="S32" s="12"/>
-      <c r="T32" s="12"/>
+      <c r="R32" s="12">
+        <v>21.503</v>
+      </c>
+      <c r="S32" s="12">
+        <v>21.387</v>
+      </c>
+      <c r="T32" s="12">
+        <v>21.050999999999998</v>
+      </c>
+      <c r="U32" s="12"/>
+      <c r="V32" s="12"/>
+      <c r="W32" s="12"/>
+      <c r="X32" s="12"/>
     </row>
-    <row r="33" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C33" s="1" t="s">
         <v>54</v>
       </c>
@@ -4233,14 +4538,24 @@
       <c r="P33" s="12">
         <v>293.54199999999997</v>
       </c>
-      <c r="Q33" s="13">
+      <c r="Q33" s="12">
         <v>338.23599999999999</v>
       </c>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
-      <c r="T33" s="12"/>
+      <c r="R33" s="12">
+        <v>321.37799999999999</v>
+      </c>
+      <c r="S33" s="12">
+        <v>314.846</v>
+      </c>
+      <c r="T33" s="12">
+        <v>311.09399999999999</v>
+      </c>
+      <c r="U33" s="12"/>
+      <c r="V33" s="12"/>
+      <c r="W33" s="12"/>
+      <c r="X33" s="12"/>
     </row>
-    <row r="34" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C34" s="1" t="s">
         <v>55</v>
       </c>
@@ -4283,14 +4598,24 @@
       <c r="P34" s="12">
         <v>0</v>
       </c>
-      <c r="Q34" s="13">
+      <c r="Q34" s="12">
         <v>0</v>
       </c>
-      <c r="R34" s="12"/>
-      <c r="S34" s="12"/>
-      <c r="T34" s="12"/>
+      <c r="R34" s="12">
+        <v>0</v>
+      </c>
+      <c r="S34" s="12">
+        <v>0</v>
+      </c>
+      <c r="T34" s="12">
+        <v>0</v>
+      </c>
+      <c r="U34" s="12"/>
+      <c r="V34" s="12"/>
+      <c r="W34" s="12"/>
+      <c r="X34" s="12"/>
     </row>
-    <row r="35" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C35" s="1" t="s">
         <v>56</v>
       </c>
@@ -4333,55 +4658,65 @@
       <c r="P35" s="12">
         <v>2</v>
       </c>
-      <c r="Q35" s="13">
+      <c r="Q35" s="12">
         <v>2</v>
       </c>
-      <c r="R35" s="12"/>
-      <c r="S35" s="12"/>
-      <c r="T35" s="12"/>
+      <c r="R35" s="12">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="S35" s="12">
+        <v>1</v>
+      </c>
+      <c r="T35" s="12">
+        <v>1.147</v>
+      </c>
+      <c r="U35" s="12"/>
+      <c r="V35" s="12"/>
+      <c r="W35" s="12"/>
+      <c r="X35" s="12"/>
     </row>
-    <row r="36" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C36" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D36" s="31">
-        <f t="shared" ref="D36" si="40">SUM(D27:D35)</f>
+        <f t="shared" ref="D36" si="42">SUM(D27:D35)</f>
         <v>376.58799999999997</v>
       </c>
       <c r="E36" s="31">
-        <f t="shared" ref="E36" si="41">SUM(E27:E35)</f>
+        <f t="shared" ref="E36" si="43">SUM(E27:E35)</f>
         <v>375.89</v>
       </c>
       <c r="F36" s="31">
-        <f t="shared" ref="F36" si="42">SUM(F27:F35)</f>
+        <f t="shared" ref="F36" si="44">SUM(F27:F35)</f>
         <v>373.79099999999994</v>
       </c>
       <c r="G36" s="31">
-        <f t="shared" ref="G36:M36" si="43">SUM(G27:G35)</f>
+        <f t="shared" ref="G36:M36" si="45">SUM(G27:G35)</f>
         <v>361.03599999999994</v>
       </c>
       <c r="H36" s="31">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>369.89400000000001</v>
       </c>
       <c r="I36" s="31">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>365.83599999999996</v>
       </c>
       <c r="J36" s="31">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>352.85699999999997</v>
       </c>
       <c r="K36" s="31">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>492.44400000000002</v>
       </c>
       <c r="L36" s="31">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>513.37400000000002</v>
       </c>
       <c r="M36" s="31">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>508.36699999999996</v>
       </c>
       <c r="N36" s="31">
@@ -4396,21 +4731,28 @@
         <f>SUM(P27:P35)</f>
         <v>455.02099999999996</v>
       </c>
-      <c r="Q36" s="34">
-        <f t="shared" ref="Q36:S36" si="44">SUM(Q27:Q35)</f>
+      <c r="Q36" s="31">
+        <f t="shared" ref="Q36:S36" si="46">SUM(Q27:Q35)</f>
         <v>505.33699999999999</v>
       </c>
       <c r="R36" s="31">
-        <f t="shared" si="44"/>
-        <v>0</v>
+        <f t="shared" si="46"/>
+        <v>488.34399999999999</v>
       </c>
       <c r="S36" s="31">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="T36" s="12"/>
+        <f t="shared" si="46"/>
+        <v>467.32100000000003</v>
+      </c>
+      <c r="T36" s="31">
+        <f>SUM(T27:T35)</f>
+        <v>461.363</v>
+      </c>
+      <c r="U36" s="31"/>
+      <c r="V36" s="31"/>
+      <c r="W36" s="31"/>
+      <c r="X36" s="12"/>
     </row>
-    <row r="37" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C37" s="1" t="s">
         <v>58</v>
       </c>
@@ -4453,14 +4795,24 @@
       <c r="P37" s="12">
         <v>44.868000000000002</v>
       </c>
-      <c r="Q37" s="13">
+      <c r="Q37" s="12">
         <v>69.834999999999994</v>
       </c>
-      <c r="R37" s="12"/>
-      <c r="S37" s="12"/>
-      <c r="T37" s="12"/>
+      <c r="R37" s="12">
+        <v>52.228999999999999</v>
+      </c>
+      <c r="S37" s="12">
+        <v>56.332000000000001</v>
+      </c>
+      <c r="T37" s="12">
+        <v>73.629000000000005</v>
+      </c>
+      <c r="U37" s="12"/>
+      <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
+      <c r="X37" s="12"/>
     </row>
-    <row r="38" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C38" s="1" t="s">
         <v>59</v>
       </c>
@@ -4503,14 +4855,24 @@
       <c r="P38" s="12">
         <v>669.61</v>
       </c>
-      <c r="Q38" s="13">
+      <c r="Q38" s="12">
         <v>609.79999999999995</v>
       </c>
-      <c r="R38" s="12"/>
-      <c r="S38" s="12"/>
-      <c r="T38" s="12"/>
+      <c r="R38" s="12">
+        <v>664.173</v>
+      </c>
+      <c r="S38" s="12">
+        <v>477.21300000000002</v>
+      </c>
+      <c r="T38" s="12">
+        <v>629.68299999999999</v>
+      </c>
+      <c r="U38" s="12"/>
+      <c r="V38" s="12"/>
+      <c r="W38" s="12"/>
+      <c r="X38" s="12"/>
     </row>
-    <row r="39" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C39" s="1" t="s">
         <v>60</v>
       </c>
@@ -4553,14 +4915,24 @@
       <c r="P39" s="12">
         <v>113.988</v>
       </c>
-      <c r="Q39" s="13">
+      <c r="Q39" s="12">
         <v>100.8</v>
       </c>
-      <c r="R39" s="12"/>
-      <c r="S39" s="12"/>
-      <c r="T39" s="12"/>
+      <c r="R39" s="12">
+        <v>77.168999999999997</v>
+      </c>
+      <c r="S39" s="12">
+        <v>55.421999999999997</v>
+      </c>
+      <c r="T39" s="12">
+        <v>116.72199999999999</v>
+      </c>
+      <c r="U39" s="12"/>
+      <c r="V39" s="12"/>
+      <c r="W39" s="12"/>
+      <c r="X39" s="12"/>
     </row>
-    <row r="40" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C40" s="1" t="s">
         <v>61</v>
       </c>
@@ -4603,55 +4975,65 @@
       <c r="P40" s="12">
         <v>741.18499999999995</v>
       </c>
-      <c r="Q40" s="13">
+      <c r="Q40" s="12">
         <v>383.48099999999999</v>
       </c>
-      <c r="R40" s="12"/>
-      <c r="S40" s="12"/>
-      <c r="T40" s="12"/>
+      <c r="R40" s="12">
+        <v>373.41899999999998</v>
+      </c>
+      <c r="S40" s="12">
+        <v>672.30399999999997</v>
+      </c>
+      <c r="T40" s="12">
+        <v>551.20299999999997</v>
+      </c>
+      <c r="U40" s="12"/>
+      <c r="V40" s="12"/>
+      <c r="W40" s="12"/>
+      <c r="X40" s="12"/>
     </row>
-    <row r="41" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C41" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D41" s="31">
-        <f t="shared" ref="D41:M41" si="45">SUM(D37:D40)</f>
+        <f t="shared" ref="D41:M41" si="47">SUM(D37:D40)</f>
         <v>1216.9189999999999</v>
       </c>
       <c r="E41" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>952.78499999999985</v>
       </c>
       <c r="F41" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>941.11400000000003</v>
       </c>
       <c r="G41" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1083.67</v>
       </c>
       <c r="H41" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1319.848</v>
       </c>
       <c r="I41" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1054.277</v>
       </c>
       <c r="J41" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1036.999</v>
       </c>
       <c r="K41" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1223.098</v>
       </c>
       <c r="L41" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1442.579</v>
       </c>
       <c r="M41" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1211.2829999999999</v>
       </c>
       <c r="N41" s="31">
@@ -4666,62 +5048,69 @@
         <f>SUM(P37:P40)</f>
         <v>1569.6510000000001</v>
       </c>
-      <c r="Q41" s="34">
-        <f t="shared" ref="Q41:S41" si="46">SUM(Q37:Q40)</f>
+      <c r="Q41" s="31">
+        <f t="shared" ref="Q41:T41" si="48">SUM(Q37:Q40)</f>
         <v>1163.9159999999999</v>
       </c>
       <c r="R41" s="31">
-        <f t="shared" si="46"/>
-        <v>0</v>
+        <f t="shared" si="48"/>
+        <v>1166.99</v>
       </c>
       <c r="S41" s="31">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="T41" s="12"/>
+        <f t="shared" si="48"/>
+        <v>1261.2710000000002</v>
+      </c>
+      <c r="T41" s="31">
+        <f t="shared" si="48"/>
+        <v>1371.2370000000001</v>
+      </c>
+      <c r="U41" s="31"/>
+      <c r="V41" s="31"/>
+      <c r="W41" s="31"/>
+      <c r="X41" s="12"/>
     </row>
-    <row r="42" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C42" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D42" s="18">
-        <f t="shared" ref="D42:M42" si="47">D36+D41</f>
+        <f t="shared" ref="D42:M42" si="49">D36+D41</f>
         <v>1593.5069999999998</v>
       </c>
       <c r="E42" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>1328.6749999999997</v>
       </c>
       <c r="F42" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>1314.905</v>
       </c>
       <c r="G42" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>1444.7060000000001</v>
       </c>
       <c r="H42" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>1689.742</v>
       </c>
       <c r="I42" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>1420.1130000000001</v>
       </c>
       <c r="J42" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>1389.856</v>
       </c>
       <c r="K42" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>1715.5419999999999</v>
       </c>
       <c r="L42" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>1955.953</v>
       </c>
       <c r="M42" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>1719.6499999999999</v>
       </c>
       <c r="N42" s="18">
@@ -4736,21 +5125,28 @@
         <f>P36+P41</f>
         <v>2024.672</v>
       </c>
-      <c r="Q42" s="35">
-        <f t="shared" ref="Q42:S42" si="48">Q36+Q41</f>
+      <c r="Q42" s="18">
+        <f t="shared" ref="Q42:S42" si="50">Q36+Q41</f>
         <v>1669.2529999999999</v>
       </c>
       <c r="R42" s="18">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="50"/>
+        <v>1655.3340000000001</v>
       </c>
       <c r="S42" s="18">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="T42" s="12"/>
+        <f t="shared" si="50"/>
+        <v>1728.5920000000001</v>
+      </c>
+      <c r="T42" s="18">
+        <f>T36+T41</f>
+        <v>1832.6000000000001</v>
+      </c>
+      <c r="U42" s="18"/>
+      <c r="V42" s="18"/>
+      <c r="W42" s="18"/>
+      <c r="X42" s="12"/>
     </row>
-    <row r="43" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C43" s="1" t="s">
         <v>64</v>
       </c>
@@ -4793,14 +5189,24 @@
       <c r="P43" s="12">
         <v>10.38</v>
       </c>
-      <c r="Q43" s="13">
+      <c r="Q43" s="12">
         <v>10.38</v>
       </c>
-      <c r="R43" s="12"/>
-      <c r="S43" s="12"/>
-      <c r="T43" s="12"/>
+      <c r="R43" s="12">
+        <v>10.38</v>
+      </c>
+      <c r="S43" s="12">
+        <v>10.38</v>
+      </c>
+      <c r="T43" s="12">
+        <v>10.38</v>
+      </c>
+      <c r="U43" s="12"/>
+      <c r="V43" s="12"/>
+      <c r="W43" s="12"/>
+      <c r="X43" s="12"/>
     </row>
-    <row r="44" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C44" s="1" t="s">
         <v>65</v>
       </c>
@@ -4843,14 +5249,24 @@
       <c r="P44" s="12">
         <v>-9.1999999999999998E-2</v>
       </c>
-      <c r="Q44" s="13">
+      <c r="Q44" s="12">
         <v>0</v>
       </c>
-      <c r="R44" s="12"/>
-      <c r="S44" s="12"/>
-      <c r="T44" s="12"/>
+      <c r="R44" s="12">
+        <v>0</v>
+      </c>
+      <c r="S44" s="12">
+        <v>-4.3999999999999997E-2</v>
+      </c>
+      <c r="T44" s="12">
+        <v>-0.14399999999999999</v>
+      </c>
+      <c r="U44" s="12"/>
+      <c r="V44" s="12"/>
+      <c r="W44" s="12"/>
+      <c r="X44" s="12"/>
     </row>
-    <row r="45" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C45" s="1" t="s">
         <v>66</v>
       </c>
@@ -4893,14 +5309,24 @@
       <c r="P45" s="12">
         <v>0.17899999999999999</v>
       </c>
-      <c r="Q45" s="13">
+      <c r="Q45" s="12">
         <v>0</v>
       </c>
-      <c r="R45" s="12"/>
-      <c r="S45" s="12"/>
-      <c r="T45" s="12"/>
+      <c r="R45" s="12">
+        <v>0</v>
+      </c>
+      <c r="S45" s="12">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="T45" s="12">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="U45" s="12"/>
+      <c r="V45" s="12"/>
+      <c r="W45" s="12"/>
+      <c r="X45" s="12"/>
     </row>
-    <row r="46" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C46" s="1" t="s">
         <v>67</v>
       </c>
@@ -4943,14 +5369,24 @@
       <c r="P46" s="12">
         <v>537.93200000000002</v>
       </c>
-      <c r="Q46" s="13">
+      <c r="Q46" s="12">
         <v>301.48099999999999</v>
       </c>
-      <c r="R46" s="12"/>
-      <c r="S46" s="12"/>
-      <c r="T46" s="12"/>
+      <c r="R46" s="12">
+        <v>377.54399999999998</v>
+      </c>
+      <c r="S46" s="12">
+        <v>413.47699999999998</v>
+      </c>
+      <c r="T46" s="12">
+        <v>466.31599999999997</v>
+      </c>
+      <c r="U46" s="12"/>
+      <c r="V46" s="12"/>
+      <c r="W46" s="12"/>
+      <c r="X46" s="12"/>
     </row>
-    <row r="47" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C47" s="1" t="s">
         <v>68</v>
       </c>
@@ -4993,55 +5429,65 @@
       <c r="P47" s="12">
         <v>0</v>
       </c>
-      <c r="Q47" s="13">
+      <c r="Q47" s="12">
         <v>0</v>
       </c>
-      <c r="R47" s="12"/>
-      <c r="S47" s="12"/>
-      <c r="T47" s="12"/>
+      <c r="R47" s="12">
+        <v>0</v>
+      </c>
+      <c r="S47" s="12">
+        <v>0</v>
+      </c>
+      <c r="T47" s="12">
+        <v>0</v>
+      </c>
+      <c r="U47" s="12"/>
+      <c r="V47" s="12"/>
+      <c r="W47" s="12"/>
+      <c r="X47" s="12"/>
     </row>
-    <row r="48" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C48" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D48" s="18">
-        <f t="shared" ref="D48:M48" si="49">SUM(D43:D47)</f>
+        <f t="shared" ref="D48:M48" si="51">SUM(D43:D47)</f>
         <v>516.57100000000003</v>
       </c>
       <c r="E48" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>333.16500000000002</v>
       </c>
       <c r="F48" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>386.48499999999996</v>
       </c>
       <c r="G48" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>456.96899999999999</v>
       </c>
       <c r="H48" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>552.34699999999987</v>
       </c>
       <c r="I48" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>331.40500000000003</v>
       </c>
       <c r="J48" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>387.86200000000002</v>
       </c>
       <c r="K48" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>458.3</v>
       </c>
       <c r="L48" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>547.56699999999989</v>
       </c>
       <c r="M48" s="18">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>360.33199999999999</v>
       </c>
       <c r="N48" s="18">
@@ -5056,21 +5502,28 @@
         <f>SUM(P43:P47)</f>
         <v>548.399</v>
       </c>
-      <c r="Q48" s="35">
-        <f t="shared" ref="Q48:S48" si="50">SUM(Q43:Q47)</f>
+      <c r="Q48" s="18">
+        <f t="shared" ref="Q48:S48" si="52">SUM(Q43:Q47)</f>
         <v>311.86099999999999</v>
       </c>
       <c r="R48" s="18">
-        <f t="shared" si="50"/>
-        <v>0</v>
+        <f t="shared" si="52"/>
+        <v>387.92399999999998</v>
       </c>
       <c r="S48" s="18">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="T48" s="12"/>
+        <f t="shared" si="52"/>
+        <v>423.99199999999996</v>
+      </c>
+      <c r="T48" s="18">
+        <f>SUM(T43:T47)</f>
+        <v>476.73099999999999</v>
+      </c>
+      <c r="U48" s="18"/>
+      <c r="V48" s="18"/>
+      <c r="W48" s="18"/>
+      <c r="X48" s="12"/>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C49" s="1" t="s">
         <v>70</v>
       </c>
@@ -5113,14 +5566,24 @@
       <c r="P49" s="12">
         <v>238.852</v>
       </c>
-      <c r="Q49" s="13">
+      <c r="Q49" s="12">
         <v>278</v>
       </c>
-      <c r="R49" s="12"/>
-      <c r="S49" s="12"/>
-      <c r="T49" s="12"/>
+      <c r="R49" s="12">
+        <v>262.56299999999999</v>
+      </c>
+      <c r="S49" s="12">
+        <v>256.83300000000003</v>
+      </c>
+      <c r="T49" s="12">
+        <v>257.56700000000001</v>
+      </c>
+      <c r="U49" s="12"/>
+      <c r="V49" s="12"/>
+      <c r="W49" s="12"/>
+      <c r="X49" s="12"/>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C50" s="1" t="s">
         <v>71</v>
       </c>
@@ -5163,14 +5626,24 @@
       <c r="P50" s="12">
         <v>5.5449999999999999</v>
       </c>
-      <c r="Q50" s="13">
+      <c r="Q50" s="12">
         <v>5.5</v>
       </c>
-      <c r="R50" s="12"/>
-      <c r="S50" s="12"/>
-      <c r="T50" s="12"/>
+      <c r="R50" s="12">
+        <v>5.5449999999999999</v>
+      </c>
+      <c r="S50" s="12">
+        <v>0</v>
+      </c>
+      <c r="T50" s="12">
+        <v>0</v>
+      </c>
+      <c r="U50" s="12"/>
+      <c r="V50" s="12"/>
+      <c r="W50" s="12"/>
+      <c r="X50" s="12"/>
     </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C51" s="1" t="s">
         <v>72</v>
       </c>
@@ -5213,14 +5686,24 @@
       <c r="P51" s="12">
         <v>75.224999999999994</v>
       </c>
-      <c r="Q51" s="13">
+      <c r="Q51" s="12">
         <v>83.995999999999995</v>
       </c>
-      <c r="R51" s="12"/>
-      <c r="S51" s="12"/>
-      <c r="T51" s="12"/>
+      <c r="R51" s="12">
+        <v>84.46</v>
+      </c>
+      <c r="S51" s="12">
+        <v>85.091999999999999</v>
+      </c>
+      <c r="T51" s="12">
+        <v>81.474000000000004</v>
+      </c>
+      <c r="U51" s="12"/>
+      <c r="V51" s="12"/>
+      <c r="W51" s="12"/>
+      <c r="X51" s="12"/>
     </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C52" s="1" t="s">
         <v>73</v>
       </c>
@@ -5263,14 +5746,24 @@
       <c r="P52" s="12">
         <v>97.912999999999997</v>
       </c>
-      <c r="Q52" s="13">
+      <c r="Q52" s="12">
         <v>84.454999999999998</v>
       </c>
-      <c r="R52" s="12"/>
-      <c r="S52" s="12"/>
-      <c r="T52" s="12"/>
+      <c r="R52" s="12">
+        <v>80.87</v>
+      </c>
+      <c r="S52" s="12">
+        <v>74.266000000000005</v>
+      </c>
+      <c r="T52" s="12">
+        <v>87.762</v>
+      </c>
+      <c r="U52" s="12"/>
+      <c r="V52" s="12"/>
+      <c r="W52" s="12"/>
+      <c r="X52" s="12"/>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C53" s="1" t="s">
         <v>74</v>
       </c>
@@ -5313,14 +5806,24 @@
       <c r="P53" s="12">
         <v>103.117</v>
       </c>
-      <c r="Q53" s="13">
+      <c r="Q53" s="12">
         <v>82.885000000000005</v>
       </c>
-      <c r="R53" s="12"/>
-      <c r="S53" s="12"/>
-      <c r="T53" s="12"/>
+      <c r="R53" s="12">
+        <v>102.931</v>
+      </c>
+      <c r="S53" s="12">
+        <v>104.63500000000001</v>
+      </c>
+      <c r="T53" s="12">
+        <v>73.007000000000005</v>
+      </c>
+      <c r="U53" s="12"/>
+      <c r="V53" s="12"/>
+      <c r="W53" s="12"/>
+      <c r="X53" s="12"/>
     </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C54" s="1" t="s">
         <v>75</v>
       </c>
@@ -5363,14 +5866,24 @@
       <c r="P54" s="12">
         <v>349.35199999999998</v>
       </c>
-      <c r="Q54" s="13">
+      <c r="Q54" s="12">
         <v>364</v>
       </c>
-      <c r="R54" s="12"/>
-      <c r="S54" s="12"/>
-      <c r="T54" s="12"/>
+      <c r="R54" s="12">
+        <v>309.85399999999998</v>
+      </c>
+      <c r="S54" s="12">
+        <v>318.69600000000003</v>
+      </c>
+      <c r="T54" s="12">
+        <v>290.26900000000001</v>
+      </c>
+      <c r="U54" s="12"/>
+      <c r="V54" s="12"/>
+      <c r="W54" s="12"/>
+      <c r="X54" s="12"/>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C55" s="1" t="s">
         <v>76</v>
       </c>
@@ -5413,14 +5926,24 @@
       <c r="P55" s="12">
         <v>5.883</v>
       </c>
-      <c r="Q55" s="13">
+      <c r="Q55" s="12">
         <v>5.5</v>
       </c>
-      <c r="R55" s="12"/>
-      <c r="S55" s="12"/>
-      <c r="T55" s="12"/>
+      <c r="R55" s="12">
+        <v>6</v>
+      </c>
+      <c r="S55" s="12">
+        <v>6.4779999999999998</v>
+      </c>
+      <c r="T55" s="12">
+        <v>6.3140000000000001</v>
+      </c>
+      <c r="U55" s="12"/>
+      <c r="V55" s="12"/>
+      <c r="W55" s="12"/>
+      <c r="X55" s="12"/>
     </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C56" s="1" t="s">
         <v>77</v>
       </c>
@@ -5463,55 +5986,65 @@
       <c r="P56" s="12">
         <v>600.43299999999999</v>
       </c>
-      <c r="Q56" s="13">
+      <c r="Q56" s="12">
         <v>453</v>
       </c>
-      <c r="R56" s="12"/>
-      <c r="S56" s="12"/>
-      <c r="T56" s="12"/>
+      <c r="R56" s="12">
+        <v>415.21199999999999</v>
+      </c>
+      <c r="S56" s="12">
+        <v>458.82400000000001</v>
+      </c>
+      <c r="T56" s="12">
+        <v>559.476</v>
+      </c>
+      <c r="U56" s="12"/>
+      <c r="V56" s="12"/>
+      <c r="W56" s="12"/>
+      <c r="X56" s="12"/>
     </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C57" s="3" t="s">
         <v>78</v>
       </c>
       <c r="D57" s="18">
-        <f t="shared" ref="D57:M57" si="51">SUM(D49:D56)</f>
+        <f t="shared" ref="D57:M57" si="53">SUM(D49:D56)</f>
         <v>1076.8699999999999</v>
       </c>
       <c r="E57" s="18">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>995.51499999999987</v>
       </c>
       <c r="F57" s="18">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>928.64100000000008</v>
       </c>
       <c r="G57" s="18">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>987.779</v>
       </c>
       <c r="H57" s="18">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1137.453</v>
       </c>
       <c r="I57" s="18">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1089.087</v>
       </c>
       <c r="J57" s="18">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1003.1019999999999</v>
       </c>
       <c r="K57" s="18">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1257.2359999999999</v>
       </c>
       <c r="L57" s="18">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1408.4159999999997</v>
       </c>
       <c r="M57" s="18">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>1359.307</v>
       </c>
       <c r="N57" s="18">
@@ -5526,62 +6059,69 @@
         <f>SUM(P49:P56)</f>
         <v>1476.32</v>
       </c>
-      <c r="Q57" s="35">
-        <f t="shared" ref="Q57:S57" si="52">SUM(Q49:Q56)</f>
+      <c r="Q57" s="18">
+        <f t="shared" ref="Q57:S57" si="54">SUM(Q49:Q56)</f>
         <v>1357.336</v>
       </c>
       <c r="R57" s="18">
-        <f t="shared" si="52"/>
-        <v>0</v>
+        <f t="shared" si="54"/>
+        <v>1267.4349999999999</v>
       </c>
       <c r="S57" s="18">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="T57" s="12"/>
+        <f t="shared" si="54"/>
+        <v>1304.8240000000001</v>
+      </c>
+      <c r="T57" s="18">
+        <f t="shared" ref="T57" si="55">SUM(T49:T56)</f>
+        <v>1355.8689999999999</v>
+      </c>
+      <c r="U57" s="18"/>
+      <c r="V57" s="18"/>
+      <c r="W57" s="18"/>
+      <c r="X57" s="12"/>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C58" s="3" t="s">
         <v>79</v>
       </c>
       <c r="D58" s="18">
-        <f t="shared" ref="D58:M58" si="53">D48+D57</f>
+        <f t="shared" ref="D58:M58" si="56">D48+D57</f>
         <v>1593.4409999999998</v>
       </c>
       <c r="E58" s="18">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>1328.6799999999998</v>
       </c>
       <c r="F58" s="18">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>1315.126</v>
       </c>
       <c r="G58" s="18">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>1444.748</v>
       </c>
       <c r="H58" s="18">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>1689.7999999999997</v>
       </c>
       <c r="I58" s="18">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>1420.492</v>
       </c>
       <c r="J58" s="18">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>1390.9639999999999</v>
       </c>
       <c r="K58" s="18">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>1715.5359999999998</v>
       </c>
       <c r="L58" s="18">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>1955.9829999999997</v>
       </c>
       <c r="M58" s="18">
-        <f t="shared" si="53"/>
+        <f t="shared" si="56"/>
         <v>1719.6390000000001</v>
       </c>
       <c r="N58" s="18">
@@ -5596,21 +6136,28 @@
         <f>P48+P57</f>
         <v>2024.7190000000001</v>
       </c>
-      <c r="Q58" s="35">
-        <f t="shared" ref="Q58:S58" si="54">Q48+Q57</f>
+      <c r="Q58" s="18">
+        <f t="shared" ref="Q58:S58" si="57">Q48+Q57</f>
         <v>1669.1970000000001</v>
       </c>
       <c r="R58" s="18">
-        <f t="shared" si="54"/>
-        <v>0</v>
+        <f t="shared" si="57"/>
+        <v>1655.3589999999999</v>
       </c>
       <c r="S58" s="18">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="T58" s="12"/>
+        <f t="shared" si="57"/>
+        <v>1728.816</v>
+      </c>
+      <c r="T58" s="18">
+        <f t="shared" ref="T58" si="58">T48+T57</f>
+        <v>1832.6</v>
+      </c>
+      <c r="U58" s="18"/>
+      <c r="V58" s="18"/>
+      <c r="W58" s="18"/>
+      <c r="X58" s="12"/>
     </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D59" s="12"/>
       <c r="E59" s="12"/>
       <c r="F59" s="12"/>
@@ -5624,7 +6171,7 @@
       <c r="N59" s="12"/>
       <c r="O59" s="12"/>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C60" s="4" t="s">
         <v>98</v>
       </c>
@@ -5641,76 +6188,84 @@
       <c r="N60" s="12"/>
       <c r="O60" s="12"/>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C61" s="1" t="s">
         <v>106</v>
       </c>
       <c r="D61" s="12">
-        <f t="shared" ref="D61:S61" si="55">D12</f>
+        <f t="shared" ref="D61:T61" si="59">D12</f>
         <v>121.89100000000001</v>
       </c>
       <c r="E61" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>88.753000000000085</v>
       </c>
       <c r="F61" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>73.35799999999999</v>
       </c>
       <c r="G61" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>116.982</v>
       </c>
       <c r="H61" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>133.71400000000008</v>
       </c>
       <c r="I61" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>90.53199999999994</v>
       </c>
       <c r="J61" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>81.785999999999973</v>
       </c>
       <c r="K61" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>112.38600000000007</v>
       </c>
       <c r="L61" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>134.87399999999985</v>
       </c>
       <c r="M61" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>135.87400000000002</v>
       </c>
       <c r="N61" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>100.72500000000007</v>
       </c>
       <c r="O61" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>120.5709999999999</v>
       </c>
       <c r="P61" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>156.9070000000001</v>
       </c>
-      <c r="Q61" s="13">
-        <f t="shared" si="55"/>
+      <c r="Q61" s="12">
+        <f t="shared" si="59"/>
         <v>123.44900000000004</v>
       </c>
       <c r="R61" s="12">
-        <f t="shared" si="55"/>
-        <v>0</v>
+        <f t="shared" si="59"/>
+        <v>90.40500000000003</v>
       </c>
       <c r="S61" s="12">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="59"/>
+        <v>102.31699999999998</v>
+      </c>
+      <c r="T61" s="12">
+        <f t="shared" si="59"/>
+        <v>125.83999999999999</v>
+      </c>
+      <c r="U61" s="12"/>
+      <c r="V61" s="12"/>
+      <c r="W61" s="12"/>
+      <c r="X61" s="12"/>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C62" s="1" t="s">
         <v>107</v>
       </c>
@@ -5753,11 +6308,24 @@
       <c r="P62" s="12">
         <v>157</v>
       </c>
-      <c r="Q62" s="13">
+      <c r="Q62" s="12">
         <v>123</v>
       </c>
+      <c r="R62" s="12">
+        <v>90</v>
+      </c>
+      <c r="S62" s="12">
+        <v>102</v>
+      </c>
+      <c r="T62" s="12">
+        <v>126</v>
+      </c>
+      <c r="U62" s="12"/>
+      <c r="V62" s="12"/>
+      <c r="W62" s="12"/>
+      <c r="X62" s="12"/>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C63" s="1" t="s">
         <v>108</v>
       </c>
@@ -5800,11 +6368,24 @@
       <c r="P63" s="12">
         <v>-49.381999999999998</v>
       </c>
-      <c r="Q63" s="13">
+      <c r="Q63" s="12">
         <v>-48.353000000000002</v>
       </c>
+      <c r="R63" s="12">
+        <v>0</v>
+      </c>
+      <c r="S63" s="12">
+        <v>-19.177</v>
+      </c>
+      <c r="T63" s="12">
+        <v>-60.215000000000003</v>
+      </c>
+      <c r="U63" s="12"/>
+      <c r="V63" s="12"/>
+      <c r="W63" s="12"/>
+      <c r="X63" s="12"/>
     </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C64" s="1" t="s">
         <v>109</v>
       </c>
@@ -5847,11 +6428,24 @@
       <c r="P64" s="12">
         <v>-6.8000000000000005E-2</v>
       </c>
-      <c r="Q64" s="13">
+      <c r="Q64" s="12">
         <v>0</v>
       </c>
+      <c r="R64" s="12">
+        <v>0</v>
+      </c>
+      <c r="S64" s="12">
+        <v>-2.1999999999999999E-2</v>
+      </c>
+      <c r="T64" s="12">
+        <v>-1.6E-2</v>
+      </c>
+      <c r="U64" s="12"/>
+      <c r="V64" s="12"/>
+      <c r="W64" s="12"/>
+      <c r="X64" s="12"/>
     </row>
-    <row r="65" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C65" s="1" t="s">
         <v>110</v>
       </c>
@@ -5894,11 +6488,24 @@
       <c r="P65" s="12">
         <v>22.225000000000001</v>
       </c>
-      <c r="Q65" s="13">
+      <c r="Q65" s="12">
         <v>22.582000000000001</v>
       </c>
+      <c r="R65" s="12">
+        <v>22.359000000000002</v>
+      </c>
+      <c r="S65" s="12">
+        <v>23.245000000000001</v>
+      </c>
+      <c r="T65" s="12">
+        <v>23.274999999999999</v>
+      </c>
+      <c r="U65" s="12"/>
+      <c r="V65" s="12"/>
+      <c r="W65" s="12"/>
+      <c r="X65" s="12"/>
     </row>
-    <row r="66" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C66" s="1" t="s">
         <v>111</v>
       </c>
@@ -5941,11 +6548,24 @@
       <c r="P66" s="12">
         <v>2.194</v>
       </c>
-      <c r="Q66" s="13">
+      <c r="Q66" s="12">
         <v>2</v>
       </c>
+      <c r="R66" s="12">
+        <v>2.1960000000000002</v>
+      </c>
+      <c r="S66" s="12">
+        <v>2.1960000000000002</v>
+      </c>
+      <c r="T66" s="12">
+        <v>2.1960000000000002</v>
+      </c>
+      <c r="U66" s="12"/>
+      <c r="V66" s="12"/>
+      <c r="W66" s="12"/>
+      <c r="X66" s="12"/>
     </row>
-    <row r="67" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C67" s="1" t="s">
         <v>112</v>
       </c>
@@ -5988,11 +6608,24 @@
       <c r="P67" s="12">
         <v>4.7919999999999998</v>
       </c>
-      <c r="Q67" s="13">
+      <c r="Q67" s="12">
         <v>4.7</v>
       </c>
+      <c r="R67" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="S67" s="12">
+        <v>7.4470000000000001</v>
+      </c>
+      <c r="T67" s="12">
+        <v>5.1909999999999998</v>
+      </c>
+      <c r="U67" s="12"/>
+      <c r="V67" s="12"/>
+      <c r="W67" s="12"/>
+      <c r="X67" s="12"/>
     </row>
-    <row r="68" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C68" s="1" t="s">
         <v>113</v>
       </c>
@@ -6035,11 +6668,24 @@
       <c r="P68" s="12">
         <v>-256.04300000000001</v>
       </c>
-      <c r="Q68" s="13">
+      <c r="Q68" s="12">
         <v>21.3</v>
       </c>
+      <c r="R68" s="12">
+        <v>-40.337000000000003</v>
+      </c>
+      <c r="S68" s="12">
+        <v>176.25299999999999</v>
+      </c>
+      <c r="T68" s="12">
+        <v>-156.27099999999999</v>
+      </c>
+      <c r="U68" s="12"/>
+      <c r="V68" s="12"/>
+      <c r="W68" s="12"/>
+      <c r="X68" s="12"/>
     </row>
-    <row r="69" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C69" s="1" t="s">
         <v>114</v>
       </c>
@@ -6080,11 +6726,24 @@
       <c r="P69" s="12">
         <v>-7</v>
       </c>
-      <c r="Q69" s="13">
+      <c r="Q69" s="12">
         <v>-6</v>
       </c>
+      <c r="R69" s="12">
+        <v>-5</v>
+      </c>
+      <c r="S69" s="12">
+        <v>-4.4000000000000004</v>
+      </c>
+      <c r="T69" s="12">
+        <v>-5.3609999999999998</v>
+      </c>
+      <c r="U69" s="12"/>
+      <c r="V69" s="12"/>
+      <c r="W69" s="12"/>
+      <c r="X69" s="12"/>
     </row>
-    <row r="70" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C70" s="1" t="s">
         <v>115</v>
       </c>
@@ -6127,28 +6786,41 @@
       <c r="P70" s="12">
         <v>91.756</v>
       </c>
-      <c r="Q70" s="13">
+      <c r="Q70" s="12">
         <v>-113.1</v>
       </c>
+      <c r="R70" s="12">
+        <v>-61.966999999999999</v>
+      </c>
+      <c r="S70" s="12">
+        <v>75.786000000000001</v>
+      </c>
+      <c r="T70" s="12">
+        <v>17</v>
+      </c>
+      <c r="U70" s="12"/>
+      <c r="V70" s="12"/>
+      <c r="W70" s="12"/>
+      <c r="X70" s="12"/>
     </row>
-    <row r="71" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C71" s="4" t="s">
         <v>80</v>
       </c>
       <c r="D71" s="10">
-        <f t="shared" ref="D71:N71" si="56">SUM(D62:D70)</f>
+        <f t="shared" ref="D71:N71" si="60">SUM(D62:D70)</f>
         <v>89.838999999999984</v>
       </c>
       <c r="E71" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>36.957999999999998</v>
       </c>
       <c r="F71" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>15.878999999999984</v>
       </c>
       <c r="G71" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>178.1</v>
       </c>
       <c r="H71" s="10">
@@ -6156,27 +6828,27 @@
         <v>133.393</v>
       </c>
       <c r="I71" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>124.31399999999999</v>
       </c>
       <c r="J71" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>-117.169</v>
       </c>
       <c r="K71" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>388.238</v>
       </c>
       <c r="L71" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>63.908000000000008</v>
       </c>
       <c r="M71" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>108.447</v>
       </c>
       <c r="N71" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>140.827</v>
       </c>
       <c r="O71" s="10">
@@ -6187,20 +6859,28 @@
         <f>SUM(P62:P70)</f>
         <v>-34.52600000000001</v>
       </c>
-      <c r="Q71" s="11">
-        <f t="shared" ref="Q71:S71" si="57">SUM(Q62:Q70)</f>
+      <c r="Q71" s="10">
+        <f t="shared" ref="Q71:S71" si="61">SUM(Q62:Q70)</f>
         <v>6.1289999999999907</v>
       </c>
       <c r="R71" s="10">
-        <f t="shared" si="57"/>
-        <v>0</v>
+        <f t="shared" si="61"/>
+        <v>12.051000000000002</v>
       </c>
       <c r="S71" s="10">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="61"/>
+        <v>363.32800000000003</v>
+      </c>
+      <c r="T71" s="10">
+        <f>SUM(T62:T70)</f>
+        <v>-48.201000000000008</v>
+      </c>
+      <c r="U71" s="10"/>
+      <c r="V71" s="10"/>
+      <c r="W71" s="10"/>
+      <c r="X71" s="12"/>
     </row>
-    <row r="72" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D72" s="12"/>
       <c r="E72" s="12"/>
       <c r="F72" s="12"/>
@@ -6214,9 +6894,16 @@
       <c r="N72" s="12"/>
       <c r="O72" s="12"/>
       <c r="P72" s="12"/>
-      <c r="Q72" s="13"/>
+      <c r="Q72" s="12"/>
+      <c r="R72" s="12"/>
+      <c r="S72" s="12"/>
+      <c r="T72" s="12"/>
+      <c r="U72" s="12"/>
+      <c r="V72" s="12"/>
+      <c r="W72" s="12"/>
+      <c r="X72" s="12"/>
     </row>
-    <row r="73" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C73" s="1" t="s">
         <v>116</v>
       </c>
@@ -6259,11 +6946,24 @@
       <c r="P73" s="12">
         <v>7.8E-2</v>
       </c>
-      <c r="Q73" s="13">
+      <c r="Q73" s="12">
         <v>0</v>
       </c>
+      <c r="R73" s="12">
+        <v>0</v>
+      </c>
+      <c r="S73" s="12">
+        <v>0</v>
+      </c>
+      <c r="T73" s="12">
+        <v>1.6E-2</v>
+      </c>
+      <c r="U73" s="12"/>
+      <c r="V73" s="12"/>
+      <c r="W73" s="12"/>
+      <c r="X73" s="12"/>
     </row>
-    <row r="74" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C74" s="1" t="s">
         <v>117</v>
       </c>
@@ -6317,11 +7017,24 @@
       <c r="P74" s="12">
         <v>-3.3340000000000001</v>
       </c>
-      <c r="Q74" s="13">
+      <c r="Q74" s="12">
         <v>-11.8</v>
       </c>
+      <c r="R74" s="12">
+        <v>-7</v>
+      </c>
+      <c r="S74" s="12">
+        <v>-4</v>
+      </c>
+      <c r="T74" s="12">
+        <v>-3.504</v>
+      </c>
+      <c r="U74" s="12"/>
+      <c r="V74" s="12"/>
+      <c r="W74" s="12"/>
+      <c r="X74" s="12"/>
     </row>
-    <row r="75" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C75" s="1" t="s">
         <v>118</v>
       </c>
@@ -6364,11 +7077,24 @@
       <c r="P75" s="12">
         <v>0</v>
       </c>
-      <c r="Q75" s="13">
+      <c r="Q75" s="12">
         <v>0</v>
       </c>
+      <c r="R75" s="12">
+        <v>0</v>
+      </c>
+      <c r="S75" s="12">
+        <v>-6.3E-2</v>
+      </c>
+      <c r="T75" s="12">
+        <v>-0.90900000000000003</v>
+      </c>
+      <c r="U75" s="12"/>
+      <c r="V75" s="12"/>
+      <c r="W75" s="12"/>
+      <c r="X75" s="12"/>
     </row>
-    <row r="76" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C76" s="1" t="s">
         <v>119</v>
       </c>
@@ -6411,56 +7137,69 @@
       <c r="P76" s="12">
         <v>7.2</v>
       </c>
-      <c r="Q76" s="13">
+      <c r="Q76" s="12">
         <v>6.3490000000000002</v>
       </c>
+      <c r="R76" s="12">
+        <v>6</v>
+      </c>
+      <c r="S76" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="T76" s="12">
+        <v>5.5330000000000004</v>
+      </c>
+      <c r="U76" s="12"/>
+      <c r="V76" s="12"/>
+      <c r="W76" s="12"/>
+      <c r="X76" s="12"/>
     </row>
-    <row r="77" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C77" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D77" s="10">
-        <f t="shared" ref="D77:N77" si="58">SUM(D73:D76)</f>
+        <f t="shared" ref="D77:N77" si="62">SUM(D73:D76)</f>
         <v>-12.799999999999999</v>
       </c>
       <c r="E77" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>-11.373000000000001</v>
       </c>
       <c r="F77" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>-7.7249999999999996</v>
       </c>
       <c r="G77" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>-7.7</v>
       </c>
       <c r="H77" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>-10.100000000000001</v>
       </c>
       <c r="I77" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>-14.662999999999998</v>
       </c>
       <c r="J77" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>-11.725000000000001</v>
       </c>
       <c r="K77" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>-32.691999999999993</v>
       </c>
       <c r="L77" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>-5.3960000000000008</v>
       </c>
       <c r="M77" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>-12.135</v>
       </c>
       <c r="N77" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>-5.4239999999999995</v>
       </c>
       <c r="O77" s="10">
@@ -6471,20 +7210,28 @@
         <f>SUM(P73:P76)</f>
         <v>3.944</v>
       </c>
-      <c r="Q77" s="11">
-        <f t="shared" ref="Q77:S77" si="59">SUM(Q73:Q76)</f>
+      <c r="Q77" s="10">
+        <f t="shared" ref="Q77:S77" si="63">SUM(Q73:Q76)</f>
         <v>-5.4510000000000005</v>
       </c>
       <c r="R77" s="10">
-        <f t="shared" si="59"/>
-        <v>0</v>
+        <f t="shared" si="63"/>
+        <v>-1</v>
       </c>
       <c r="S77" s="10">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="63"/>
+        <v>-1.5629999999999997</v>
+      </c>
+      <c r="T77" s="10">
+        <f>SUM(T73:T76)</f>
+        <v>1.1360000000000001</v>
+      </c>
+      <c r="U77" s="10"/>
+      <c r="V77" s="10"/>
+      <c r="W77" s="10"/>
+      <c r="X77" s="12"/>
     </row>
-    <row r="78" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D78" s="12"/>
       <c r="E78" s="12"/>
       <c r="F78" s="12"/>
@@ -6498,9 +7245,16 @@
       <c r="N78" s="12"/>
       <c r="O78" s="12"/>
       <c r="P78" s="12"/>
-      <c r="Q78" s="13"/>
+      <c r="Q78" s="12"/>
+      <c r="R78" s="12"/>
+      <c r="S78" s="12"/>
+      <c r="T78" s="12"/>
+      <c r="U78" s="12"/>
+      <c r="V78" s="12"/>
+      <c r="W78" s="12"/>
+      <c r="X78" s="12"/>
     </row>
-    <row r="79" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C79" s="1" t="s">
         <v>120</v>
       </c>
@@ -6543,11 +7297,24 @@
       <c r="P79" s="12">
         <v>-43.679000000000002</v>
       </c>
-      <c r="Q79" s="13">
+      <c r="Q79" s="12">
         <v>-30.2</v>
       </c>
+      <c r="R79" s="12">
+        <v>0</v>
+      </c>
+      <c r="S79" s="12">
+        <v>0</v>
+      </c>
+      <c r="T79" s="12">
+        <v>-50.095999999999997</v>
+      </c>
+      <c r="U79" s="12"/>
+      <c r="V79" s="12"/>
+      <c r="W79" s="12"/>
+      <c r="X79" s="12"/>
     </row>
-    <row r="80" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C80" s="1" t="s">
         <v>121</v>
       </c>
@@ -6590,11 +7357,24 @@
       <c r="P80" s="12">
         <v>0</v>
       </c>
-      <c r="Q80" s="13">
+      <c r="Q80" s="12">
         <v>0</v>
       </c>
+      <c r="R80" s="12">
+        <v>0</v>
+      </c>
+      <c r="S80" s="12">
+        <v>31.492999999999999</v>
+      </c>
+      <c r="T80" s="12">
+        <v>0</v>
+      </c>
+      <c r="U80" s="12"/>
+      <c r="V80" s="12"/>
+      <c r="W80" s="12"/>
+      <c r="X80" s="12"/>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C81" s="1" t="s">
         <v>122</v>
       </c>
@@ -6637,11 +7417,24 @@
       <c r="P81" s="12">
         <v>-5.6</v>
       </c>
-      <c r="Q81" s="13">
+      <c r="Q81" s="12">
         <v>-6.9</v>
       </c>
+      <c r="R81" s="12">
+        <v>-6.2110000000000003</v>
+      </c>
+      <c r="S81" s="12">
+        <v>-6.1689999999999996</v>
+      </c>
+      <c r="T81" s="12">
+        <v>-6.1920000000000002</v>
+      </c>
+      <c r="U81" s="12"/>
+      <c r="V81" s="12"/>
+      <c r="W81" s="12"/>
+      <c r="X81" s="12"/>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C82" s="1" t="s">
         <v>123</v>
       </c>
@@ -6684,11 +7477,24 @@
       <c r="P82" s="12">
         <v>-13.1</v>
       </c>
-      <c r="Q82" s="13">
+      <c r="Q82" s="12">
         <v>-13.6</v>
       </c>
+      <c r="R82" s="12">
+        <v>-15</v>
+      </c>
+      <c r="S82" s="12">
+        <v>-15.613</v>
+      </c>
+      <c r="T82" s="12">
+        <v>-17.231000000000002</v>
+      </c>
+      <c r="U82" s="12"/>
+      <c r="V82" s="12"/>
+      <c r="W82" s="12"/>
+      <c r="X82" s="12"/>
     </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C83" s="1" t="s">
         <v>124</v>
       </c>
@@ -6731,11 +7537,24 @@
       <c r="P83" s="12">
         <v>0</v>
       </c>
-      <c r="Q83" s="13">
+      <c r="Q83" s="12">
         <v>0</v>
       </c>
+      <c r="R83" s="12">
+        <v>0</v>
+      </c>
+      <c r="S83" s="12">
+        <v>0</v>
+      </c>
+      <c r="T83" s="12">
+        <v>0</v>
+      </c>
+      <c r="U83" s="12"/>
+      <c r="V83" s="12"/>
+      <c r="W83" s="12"/>
+      <c r="X83" s="12"/>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C84" s="1" t="s">
         <v>125</v>
       </c>
@@ -6778,11 +7597,24 @@
       <c r="P84" s="12">
         <v>-0.17199999999999999</v>
       </c>
-      <c r="Q84" s="13">
+      <c r="Q84" s="12">
         <v>0</v>
       </c>
+      <c r="R84" s="12">
+        <v>0</v>
+      </c>
+      <c r="S84" s="12">
+        <v>-0.59399999999999997</v>
+      </c>
+      <c r="T84" s="12">
+        <v>-0.17199999999999999</v>
+      </c>
+      <c r="U84" s="12"/>
+      <c r="V84" s="12"/>
+      <c r="W84" s="12"/>
+      <c r="X84" s="12"/>
     </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C85" s="1" t="s">
         <v>126</v>
       </c>
@@ -6825,80 +7657,101 @@
       <c r="P85" s="12">
         <v>0</v>
       </c>
-      <c r="Q85" s="13">
+      <c r="Q85" s="12">
         <v>-308.142</v>
       </c>
+      <c r="R85" s="12">
+        <v>0</v>
+      </c>
+      <c r="S85" s="12">
+        <v>-71.736999999999995</v>
+      </c>
+      <c r="T85" s="12">
+        <v>0</v>
+      </c>
+      <c r="U85" s="12"/>
+      <c r="V85" s="12"/>
+      <c r="W85" s="12"/>
+      <c r="X85" s="12"/>
     </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C86" s="4" t="s">
         <v>82</v>
       </c>
       <c r="D86" s="10">
-        <f t="shared" ref="D86:O86" si="60">SUM(D79:D85)</f>
+        <f t="shared" ref="D86:O86" si="64">SUM(D79:D85)</f>
         <v>-49.509</v>
       </c>
       <c r="E86" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>-267.358</v>
       </c>
       <c r="F86" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>-18.47</v>
       </c>
       <c r="G86" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>-43.584000000000003</v>
       </c>
       <c r="H86" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>-33.1</v>
       </c>
       <c r="I86" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>-311.79599999999999</v>
       </c>
       <c r="J86" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>-27.645000000000003</v>
       </c>
       <c r="K86" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>-47.861999999999995</v>
       </c>
       <c r="L86" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>-41.309999999999995</v>
       </c>
       <c r="M86" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>-318.66800000000001</v>
       </c>
       <c r="N86" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>-25</v>
       </c>
       <c r="O86" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>-90.8</v>
       </c>
       <c r="P86" s="10">
         <f>SUM(P79:P85)</f>
         <v>-62.551000000000002</v>
       </c>
-      <c r="Q86" s="11">
-        <f t="shared" ref="Q86:S86" si="61">SUM(Q79:Q85)</f>
+      <c r="Q86" s="10">
+        <f t="shared" ref="Q86:S86" si="65">SUM(Q79:Q85)</f>
         <v>-358.84199999999998</v>
       </c>
       <c r="R86" s="10">
-        <f t="shared" si="61"/>
-        <v>0</v>
+        <f t="shared" si="65"/>
+        <v>-21.210999999999999</v>
       </c>
       <c r="S86" s="10">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="65"/>
+        <v>-62.62</v>
+      </c>
+      <c r="T86" s="10">
+        <f>SUM(T79:T85)</f>
+        <v>-73.691000000000003</v>
+      </c>
+      <c r="U86" s="10"/>
+      <c r="V86" s="10"/>
+      <c r="W86" s="10"/>
+      <c r="X86" s="12"/>
     </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D87" s="12"/>
       <c r="E87" s="12"/>
       <c r="F87" s="12"/>
@@ -6912,78 +7765,93 @@
       <c r="N87" s="12"/>
       <c r="O87" s="12"/>
       <c r="P87" s="12"/>
-      <c r="Q87" s="13"/>
+      <c r="Q87" s="12"/>
+      <c r="R87" s="12"/>
+      <c r="S87" s="12"/>
+      <c r="T87" s="12"/>
+      <c r="U87" s="12"/>
+      <c r="V87" s="12"/>
+      <c r="W87" s="12"/>
+      <c r="X87" s="12"/>
     </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C88" s="1" t="s">
         <v>127</v>
       </c>
       <c r="D88" s="12">
-        <f t="shared" ref="D88:O88" si="62">D71+D77+D86</f>
+        <f t="shared" ref="D88:O88" si="66">D71+D77+D86</f>
         <v>27.529999999999987</v>
       </c>
       <c r="E88" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>-241.773</v>
       </c>
       <c r="F88" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>-10.316000000000015</v>
       </c>
       <c r="G88" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>126.816</v>
       </c>
       <c r="H88" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>90.193000000000012</v>
       </c>
       <c r="I88" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>-202.14499999999998</v>
       </c>
       <c r="J88" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>-156.53900000000002</v>
       </c>
       <c r="K88" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>307.68399999999997</v>
       </c>
       <c r="L88" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>17.202000000000012</v>
       </c>
       <c r="M88" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>-222.35599999999999</v>
       </c>
       <c r="N88" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>110.40299999999999</v>
       </c>
       <c r="O88" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>448.77699999999987</v>
       </c>
       <c r="P88" s="12">
         <f>P71+P77+P86</f>
         <v>-93.13300000000001</v>
       </c>
-      <c r="Q88" s="13">
-        <f t="shared" ref="Q88:S88" si="63">Q71+Q77+Q86</f>
+      <c r="Q88" s="12">
+        <f t="shared" ref="Q88:S88" si="67">Q71+Q77+Q86</f>
         <v>-358.16399999999999</v>
       </c>
       <c r="R88" s="12">
-        <f t="shared" si="63"/>
-        <v>0</v>
+        <f t="shared" si="67"/>
+        <v>-10.159999999999997</v>
       </c>
       <c r="S88" s="12">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="67"/>
+        <v>299.14500000000004</v>
+      </c>
+      <c r="T88" s="12">
+        <f t="shared" ref="T88" si="68">T71+T77+T86</f>
+        <v>-120.756</v>
+      </c>
+      <c r="U88" s="12"/>
+      <c r="V88" s="12"/>
+      <c r="W88" s="12"/>
+      <c r="X88" s="12"/>
     </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:24" x14ac:dyDescent="0.25">
       <c r="D89" s="12"/>
       <c r="E89" s="12"/>
       <c r="F89" s="12"/>
@@ -6997,78 +7865,91 @@
       <c r="N89" s="12"/>
       <c r="O89" s="12"/>
       <c r="P89" s="12"/>
-      <c r="Q89" s="13"/>
+      <c r="Q89" s="12"/>
       <c r="R89" s="12"/>
       <c r="S89" s="12"/>
+      <c r="T89" s="12"/>
+      <c r="U89" s="12"/>
+      <c r="V89" s="12"/>
+      <c r="W89" s="12"/>
+      <c r="X89" s="12"/>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C90" s="1" t="s">
         <v>128</v>
       </c>
       <c r="D90" s="12">
-        <f t="shared" ref="D90:O90" si="64">D71+D74</f>
+        <f t="shared" ref="D90:O90" si="69">D71+D74</f>
         <v>77.038999999999987</v>
       </c>
       <c r="E90" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>25.558</v>
       </c>
       <c r="F90" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>8.0789999999999829</v>
       </c>
       <c r="G90" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>169.4</v>
       </c>
       <c r="H90" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>123.29300000000001</v>
       </c>
       <c r="I90" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>109.61399999999999</v>
       </c>
       <c r="J90" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>-128.952</v>
       </c>
       <c r="K90" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>355.57799999999997</v>
       </c>
       <c r="L90" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>54.448000000000008</v>
       </c>
       <c r="M90" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>96.247</v>
       </c>
       <c r="N90" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>135.36799999999999</v>
       </c>
       <c r="O90" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>540.35699999999997</v>
       </c>
       <c r="P90" s="12">
         <f>P71+P74</f>
         <v>-37.860000000000014</v>
       </c>
-      <c r="Q90" s="13">
-        <f t="shared" ref="Q90:S90" si="65">Q71+Q74</f>
+      <c r="Q90" s="12">
+        <f t="shared" ref="Q90:S90" si="70">Q71+Q74</f>
         <v>-5.67100000000001</v>
       </c>
       <c r="R90" s="12">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" si="70"/>
+        <v>5.0510000000000019</v>
       </c>
       <c r="S90" s="12">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="70"/>
+        <v>359.32800000000003</v>
+      </c>
+      <c r="T90" s="12">
+        <f t="shared" ref="T90" si="71">T71+T74</f>
+        <v>-51.705000000000005</v>
+      </c>
+      <c r="U90" s="12"/>
+      <c r="V90" s="12"/>
+      <c r="W90" s="12"/>
+      <c r="X90" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -7082,19 +7963,19 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="44.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="27.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="5:8" ht="92" x14ac:dyDescent="1">
       <c r="E5" s="29"/>
       <c r="F5" s="29">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G5" s="29">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="H5" s="29">
-        <v>2027</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="6" spans="5:8" ht="92" x14ac:dyDescent="1">
@@ -7102,16 +7983,16 @@
         <v>84</v>
       </c>
       <c r="F6" s="30">
-        <f>Modell!$B$9/Modell!AB10</f>
-        <v>12.813950030360758</v>
+        <f>Modell!$B$9/Modell!AG10</f>
+        <v>9.7710052217816337</v>
       </c>
       <c r="G6" s="30">
-        <f>Modell!$B$9/Modell!AC10</f>
-        <v>11.453506874805106</v>
+        <f>Modell!$B$9/Modell!AH10</f>
+        <v>8.8597866993386045</v>
       </c>
       <c r="H6" s="30">
-        <f>Modell!$B$9/Modell!AD10</f>
-        <v>10.293912940300434</v>
+        <f>Modell!$B$9/Modell!AI10</f>
+        <v>8.5381899230350538</v>
       </c>
     </row>
     <row r="7" spans="5:8" ht="92" x14ac:dyDescent="1">
@@ -7119,16 +8000,16 @@
         <v>85</v>
       </c>
       <c r="F7" s="30">
-        <f>Modell!$B$4/Modell!AB16</f>
-        <v>17.402514285634332</v>
+        <f>Modell!$B$4/Modell!AG16</f>
+        <v>13.806017817367989</v>
       </c>
       <c r="G7" s="30">
-        <f>Modell!$B$4/Modell!AC16</f>
-        <v>15.55490824742941</v>
+        <f>Modell!$B$4/Modell!AH16</f>
+        <v>12.518504519522232</v>
       </c>
       <c r="H7" s="30">
-        <f>Modell!$B$4/Modell!AD16</f>
-        <v>13.980073792562697</v>
+        <f>Modell!$B$4/Modell!AI16</f>
+        <v>12.064101853381262</v>
       </c>
     </row>
   </sheetData>
@@ -7237,48 +8118,47 @@
         <v>3921</v>
       </c>
       <c r="K4" s="11">
-        <f>J4*1.06</f>
-        <v>4156.26</v>
+        <v>3912</v>
       </c>
       <c r="L4" s="10">
         <f>K4*1</f>
-        <v>4156.26</v>
+        <v>3912</v>
       </c>
       <c r="M4" s="10">
         <f t="shared" ref="M4:U4" si="0">L4*1</f>
-        <v>4156.26</v>
+        <v>3912</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" si="0"/>
-        <v>4156.26</v>
+        <v>3912</v>
       </c>
       <c r="O4" s="10">
         <f t="shared" si="0"/>
-        <v>4156.26</v>
+        <v>3912</v>
       </c>
       <c r="P4" s="10">
         <f t="shared" si="0"/>
-        <v>4156.26</v>
+        <v>3912</v>
       </c>
       <c r="Q4" s="10">
         <f t="shared" si="0"/>
-        <v>4156.26</v>
+        <v>3912</v>
       </c>
       <c r="R4" s="10">
         <f t="shared" si="0"/>
-        <v>4156.26</v>
+        <v>3912</v>
       </c>
       <c r="S4" s="10">
         <f t="shared" si="0"/>
-        <v>4156.26</v>
+        <v>3912</v>
       </c>
       <c r="T4" s="10">
         <f t="shared" si="0"/>
-        <v>4156.26</v>
+        <v>3912</v>
       </c>
       <c r="U4" s="10">
         <f t="shared" si="0"/>
-        <v>4156.26</v>
+        <v>3912</v>
       </c>
       <c r="V4" s="10"/>
       <c r="W4" s="10"/>
@@ -7302,7 +8182,7 @@
     <row r="5" spans="1:16367" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <f>X21</f>
-        <v>44.89667812286153</v>
+        <v>38.191249542350683</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>34</v>
@@ -7329,8 +8209,7 @@
         <v>-325</v>
       </c>
       <c r="K5" s="13">
-        <f>-350</f>
-        <v>-350</v>
+        <v>-302</v>
       </c>
       <c r="L5" s="12">
         <f t="shared" ref="L5:U5" si="1">-350</f>
@@ -7376,7 +8255,7 @@
     <row r="6" spans="1:16367" x14ac:dyDescent="0.25">
       <c r="A6" s="27">
         <f>X22</f>
-        <v>-0.31871505124641081</v>
+        <v>-0.15130556572554038</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>35</v>
@@ -7403,48 +8282,47 @@
         <v>-2671</v>
       </c>
       <c r="K6" s="13">
-        <f>J6*1.06</f>
-        <v>-2831.26</v>
+        <v>-2731</v>
       </c>
       <c r="L6" s="12">
         <f>K6*1</f>
-        <v>-2831.26</v>
+        <v>-2731</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" ref="M6:U6" si="2">L6*1</f>
-        <v>-2831.26</v>
+        <v>-2731</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="2"/>
-        <v>-2831.26</v>
+        <v>-2731</v>
       </c>
       <c r="O6" s="12">
         <f t="shared" si="2"/>
-        <v>-2831.26</v>
+        <v>-2731</v>
       </c>
       <c r="P6" s="12">
         <f t="shared" si="2"/>
-        <v>-2831.26</v>
+        <v>-2731</v>
       </c>
       <c r="Q6" s="12">
         <f t="shared" si="2"/>
-        <v>-2831.26</v>
+        <v>-2731</v>
       </c>
       <c r="R6" s="12">
         <f t="shared" si="2"/>
-        <v>-2831.26</v>
+        <v>-2731</v>
       </c>
       <c r="S6" s="12">
         <f t="shared" si="2"/>
-        <v>-2831.26</v>
+        <v>-2731</v>
       </c>
       <c r="T6" s="12">
         <f t="shared" si="2"/>
-        <v>-2831.26</v>
+        <v>-2731</v>
       </c>
       <c r="U6" s="12">
         <f t="shared" si="2"/>
-        <v>-2831.26</v>
+        <v>-2731</v>
       </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
@@ -7491,48 +8369,47 @@
         <v>-93</v>
       </c>
       <c r="K7" s="13">
-        <f>J7*1.02</f>
-        <v>-94.86</v>
+        <v>-90</v>
       </c>
       <c r="L7" s="12">
         <f t="shared" ref="L7:U9" si="3">K7*1</f>
-        <v>-94.86</v>
+        <v>-90</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" si="3"/>
-        <v>-94.86</v>
+        <v>-90</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="3"/>
-        <v>-94.86</v>
+        <v>-90</v>
       </c>
       <c r="O7" s="12">
         <f t="shared" si="3"/>
-        <v>-94.86</v>
+        <v>-90</v>
       </c>
       <c r="P7" s="12">
         <f t="shared" si="3"/>
-        <v>-94.86</v>
+        <v>-90</v>
       </c>
       <c r="Q7" s="12">
         <f t="shared" si="3"/>
-        <v>-94.86</v>
+        <v>-90</v>
       </c>
       <c r="R7" s="12">
         <f t="shared" si="3"/>
-        <v>-94.86</v>
+        <v>-90</v>
       </c>
       <c r="S7" s="12">
         <f t="shared" si="3"/>
-        <v>-94.86</v>
+        <v>-90</v>
       </c>
       <c r="T7" s="12">
         <f t="shared" si="3"/>
-        <v>-94.86</v>
+        <v>-90</v>
       </c>
       <c r="U7" s="12">
         <f t="shared" si="3"/>
-        <v>-94.86</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="8" spans="1:16367" x14ac:dyDescent="0.25">
@@ -7561,48 +8438,47 @@
         <v>-27</v>
       </c>
       <c r="K8" s="13">
-        <f>J8*1.1</f>
-        <v>-29.700000000000003</v>
+        <v>-8</v>
       </c>
       <c r="L8" s="12">
         <f t="shared" si="3"/>
-        <v>-29.700000000000003</v>
+        <v>-8</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="3"/>
-        <v>-29.700000000000003</v>
+        <v>-8</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" si="3"/>
-        <v>-29.700000000000003</v>
+        <v>-8</v>
       </c>
       <c r="O8" s="12">
         <f t="shared" si="3"/>
-        <v>-29.700000000000003</v>
+        <v>-8</v>
       </c>
       <c r="P8" s="12">
         <f t="shared" si="3"/>
-        <v>-29.700000000000003</v>
+        <v>-8</v>
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="3"/>
-        <v>-29.700000000000003</v>
+        <v>-8</v>
       </c>
       <c r="R8" s="12">
         <f t="shared" si="3"/>
-        <v>-29.700000000000003</v>
+        <v>-8</v>
       </c>
       <c r="S8" s="12">
         <f t="shared" si="3"/>
-        <v>-29.700000000000003</v>
+        <v>-8</v>
       </c>
       <c r="T8" s="12">
         <f t="shared" si="3"/>
-        <v>-29.700000000000003</v>
+        <v>-8</v>
       </c>
       <c r="U8" s="12">
         <f t="shared" si="3"/>
-        <v>-29.700000000000003</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="9" spans="1:16367" x14ac:dyDescent="0.25">
@@ -7631,48 +8507,47 @@
         <v>-315</v>
       </c>
       <c r="K9" s="13">
-        <f>J9*1.1</f>
-        <v>-346.5</v>
+        <v>-307</v>
       </c>
       <c r="L9" s="12">
         <f t="shared" si="3"/>
-        <v>-346.5</v>
+        <v>-307</v>
       </c>
       <c r="M9" s="12">
         <f t="shared" si="3"/>
-        <v>-346.5</v>
+        <v>-307</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="3"/>
-        <v>-346.5</v>
+        <v>-307</v>
       </c>
       <c r="O9" s="12">
         <f t="shared" si="3"/>
-        <v>-346.5</v>
+        <v>-307</v>
       </c>
       <c r="P9" s="12">
         <f t="shared" si="3"/>
-        <v>-346.5</v>
+        <v>-307</v>
       </c>
       <c r="Q9" s="12">
         <f t="shared" si="3"/>
-        <v>-346.5</v>
+        <v>-307</v>
       </c>
       <c r="R9" s="12">
         <f t="shared" si="3"/>
-        <v>-346.5</v>
+        <v>-307</v>
       </c>
       <c r="S9" s="12">
         <f t="shared" si="3"/>
-        <v>-346.5</v>
+        <v>-307</v>
       </c>
       <c r="T9" s="12">
         <f t="shared" si="3"/>
-        <v>-346.5</v>
+        <v>-307</v>
       </c>
       <c r="U9" s="12">
         <f t="shared" si="3"/>
-        <v>-346.5</v>
+        <v>-307</v>
       </c>
     </row>
     <row r="10" spans="1:16367" x14ac:dyDescent="0.25">
@@ -7708,48 +8583,48 @@
         <v>490</v>
       </c>
       <c r="K10" s="11">
-        <f t="shared" ref="K10:U10" si="5">SUM(K4:K9)</f>
-        <v>503.93999999999994</v>
+        <f t="shared" ref="K10" si="5">SUM(K4:K9)</f>
+        <v>474</v>
       </c>
       <c r="L10" s="10">
-        <f t="shared" si="5"/>
-        <v>503.93999999999994</v>
+        <f t="shared" ref="L10:U10" si="6">SUM(L4:L9)</f>
+        <v>426</v>
       </c>
       <c r="M10" s="10">
-        <f t="shared" si="5"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="6"/>
+        <v>426</v>
       </c>
       <c r="N10" s="10">
-        <f t="shared" si="5"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="6"/>
+        <v>426</v>
       </c>
       <c r="O10" s="10">
-        <f t="shared" si="5"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="6"/>
+        <v>426</v>
       </c>
       <c r="P10" s="10">
-        <f t="shared" si="5"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="6"/>
+        <v>426</v>
       </c>
       <c r="Q10" s="10">
-        <f t="shared" si="5"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="6"/>
+        <v>426</v>
       </c>
       <c r="R10" s="10">
-        <f t="shared" si="5"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="6"/>
+        <v>426</v>
       </c>
       <c r="S10" s="10">
-        <f t="shared" si="5"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="6"/>
+        <v>426</v>
       </c>
       <c r="T10" s="10">
-        <f t="shared" si="5"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="6"/>
+        <v>426</v>
       </c>
       <c r="U10" s="10">
-        <f t="shared" si="5"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="6"/>
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:16367" x14ac:dyDescent="0.25">
@@ -7778,7 +8653,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="13">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L11" s="12">
         <v>0</v>
@@ -7816,76 +8691,76 @@
         <v>41</v>
       </c>
       <c r="D12" s="12">
-        <f t="shared" ref="D12:K12" si="6">SUM(D10:D11)</f>
+        <f t="shared" ref="D12:J12" si="7">SUM(D10:D11)</f>
         <v>192.44100000000009</v>
       </c>
       <c r="E12" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>228.97199999999975</v>
       </c>
       <c r="F12" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>311.82700000000006</v>
       </c>
       <c r="G12" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>335.1930000000001</v>
       </c>
       <c r="H12" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>400</v>
       </c>
       <c r="I12" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>419</v>
       </c>
       <c r="J12" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>491</v>
       </c>
       <c r="K12" s="13">
-        <f t="shared" si="6"/>
-        <v>503.93999999999994</v>
+        <f t="shared" ref="K12" si="8">SUM(K10:K11)</f>
+        <v>473</v>
       </c>
       <c r="L12" s="12">
-        <f t="shared" ref="L12:U12" si="7">SUM(L10:L11)</f>
-        <v>503.93999999999994</v>
+        <f t="shared" ref="L12:U12" si="9">SUM(L10:L11)</f>
+        <v>426</v>
       </c>
       <c r="M12" s="12">
-        <f t="shared" si="7"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="9"/>
+        <v>426</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" si="7"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="9"/>
+        <v>426</v>
       </c>
       <c r="O12" s="12">
-        <f t="shared" si="7"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="9"/>
+        <v>426</v>
       </c>
       <c r="P12" s="12">
-        <f t="shared" si="7"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="9"/>
+        <v>426</v>
       </c>
       <c r="Q12" s="12">
-        <f t="shared" si="7"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="9"/>
+        <v>426</v>
       </c>
       <c r="R12" s="12">
-        <f t="shared" si="7"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="9"/>
+        <v>426</v>
       </c>
       <c r="S12" s="12">
-        <f t="shared" si="7"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="9"/>
+        <v>426</v>
       </c>
       <c r="T12" s="12">
-        <f t="shared" si="7"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="9"/>
+        <v>426</v>
       </c>
       <c r="U12" s="12">
-        <f t="shared" si="7"/>
-        <v>503.93999999999994</v>
+        <f t="shared" si="9"/>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:16367" x14ac:dyDescent="0.25">
@@ -7914,48 +8789,47 @@
         <v>-108</v>
       </c>
       <c r="K13" s="13">
-        <f>K12*-0.22</f>
-        <v>-110.86679999999998</v>
+        <v>-114</v>
       </c>
       <c r="L13" s="12">
-        <f t="shared" ref="L13:U13" si="8">L12*-0.22</f>
-        <v>-110.86679999999998</v>
+        <f t="shared" ref="L13:U13" si="10">L12*-0.22</f>
+        <v>-93.72</v>
       </c>
       <c r="M13" s="12">
-        <f t="shared" si="8"/>
-        <v>-110.86679999999998</v>
+        <f t="shared" si="10"/>
+        <v>-93.72</v>
       </c>
       <c r="N13" s="12">
-        <f t="shared" si="8"/>
-        <v>-110.86679999999998</v>
+        <f t="shared" si="10"/>
+        <v>-93.72</v>
       </c>
       <c r="O13" s="12">
-        <f t="shared" si="8"/>
-        <v>-110.86679999999998</v>
+        <f t="shared" si="10"/>
+        <v>-93.72</v>
       </c>
       <c r="P13" s="12">
-        <f t="shared" si="8"/>
-        <v>-110.86679999999998</v>
+        <f t="shared" si="10"/>
+        <v>-93.72</v>
       </c>
       <c r="Q13" s="12">
-        <f t="shared" si="8"/>
-        <v>-110.86679999999998</v>
+        <f t="shared" si="10"/>
+        <v>-93.72</v>
       </c>
       <c r="R13" s="12">
-        <f t="shared" si="8"/>
-        <v>-110.86679999999998</v>
+        <f t="shared" si="10"/>
+        <v>-93.72</v>
       </c>
       <c r="S13" s="12">
-        <f t="shared" si="8"/>
-        <v>-110.86679999999998</v>
+        <f t="shared" si="10"/>
+        <v>-93.72</v>
       </c>
       <c r="T13" s="12">
-        <f t="shared" si="8"/>
-        <v>-110.86679999999998</v>
+        <f t="shared" si="10"/>
+        <v>-93.72</v>
       </c>
       <c r="U13" s="12">
-        <f t="shared" si="8"/>
-        <v>-110.86679999999998</v>
+        <f t="shared" si="10"/>
+        <v>-93.72</v>
       </c>
     </row>
     <row r="14" spans="1:16367" x14ac:dyDescent="0.25">
@@ -7963,488 +8837,488 @@
         <v>43</v>
       </c>
       <c r="D14" s="10">
-        <f t="shared" ref="D14:J14" si="9">SUM(D12:D13)</f>
+        <f t="shared" ref="D14:J14" si="11">SUM(D12:D13)</f>
         <v>151.44100000000009</v>
       </c>
       <c r="E14" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>180.97199999999975</v>
       </c>
       <c r="F14" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>241.32700000000006</v>
       </c>
       <c r="G14" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>265.93700000000013</v>
       </c>
       <c r="H14" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>315</v>
       </c>
       <c r="I14" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>326</v>
       </c>
       <c r="J14" s="10">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>383</v>
       </c>
       <c r="K14" s="11">
-        <f t="shared" ref="K14:U14" si="10">SUM(K12:K13)</f>
-        <v>393.07319999999993</v>
+        <f t="shared" ref="K14" si="12">SUM(K12:K13)</f>
+        <v>359</v>
       </c>
       <c r="L14" s="10">
-        <f t="shared" si="10"/>
-        <v>393.07319999999993</v>
+        <f t="shared" ref="L14:U14" si="13">SUM(L12:L13)</f>
+        <v>332.28</v>
       </c>
       <c r="M14" s="10">
-        <f t="shared" si="10"/>
-        <v>393.07319999999993</v>
+        <f t="shared" si="13"/>
+        <v>332.28</v>
       </c>
       <c r="N14" s="10">
-        <f t="shared" si="10"/>
-        <v>393.07319999999993</v>
+        <f t="shared" si="13"/>
+        <v>332.28</v>
       </c>
       <c r="O14" s="10">
-        <f t="shared" si="10"/>
-        <v>393.07319999999993</v>
+        <f t="shared" si="13"/>
+        <v>332.28</v>
       </c>
       <c r="P14" s="10">
-        <f t="shared" si="10"/>
-        <v>393.07319999999993</v>
+        <f t="shared" si="13"/>
+        <v>332.28</v>
       </c>
       <c r="Q14" s="10">
-        <f t="shared" si="10"/>
-        <v>393.07319999999993</v>
+        <f t="shared" si="13"/>
+        <v>332.28</v>
       </c>
       <c r="R14" s="10">
-        <f t="shared" si="10"/>
-        <v>393.07319999999993</v>
+        <f t="shared" si="13"/>
+        <v>332.28</v>
       </c>
       <c r="S14" s="10">
-        <f t="shared" si="10"/>
-        <v>393.07319999999993</v>
+        <f t="shared" si="13"/>
+        <v>332.28</v>
       </c>
       <c r="T14" s="10">
-        <f t="shared" si="10"/>
-        <v>393.07319999999993</v>
+        <f t="shared" si="13"/>
+        <v>332.28</v>
       </c>
       <c r="U14" s="10">
-        <f t="shared" si="10"/>
-        <v>393.07319999999993</v>
+        <f t="shared" si="13"/>
+        <v>332.28</v>
       </c>
       <c r="V14" s="10">
         <f>U14*(1+$X$18)</f>
-        <v>389.14246799999995</v>
+        <v>328.95719999999994</v>
       </c>
       <c r="W14" s="10">
-        <f t="shared" ref="W14:CH14" si="11">V14*(1+$X$18)</f>
-        <v>385.25104331999995</v>
+        <f t="shared" ref="W14:CH14" si="14">V14*(1+$X$18)</f>
+        <v>325.66762799999992</v>
       </c>
       <c r="X14" s="10">
-        <f t="shared" si="11"/>
-        <v>381.39853288679996</v>
+        <f t="shared" si="14"/>
+        <v>322.4109517199999</v>
       </c>
       <c r="Y14" s="10">
-        <f t="shared" si="11"/>
-        <v>377.58454755793196</v>
+        <f t="shared" si="14"/>
+        <v>319.18684220279988</v>
       </c>
       <c r="Z14" s="10">
-        <f t="shared" si="11"/>
-        <v>373.80870208235262</v>
+        <f t="shared" si="14"/>
+        <v>315.99497378077189</v>
       </c>
       <c r="AA14" s="10">
-        <f t="shared" si="11"/>
-        <v>370.07061506152911</v>
+        <f t="shared" si="14"/>
+        <v>312.83502404296416</v>
       </c>
       <c r="AB14" s="10">
-        <f t="shared" si="11"/>
-        <v>366.36990891091381</v>
+        <f t="shared" si="14"/>
+        <v>309.70667380253451</v>
       </c>
       <c r="AC14" s="10">
-        <f t="shared" si="11"/>
-        <v>362.70620982180469</v>
+        <f t="shared" si="14"/>
+        <v>306.60960706450913</v>
       </c>
       <c r="AD14" s="10">
-        <f t="shared" si="11"/>
-        <v>359.07914772358663</v>
+        <f t="shared" si="14"/>
+        <v>303.54351099386406</v>
       </c>
       <c r="AE14" s="10">
-        <f t="shared" si="11"/>
-        <v>355.48835624635075</v>
+        <f t="shared" si="14"/>
+        <v>300.50807588392541</v>
       </c>
       <c r="AF14" s="10">
-        <f t="shared" si="11"/>
-        <v>351.93347268388726</v>
+        <f t="shared" si="14"/>
+        <v>297.50299512508616</v>
       </c>
       <c r="AG14" s="10">
-        <f t="shared" si="11"/>
-        <v>348.41413795704841</v>
+        <f t="shared" si="14"/>
+        <v>294.5279651738353</v>
       </c>
       <c r="AH14" s="10">
-        <f t="shared" si="11"/>
-        <v>344.92999657747794</v>
+        <f t="shared" si="14"/>
+        <v>291.58268552209694</v>
       </c>
       <c r="AI14" s="10">
-        <f t="shared" si="11"/>
-        <v>341.48069661170314</v>
+        <f t="shared" si="14"/>
+        <v>288.66685866687595</v>
       </c>
       <c r="AJ14" s="10">
-        <f t="shared" si="11"/>
-        <v>338.06588964558608</v>
+        <f t="shared" si="14"/>
+        <v>285.78019008020721</v>
       </c>
       <c r="AK14" s="10">
-        <f t="shared" si="11"/>
-        <v>334.6852307491302</v>
+        <f t="shared" si="14"/>
+        <v>282.92238817940512</v>
       </c>
       <c r="AL14" s="10">
-        <f t="shared" si="11"/>
-        <v>331.33837844163889</v>
+        <f t="shared" si="14"/>
+        <v>280.09316429761105</v>
       </c>
       <c r="AM14" s="10">
-        <f t="shared" si="11"/>
-        <v>328.02499465722252</v>
+        <f t="shared" si="14"/>
+        <v>277.29223265463492</v>
       </c>
       <c r="AN14" s="10">
-        <f t="shared" si="11"/>
-        <v>324.74474471065031</v>
+        <f t="shared" si="14"/>
+        <v>274.51931032808858</v>
       </c>
       <c r="AO14" s="10">
-        <f t="shared" si="11"/>
-        <v>321.49729726354383</v>
+        <f t="shared" si="14"/>
+        <v>271.7741172248077</v>
       </c>
       <c r="AP14" s="10">
-        <f t="shared" si="11"/>
-        <v>318.28232429090838</v>
+        <f t="shared" si="14"/>
+        <v>269.05637605255964</v>
       </c>
       <c r="AQ14" s="10">
-        <f t="shared" si="11"/>
-        <v>315.0995010479993</v>
+        <f t="shared" si="14"/>
+        <v>266.36581229203404</v>
       </c>
       <c r="AR14" s="10">
-        <f t="shared" si="11"/>
-        <v>311.94850603751928</v>
+        <f t="shared" si="14"/>
+        <v>263.70215416911367</v>
       </c>
       <c r="AS14" s="10">
-        <f t="shared" si="11"/>
-        <v>308.82902097714407</v>
+        <f t="shared" si="14"/>
+        <v>261.06513262742254</v>
       </c>
       <c r="AT14" s="10">
-        <f t="shared" si="11"/>
-        <v>305.74073076737261</v>
+        <f t="shared" si="14"/>
+        <v>258.45448130114829</v>
       </c>
       <c r="AU14" s="10">
-        <f t="shared" si="11"/>
-        <v>302.6833234596989</v>
+        <f t="shared" si="14"/>
+        <v>255.8699364881368</v>
       </c>
       <c r="AV14" s="10">
-        <f t="shared" si="11"/>
-        <v>299.65649022510189</v>
+        <f t="shared" si="14"/>
+        <v>253.31123712325544</v>
       </c>
       <c r="AW14" s="10">
-        <f t="shared" si="11"/>
-        <v>296.65992532285088</v>
+        <f t="shared" si="14"/>
+        <v>250.77812475202288</v>
       </c>
       <c r="AX14" s="10">
-        <f t="shared" si="11"/>
-        <v>293.69332606962234</v>
+        <f t="shared" si="14"/>
+        <v>248.27034350450265</v>
       </c>
       <c r="AY14" s="10">
-        <f t="shared" si="11"/>
-        <v>290.75639280892614</v>
+        <f t="shared" si="14"/>
+        <v>245.78764006945761</v>
       </c>
       <c r="AZ14" s="10">
-        <f t="shared" si="11"/>
-        <v>287.84882888083689</v>
+        <f t="shared" si="14"/>
+        <v>243.32976366876304</v>
       </c>
       <c r="BA14" s="10">
-        <f t="shared" si="11"/>
-        <v>284.97034059202849</v>
+        <f t="shared" si="14"/>
+        <v>240.89646603207541</v>
       </c>
       <c r="BB14" s="10">
-        <f t="shared" si="11"/>
-        <v>282.12063718610818</v>
+        <f t="shared" si="14"/>
+        <v>238.48750137175466</v>
       </c>
       <c r="BC14" s="10">
-        <f t="shared" si="11"/>
-        <v>279.2994308142471</v>
+        <f t="shared" si="14"/>
+        <v>236.1026263580371</v>
       </c>
       <c r="BD14" s="10">
-        <f t="shared" si="11"/>
-        <v>276.50643650610465</v>
+        <f t="shared" si="14"/>
+        <v>233.74160009445671</v>
       </c>
       <c r="BE14" s="10">
-        <f t="shared" si="11"/>
-        <v>273.7413721410436</v>
+        <f t="shared" si="14"/>
+        <v>231.40418409351216</v>
       </c>
       <c r="BF14" s="10">
-        <f t="shared" si="11"/>
-        <v>271.00395841963314</v>
+        <f t="shared" si="14"/>
+        <v>229.09014225257704</v>
       </c>
       <c r="BG14" s="10">
-        <f t="shared" si="11"/>
-        <v>268.29391883543678</v>
+        <f t="shared" si="14"/>
+        <v>226.79924083005127</v>
       </c>
       <c r="BH14" s="10">
-        <f t="shared" si="11"/>
-        <v>265.61097964708239</v>
+        <f t="shared" si="14"/>
+        <v>224.53124842175075</v>
       </c>
       <c r="BI14" s="10">
-        <f t="shared" si="11"/>
-        <v>262.95486985061154</v>
+        <f t="shared" si="14"/>
+        <v>222.28593593753322</v>
       </c>
       <c r="BJ14" s="10">
-        <f t="shared" si="11"/>
-        <v>260.3253211521054</v>
+        <f t="shared" si="14"/>
+        <v>220.0630765781579</v>
       </c>
       <c r="BK14" s="10">
-        <f t="shared" si="11"/>
-        <v>257.72206794058434</v>
+        <f t="shared" si="14"/>
+        <v>217.86244581237634</v>
       </c>
       <c r="BL14" s="10">
-        <f t="shared" si="11"/>
-        <v>255.14484726117848</v>
+        <f t="shared" si="14"/>
+        <v>215.68382135425256</v>
       </c>
       <c r="BM14" s="10">
-        <f t="shared" si="11"/>
-        <v>252.5933987885667</v>
+        <f t="shared" si="14"/>
+        <v>213.52698314071003</v>
       </c>
       <c r="BN14" s="10">
-        <f t="shared" si="11"/>
-        <v>250.06746480068102</v>
+        <f t="shared" si="14"/>
+        <v>211.39171330930293</v>
       </c>
       <c r="BO14" s="10">
-        <f t="shared" si="11"/>
-        <v>247.5667901526742</v>
+        <f t="shared" si="14"/>
+        <v>209.2777961762099</v>
       </c>
       <c r="BP14" s="10">
-        <f t="shared" si="11"/>
-        <v>245.09112225114745</v>
+        <f t="shared" si="14"/>
+        <v>207.18501821444781</v>
       </c>
       <c r="BQ14" s="10">
-        <f t="shared" si="11"/>
-        <v>242.64021102863597</v>
+        <f t="shared" si="14"/>
+        <v>205.11316803230332</v>
       </c>
       <c r="BR14" s="10">
-        <f t="shared" si="11"/>
-        <v>240.2138089183496</v>
+        <f t="shared" si="14"/>
+        <v>203.06203635198028</v>
       </c>
       <c r="BS14" s="10">
-        <f t="shared" si="11"/>
-        <v>237.8116708291661</v>
+        <f t="shared" si="14"/>
+        <v>201.03141598846048</v>
       </c>
       <c r="BT14" s="10">
-        <f t="shared" si="11"/>
-        <v>235.43355412087445</v>
+        <f t="shared" si="14"/>
+        <v>199.02110182857587</v>
       </c>
       <c r="BU14" s="10">
-        <f t="shared" si="11"/>
-        <v>233.07921857966571</v>
+        <f t="shared" si="14"/>
+        <v>197.03089081029012</v>
       </c>
       <c r="BV14" s="10">
-        <f t="shared" si="11"/>
-        <v>230.74842639386904</v>
+        <f t="shared" si="14"/>
+        <v>195.06058190218721</v>
       </c>
       <c r="BW14" s="10">
-        <f t="shared" si="11"/>
-        <v>228.44094212993033</v>
+        <f t="shared" si="14"/>
+        <v>193.10997608316532</v>
       </c>
       <c r="BX14" s="10">
-        <f t="shared" si="11"/>
-        <v>226.15653270863103</v>
+        <f t="shared" si="14"/>
+        <v>191.17887632233368</v>
       </c>
       <c r="BY14" s="10">
-        <f t="shared" si="11"/>
-        <v>223.89496738154472</v>
+        <f t="shared" si="14"/>
+        <v>189.26708755911034</v>
       </c>
       <c r="BZ14" s="10">
-        <f t="shared" si="11"/>
-        <v>221.65601770772926</v>
+        <f t="shared" si="14"/>
+        <v>187.37441668351923</v>
       </c>
       <c r="CA14" s="10">
-        <f t="shared" si="11"/>
-        <v>219.43945753065196</v>
+        <f t="shared" si="14"/>
+        <v>185.50067251668403</v>
       </c>
       <c r="CB14" s="10">
-        <f t="shared" si="11"/>
-        <v>217.24506295534545</v>
+        <f t="shared" si="14"/>
+        <v>183.64566579151719</v>
       </c>
       <c r="CC14" s="10">
-        <f t="shared" si="11"/>
-        <v>215.07261232579199</v>
+        <f t="shared" si="14"/>
+        <v>181.80920913360202</v>
       </c>
       <c r="CD14" s="10">
-        <f t="shared" si="11"/>
-        <v>212.92188620253407</v>
+        <f t="shared" si="14"/>
+        <v>179.99111704226601</v>
       </c>
       <c r="CE14" s="10">
-        <f t="shared" si="11"/>
-        <v>210.79266734050873</v>
+        <f t="shared" si="14"/>
+        <v>178.19120587184335</v>
       </c>
       <c r="CF14" s="10">
-        <f t="shared" si="11"/>
-        <v>208.68474066710363</v>
+        <f t="shared" si="14"/>
+        <v>176.40929381312492</v>
       </c>
       <c r="CG14" s="10">
-        <f t="shared" si="11"/>
-        <v>206.59789326043258</v>
+        <f t="shared" si="14"/>
+        <v>174.64520087499366</v>
       </c>
       <c r="CH14" s="10">
-        <f t="shared" si="11"/>
-        <v>204.53191432782825</v>
+        <f t="shared" si="14"/>
+        <v>172.89874886624372</v>
       </c>
       <c r="CI14" s="10">
-        <f t="shared" ref="CI14:DT14" si="12">CH14*(1+$X$18)</f>
-        <v>202.48659518454997</v>
+        <f t="shared" ref="CI14:DT14" si="15">CH14*(1+$X$18)</f>
+        <v>171.1697613775813</v>
       </c>
       <c r="CJ14" s="10">
-        <f t="shared" si="12"/>
-        <v>200.46172923270447</v>
+        <f t="shared" si="15"/>
+        <v>169.45806376380548</v>
       </c>
       <c r="CK14" s="10">
-        <f t="shared" si="12"/>
-        <v>198.45711194037742</v>
+        <f t="shared" si="15"/>
+        <v>167.76348312616742</v>
       </c>
       <c r="CL14" s="10">
-        <f t="shared" si="12"/>
-        <v>196.47254082097365</v>
+        <f t="shared" si="15"/>
+        <v>166.08584829490573</v>
       </c>
       <c r="CM14" s="10">
-        <f t="shared" si="12"/>
-        <v>194.5078154127639</v>
+        <f t="shared" si="15"/>
+        <v>164.42498981195666</v>
       </c>
       <c r="CN14" s="10">
-        <f t="shared" si="12"/>
-        <v>192.56273725863628</v>
+        <f t="shared" si="15"/>
+        <v>162.7807399138371</v>
       </c>
       <c r="CO14" s="10">
-        <f t="shared" si="12"/>
-        <v>190.6371098860499</v>
+        <f t="shared" si="15"/>
+        <v>161.15293251469873</v>
       </c>
       <c r="CP14" s="10">
-        <f t="shared" si="12"/>
-        <v>188.73073878718941</v>
+        <f t="shared" si="15"/>
+        <v>159.54140318955174</v>
       </c>
       <c r="CQ14" s="10">
-        <f t="shared" si="12"/>
-        <v>186.84343139931752</v>
+        <f t="shared" si="15"/>
+        <v>157.94598915765621</v>
       </c>
       <c r="CR14" s="10">
-        <f t="shared" si="12"/>
-        <v>184.97499708532436</v>
+        <f t="shared" si="15"/>
+        <v>156.36652926607965</v>
       </c>
       <c r="CS14" s="10">
-        <f t="shared" si="12"/>
-        <v>183.12524711447111</v>
+        <f t="shared" si="15"/>
+        <v>154.80286397341885</v>
       </c>
       <c r="CT14" s="10">
-        <f t="shared" si="12"/>
-        <v>181.29399464332639</v>
+        <f t="shared" si="15"/>
+        <v>153.25483533368467</v>
       </c>
       <c r="CU14" s="10">
-        <f t="shared" si="12"/>
-        <v>179.48105469689312</v>
+        <f t="shared" si="15"/>
+        <v>151.72228698034783</v>
       </c>
       <c r="CV14" s="10">
-        <f t="shared" si="12"/>
-        <v>177.68624414992419</v>
+        <f t="shared" si="15"/>
+        <v>150.20506411054436</v>
       </c>
       <c r="CW14" s="10">
-        <f t="shared" si="12"/>
-        <v>175.90938170842495</v>
+        <f t="shared" si="15"/>
+        <v>148.7030134694389</v>
       </c>
       <c r="CX14" s="10">
-        <f t="shared" si="12"/>
-        <v>174.1502878913407</v>
+        <f t="shared" si="15"/>
+        <v>147.21598333474452</v>
       </c>
       <c r="CY14" s="10">
-        <f t="shared" si="12"/>
-        <v>172.40878501242727</v>
+        <f t="shared" si="15"/>
+        <v>145.74382350139709</v>
       </c>
       <c r="CZ14" s="10">
-        <f t="shared" si="12"/>
-        <v>170.684697162303</v>
+        <f t="shared" si="15"/>
+        <v>144.28638526638312</v>
       </c>
       <c r="DA14" s="10">
-        <f t="shared" si="12"/>
-        <v>168.97785019067996</v>
+        <f t="shared" si="15"/>
+        <v>142.84352141371929</v>
       </c>
       <c r="DB14" s="10">
-        <f t="shared" si="12"/>
-        <v>167.28807168877316</v>
+        <f t="shared" si="15"/>
+        <v>141.41508619958211</v>
       </c>
       <c r="DC14" s="10">
-        <f t="shared" si="12"/>
-        <v>165.61519097188543</v>
+        <f t="shared" si="15"/>
+        <v>140.00093533758627</v>
       </c>
       <c r="DD14" s="10">
-        <f t="shared" si="12"/>
-        <v>163.95903906216657</v>
+        <f t="shared" si="15"/>
+        <v>138.60092598421042</v>
       </c>
       <c r="DE14" s="10">
-        <f t="shared" si="12"/>
-        <v>162.3194486715449</v>
+        <f t="shared" si="15"/>
+        <v>137.21491672436832</v>
       </c>
       <c r="DF14" s="10">
-        <f t="shared" si="12"/>
-        <v>160.69625418482946</v>
+        <f t="shared" si="15"/>
+        <v>135.84276755712463</v>
       </c>
       <c r="DG14" s="10">
-        <f t="shared" si="12"/>
-        <v>159.08929164298115</v>
+        <f t="shared" si="15"/>
+        <v>134.48433988155338</v>
       </c>
       <c r="DH14" s="10">
-        <f t="shared" si="12"/>
-        <v>157.49839872655133</v>
+        <f t="shared" si="15"/>
+        <v>133.13949648273785</v>
       </c>
       <c r="DI14" s="10">
-        <f t="shared" si="12"/>
-        <v>155.92341473928582</v>
+        <f t="shared" si="15"/>
+        <v>131.80810151791047</v>
       </c>
       <c r="DJ14" s="10">
-        <f t="shared" si="12"/>
-        <v>154.36418059189296</v>
+        <f t="shared" si="15"/>
+        <v>130.49002050273137</v>
       </c>
       <c r="DK14" s="10">
-        <f t="shared" si="12"/>
-        <v>152.82053878597404</v>
+        <f t="shared" si="15"/>
+        <v>129.18512029770406</v>
       </c>
       <c r="DL14" s="10">
-        <f t="shared" si="12"/>
-        <v>151.29233339811429</v>
+        <f t="shared" si="15"/>
+        <v>127.89326909472702</v>
       </c>
       <c r="DM14" s="10">
-        <f t="shared" si="12"/>
-        <v>149.77941006413315</v>
+        <f t="shared" si="15"/>
+        <v>126.61433640377975</v>
       </c>
       <c r="DN14" s="10">
-        <f t="shared" si="12"/>
-        <v>148.28161596349182</v>
+        <f t="shared" si="15"/>
+        <v>125.34819303974194</v>
       </c>
       <c r="DO14" s="10">
-        <f t="shared" si="12"/>
-        <v>146.79879980385689</v>
+        <f t="shared" si="15"/>
+        <v>124.09471110934452</v>
       </c>
       <c r="DP14" s="10">
-        <f t="shared" si="12"/>
-        <v>145.33081180581831</v>
+        <f t="shared" si="15"/>
+        <v>122.85376399825107</v>
       </c>
       <c r="DQ14" s="10">
-        <f t="shared" si="12"/>
-        <v>143.87750368776014</v>
+        <f t="shared" si="15"/>
+        <v>121.62522635826856</v>
       </c>
       <c r="DR14" s="10">
-        <f t="shared" si="12"/>
-        <v>142.43872865088252</v>
+        <f t="shared" si="15"/>
+        <v>120.40897409468587</v>
       </c>
       <c r="DS14" s="10">
-        <f t="shared" si="12"/>
-        <v>141.01434136437371</v>
+        <f t="shared" si="15"/>
+        <v>119.20488435373902</v>
       </c>
       <c r="DT14" s="10">
-        <f t="shared" si="12"/>
-        <v>139.60419795072997</v>
+        <f t="shared" si="15"/>
+        <v>118.01283551020163</v>
       </c>
       <c r="DU14" s="4"/>
       <c r="DV14" s="4"/>
@@ -24754,76 +25628,76 @@
         <v>46</v>
       </c>
       <c r="D16" s="15">
-        <f t="shared" ref="D16:K16" si="13">D14/D15</f>
+        <f t="shared" ref="D16:K16" si="16">D14/D15</f>
         <v>14.847156862745107</v>
       </c>
       <c r="E16" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>17.742352941176449</v>
       </c>
       <c r="F16" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2.3249086612060008</v>
       </c>
       <c r="G16" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2.561997765004083</v>
       </c>
       <c r="H16" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>3.0346634577974703</v>
       </c>
       <c r="I16" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>3.140635832514207</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>3.6897654105918445</v>
       </c>
       <c r="K16" s="14">
-        <f t="shared" si="13"/>
-        <v>3.7868091310460836</v>
+        <f t="shared" si="16"/>
+        <v>3.4585529566644184</v>
       </c>
       <c r="L16" s="15">
-        <f t="shared" ref="L16:U16" si="14">L14/L15</f>
-        <v>3.7868091310460836</v>
+        <f t="shared" ref="L16:U16" si="17">L14/L15</f>
+        <v>3.2011364246252167</v>
       </c>
       <c r="M16" s="15">
-        <f t="shared" si="14"/>
-        <v>3.7868091310460836</v>
+        <f t="shared" si="17"/>
+        <v>3.2011364246252167</v>
       </c>
       <c r="N16" s="15">
-        <f t="shared" si="14"/>
-        <v>3.7868091310460836</v>
+        <f t="shared" si="17"/>
+        <v>3.2011364246252167</v>
       </c>
       <c r="O16" s="15">
-        <f t="shared" si="14"/>
-        <v>3.7868091310460836</v>
+        <f t="shared" si="17"/>
+        <v>3.2011364246252167</v>
       </c>
       <c r="P16" s="15">
-        <f t="shared" si="14"/>
-        <v>3.7868091310460836</v>
+        <f t="shared" si="17"/>
+        <v>3.2011364246252167</v>
       </c>
       <c r="Q16" s="15">
-        <f t="shared" si="14"/>
-        <v>3.7868091310460836</v>
+        <f t="shared" si="17"/>
+        <v>3.2011364246252167</v>
       </c>
       <c r="R16" s="15">
-        <f t="shared" si="14"/>
-        <v>3.7868091310460836</v>
+        <f t="shared" si="17"/>
+        <v>3.2011364246252167</v>
       </c>
       <c r="S16" s="15">
-        <f t="shared" si="14"/>
-        <v>3.7868091310460836</v>
+        <f t="shared" si="17"/>
+        <v>3.2011364246252167</v>
       </c>
       <c r="T16" s="15">
-        <f t="shared" si="14"/>
-        <v>3.7868091310460836</v>
+        <f t="shared" si="17"/>
+        <v>3.2011364246252167</v>
       </c>
       <c r="U16" s="15">
-        <f t="shared" si="14"/>
-        <v>3.7868091310460836</v>
+        <f t="shared" si="17"/>
+        <v>3.2011364246252167</v>
       </c>
     </row>
     <row r="17" spans="3:24" x14ac:dyDescent="0.25">
@@ -24841,19 +25715,19 @@
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="17">
-        <f t="shared" ref="E18:H18" si="15">(E4-D4)/D4</f>
+        <f t="shared" ref="E18:H18" si="18">(E4-D4)/D4</f>
         <v>0.15448491940536443</v>
       </c>
       <c r="F18" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.12656848030018764</v>
       </c>
       <c r="G18" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.12205455475043339</v>
       </c>
       <c r="H18" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.15102040816326531</v>
       </c>
       <c r="I18" s="17">
@@ -24865,11 +25739,11 @@
         <v>0.11202495745887692</v>
       </c>
       <c r="K18" s="16">
-        <f t="shared" ref="K18:U18" si="16">(K4-J4)/J4</f>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" ref="K18" si="19">(K4-J4)/J4</f>
+        <v>-2.2953328232593728E-3</v>
       </c>
       <c r="L18" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="L18:U18" si="20">(L4-K4)/K4</f>
         <v>0</v>
       </c>
       <c r="M18" s="17">
@@ -24877,35 +25751,35 @@
         <v>0</v>
       </c>
       <c r="N18" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="O18" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="P18" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q18" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R18" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S18" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="T18" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="U18" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="W18" s="1" t="s">
@@ -24920,23 +25794,23 @@
         <v>100</v>
       </c>
       <c r="D19" s="19">
-        <f t="shared" ref="D19:H19" si="17">D10/D4</f>
+        <f t="shared" ref="D19:H19" si="21">D10/D4</f>
         <v>0.10420742606720818</v>
       </c>
       <c r="E19" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.10918011257035636</v>
       </c>
       <c r="F19" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.13099393632558987</v>
       </c>
       <c r="G19" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.12623116883116886</v>
       </c>
       <c r="H19" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0.12927143778207609</v>
       </c>
       <c r="I19" s="19">
@@ -24944,59 +25818,59 @@
         <v>0.11571185479296653</v>
       </c>
       <c r="J19" s="19">
-        <f t="shared" ref="J19:U19" si="18">J10/J4</f>
+        <f t="shared" ref="J19:U19" si="22">J10/J4</f>
         <v>0.12496812037745474</v>
       </c>
       <c r="K19" s="20">
         <f>K10/K4</f>
-        <v>0.1212484300789652</v>
+        <v>0.12116564417177914</v>
       </c>
       <c r="L19" s="19">
-        <f t="shared" si="18"/>
-        <v>0.1212484300789652</v>
+        <f t="shared" si="22"/>
+        <v>0.10889570552147239</v>
       </c>
       <c r="M19" s="19">
-        <f t="shared" si="18"/>
-        <v>0.1212484300789652</v>
+        <f t="shared" si="22"/>
+        <v>0.10889570552147239</v>
       </c>
       <c r="N19" s="19">
-        <f t="shared" si="18"/>
-        <v>0.1212484300789652</v>
+        <f t="shared" si="22"/>
+        <v>0.10889570552147239</v>
       </c>
       <c r="O19" s="19">
-        <f t="shared" si="18"/>
-        <v>0.1212484300789652</v>
+        <f t="shared" si="22"/>
+        <v>0.10889570552147239</v>
       </c>
       <c r="P19" s="19">
-        <f t="shared" si="18"/>
-        <v>0.1212484300789652</v>
+        <f t="shared" si="22"/>
+        <v>0.10889570552147239</v>
       </c>
       <c r="Q19" s="19">
-        <f t="shared" si="18"/>
-        <v>0.1212484300789652</v>
+        <f t="shared" si="22"/>
+        <v>0.10889570552147239</v>
       </c>
       <c r="R19" s="19">
-        <f t="shared" si="18"/>
-        <v>0.1212484300789652</v>
+        <f t="shared" si="22"/>
+        <v>0.10889570552147239</v>
       </c>
       <c r="S19" s="19">
-        <f t="shared" si="18"/>
-        <v>0.1212484300789652</v>
+        <f t="shared" si="22"/>
+        <v>0.10889570552147239</v>
       </c>
       <c r="T19" s="19">
-        <f t="shared" si="18"/>
-        <v>0.1212484300789652</v>
+        <f t="shared" si="22"/>
+        <v>0.10889570552147239</v>
       </c>
       <c r="U19" s="19">
-        <f t="shared" si="18"/>
-        <v>0.1212484300789652</v>
+        <f t="shared" si="22"/>
+        <v>0.10889570552147239</v>
       </c>
       <c r="W19" s="23" t="s">
         <v>88</v>
       </c>
       <c r="X19" s="24">
         <f>NPV(X17,K14:DT14)</f>
-        <v>4660.3037883369907</v>
+        <v>3964.2760303219588</v>
       </c>
     </row>
     <row r="20" spans="3:24" x14ac:dyDescent="0.25">
@@ -25006,7 +25880,7 @@
       <c r="H20" s="19"/>
       <c r="I20" s="19"/>
       <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
+      <c r="K20" s="20"/>
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" s="19"/>
@@ -25044,7 +25918,7 @@
       </c>
       <c r="X21" s="26">
         <f>X19/X20</f>
-        <v>44.89667812286153</v>
+        <v>38.191249542350683</v>
       </c>
     </row>
     <row r="22" spans="3:24" x14ac:dyDescent="0.25">
@@ -25053,7 +25927,7 @@
       </c>
       <c r="X22" s="27">
         <f>(X21-Modell!B4)/Modell!B4</f>
-        <v>-0.31871505124641081</v>
+        <v>-0.15130556572554038</v>
       </c>
     </row>
   </sheetData>

--- a/Bouvet modell.xlsx
+++ b/Bouvet modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB88CF3-B90D-194E-9711-F60A1001EE10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4F6363-F85C-4C43-8C45-BD67AF6F94F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25440" yWindow="500" windowWidth="25760" windowHeight="26740" activeTab="1" xr2:uid="{880FDD81-14BC-AE47-8673-E11DDB2293DC}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17240" activeTab="1" xr2:uid="{880FDD81-14BC-AE47-8673-E11DDB2293DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -1134,7 +1134,9 @@
     <col min="1" max="1" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="5"/>
     <col min="3" max="3" width="38.1640625" style="1" customWidth="1"/>
-    <col min="4" max="36" width="10.83203125" style="1"/>
+    <col min="4" max="32" width="10.83203125" style="1"/>
+    <col min="33" max="33" width="10.83203125" style="5"/>
+    <col min="34" max="36" width="10.83203125" style="1"/>
     <col min="37" max="41" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="11.5" style="1" bestFit="1" customWidth="1"/>
@@ -1238,7 +1240,7 @@
       <c r="AF3" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="AG3" s="21" t="s">
+      <c r="AG3" s="6" t="s">
         <v>23</v>
       </c>
       <c r="AH3" s="21" t="s">
@@ -1274,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="6">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>44</v>
@@ -1358,45 +1360,45 @@
       <c r="AF4" s="10">
         <v>3912</v>
       </c>
-      <c r="AG4" s="10">
-        <f>AF4*1.01</f>
-        <v>3951.12</v>
+      <c r="AG4" s="11">
+        <f>AF4*1</f>
+        <v>3912</v>
       </c>
       <c r="AH4" s="10">
         <f t="shared" ref="AH4:AP4" si="0">AG4*1.05</f>
-        <v>4148.6760000000004</v>
+        <v>4107.6000000000004</v>
       </c>
       <c r="AI4" s="10">
         <f t="shared" si="0"/>
-        <v>4356.1098000000002</v>
+        <v>4312.9800000000005</v>
       </c>
       <c r="AJ4" s="10">
         <f t="shared" si="0"/>
-        <v>4573.9152900000008</v>
+        <v>4528.6290000000008</v>
       </c>
       <c r="AK4" s="10">
         <f t="shared" si="0"/>
-        <v>4802.611054500001</v>
+        <v>4755.0604500000009</v>
       </c>
       <c r="AL4" s="10">
         <f t="shared" si="0"/>
-        <v>5042.7416072250016</v>
+        <v>4992.8134725000009</v>
       </c>
       <c r="AM4" s="10">
         <f t="shared" si="0"/>
-        <v>5294.8786875862515</v>
+        <v>5242.454146125001</v>
       </c>
       <c r="AN4" s="10">
         <f t="shared" si="0"/>
-        <v>5559.6226219655646</v>
+        <v>5504.576853431251</v>
       </c>
       <c r="AO4" s="10">
         <f t="shared" si="0"/>
-        <v>5837.6037530638432</v>
+        <v>5779.8056961028142</v>
       </c>
       <c r="AP4" s="10">
         <f t="shared" si="0"/>
-        <v>6129.4839407170357</v>
+        <v>6068.7959809079548</v>
       </c>
       <c r="AQ4" s="10"/>
       <c r="AR4" s="10"/>
@@ -1506,7 +1508,7 @@
       <c r="AF5" s="12">
         <v>-302</v>
       </c>
-      <c r="AG5" s="12">
+      <c r="AG5" s="13">
         <f t="shared" ref="AG5:AP5" si="1">-350</f>
         <v>-350</v>
       </c>
@@ -1553,7 +1555,7 @@
       </c>
       <c r="B6" s="7">
         <f>B4*B5</f>
-        <v>4611.6902250000003</v>
+        <v>4406.7262149999997</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>35</v>
@@ -1637,45 +1639,45 @@
       <c r="AF6" s="12">
         <v>-2731</v>
       </c>
-      <c r="AG6" s="12">
-        <f>AF6*1.01</f>
-        <v>-2758.31</v>
+      <c r="AG6" s="13">
+        <f>AF6*1.005</f>
+        <v>-2744.6549999999997</v>
       </c>
       <c r="AH6" s="12">
         <f t="shared" ref="AH6:AP6" si="2">AG6*1.05</f>
-        <v>-2896.2255</v>
+        <v>-2881.8877499999999</v>
       </c>
       <c r="AI6" s="12">
         <f>AH6*1.06</f>
-        <v>-3069.9990299999999</v>
+        <v>-3054.801015</v>
       </c>
       <c r="AJ6" s="12">
         <f t="shared" si="2"/>
-        <v>-3223.4989814999999</v>
+        <v>-3207.5410657500001</v>
       </c>
       <c r="AK6" s="12">
         <f t="shared" si="2"/>
-        <v>-3384.6739305750002</v>
+        <v>-3367.9181190375002</v>
       </c>
       <c r="AL6" s="12">
         <f t="shared" si="2"/>
-        <v>-3553.9076271037502</v>
+        <v>-3536.3140249893754</v>
       </c>
       <c r="AM6" s="12">
         <f t="shared" si="2"/>
-        <v>-3731.6030084589379</v>
+        <v>-3713.1297262388443</v>
       </c>
       <c r="AN6" s="12">
         <f t="shared" si="2"/>
-        <v>-3918.183158881885</v>
+        <v>-3898.7862125507868</v>
       </c>
       <c r="AO6" s="12">
         <f t="shared" si="2"/>
-        <v>-4114.0923168259797</v>
+        <v>-4093.7255231783265</v>
       </c>
       <c r="AP6" s="12">
         <f t="shared" si="2"/>
-        <v>-4319.7969326672792</v>
+        <v>-4298.4117993372429</v>
       </c>
       <c r="AQ6" s="12"/>
       <c r="AR6" s="12"/>
@@ -1787,7 +1789,7 @@
       <c r="AF7" s="12">
         <v>-90</v>
       </c>
-      <c r="AG7" s="12">
+      <c r="AG7" s="13">
         <f>AF7*1.01</f>
         <v>-90.9</v>
       </c>
@@ -1917,7 +1919,7 @@
       <c r="AF8" s="12">
         <v>-8</v>
       </c>
-      <c r="AG8" s="12">
+      <c r="AG8" s="13">
         <f t="shared" ref="AG8:AG9" si="4">AF8*1.01</f>
         <v>-8.08</v>
       </c>
@@ -1964,7 +1966,7 @@
       </c>
       <c r="B9" s="8">
         <f>B6-B7+B8</f>
-        <v>4238.2712250000004</v>
+        <v>4033.3072149999998</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>38</v>
@@ -2048,7 +2050,7 @@
       <c r="AF9" s="12">
         <v>-307</v>
       </c>
-      <c r="AG9" s="12">
+      <c r="AG9" s="13">
         <f t="shared" si="4"/>
         <v>-310.07</v>
       </c>
@@ -2198,45 +2200,45 @@
         <f t="shared" ref="AF10:AP10" si="9">SUM(AF4:AF9)</f>
         <v>474</v>
       </c>
-      <c r="AG10" s="10">
+      <c r="AG10" s="11">
         <f t="shared" si="9"/>
-        <v>433.75999999999993</v>
+        <v>408.29500000000024</v>
       </c>
       <c r="AH10" s="10">
         <f t="shared" si="9"/>
-        <v>478.37170000000037</v>
+        <v>451.63345000000049</v>
       </c>
       <c r="AI10" s="10">
         <f t="shared" si="9"/>
-        <v>496.38989800000024</v>
+        <v>468.45811300000048</v>
       </c>
       <c r="AJ10" s="10">
         <f t="shared" si="9"/>
-        <v>544.41144082000085</v>
+        <v>515.0830665700006</v>
       </c>
       <c r="AK10" s="10">
         <f t="shared" si="9"/>
-        <v>594.97606888180076</v>
+        <v>564.18127591930056</v>
       </c>
       <c r="AL10" s="10">
         <f t="shared" si="9"/>
-        <v>648.21254886320344</v>
+        <v>615.87801625257748</v>
       </c>
       <c r="AM10" s="10">
         <f t="shared" si="9"/>
-        <v>704.25583427116135</v>
+        <v>670.30457503000434</v>
       </c>
       <c r="AN10" s="10">
         <f t="shared" si="9"/>
-        <v>763.24733493870303</v>
+        <v>727.5985127354877</v>
       </c>
       <c r="AO10" s="10">
         <f t="shared" si="9"/>
-        <v>825.33519546079424</v>
+        <v>787.90393214741835</v>
       </c>
       <c r="AP10" s="10">
         <f t="shared" si="9"/>
-        <v>890.67458254117855</v>
+        <v>851.37175606213395</v>
       </c>
     </row>
     <row r="11" spans="1:145" x14ac:dyDescent="0.25">
@@ -2322,7 +2324,7 @@
       <c r="AF11" s="12">
         <v>-1</v>
       </c>
-      <c r="AG11" s="12">
+      <c r="AG11" s="13">
         <v>0</v>
       </c>
       <c r="AH11" s="12">
@@ -2461,45 +2463,45 @@
         <f t="shared" si="11"/>
         <v>473</v>
       </c>
-      <c r="AG12" s="12">
+      <c r="AG12" s="13">
         <f t="shared" ref="AG12:AP12" si="12">SUM(AG10:AG11)</f>
-        <v>433.75999999999993</v>
+        <v>408.29500000000024</v>
       </c>
       <c r="AH12" s="12">
         <f t="shared" si="12"/>
-        <v>478.37170000000037</v>
+        <v>451.63345000000049</v>
       </c>
       <c r="AI12" s="12">
         <f t="shared" si="12"/>
-        <v>496.38989800000024</v>
+        <v>468.45811300000048</v>
       </c>
       <c r="AJ12" s="12">
         <f t="shared" si="12"/>
-        <v>544.41144082000085</v>
+        <v>515.0830665700006</v>
       </c>
       <c r="AK12" s="12">
         <f t="shared" si="12"/>
-        <v>594.97606888180076</v>
+        <v>564.18127591930056</v>
       </c>
       <c r="AL12" s="12">
         <f t="shared" si="12"/>
-        <v>648.21254886320344</v>
+        <v>615.87801625257748</v>
       </c>
       <c r="AM12" s="12">
         <f t="shared" si="12"/>
-        <v>704.25583427116135</v>
+        <v>670.30457503000434</v>
       </c>
       <c r="AN12" s="12">
         <f t="shared" si="12"/>
-        <v>763.24733493870303</v>
+        <v>727.5985127354877</v>
       </c>
       <c r="AO12" s="12">
         <f t="shared" si="12"/>
-        <v>825.33519546079424</v>
+        <v>787.90393214741835</v>
       </c>
       <c r="AP12" s="12">
         <f t="shared" si="12"/>
-        <v>890.67458254117855</v>
+        <v>851.37175606213395</v>
       </c>
     </row>
     <row r="13" spans="1:145" x14ac:dyDescent="0.25">
@@ -2585,45 +2587,45 @@
       <c r="AF13" s="12">
         <v>-114</v>
       </c>
-      <c r="AG13" s="12">
+      <c r="AG13" s="13">
         <f t="shared" ref="AG13:AP13" si="13">AG12*-0.22</f>
-        <v>-95.427199999999985</v>
+        <v>-89.824900000000056</v>
       </c>
       <c r="AH13" s="12">
         <f t="shared" si="13"/>
-        <v>-105.24177400000008</v>
+        <v>-99.359359000000111</v>
       </c>
       <c r="AI13" s="12">
         <f t="shared" si="13"/>
-        <v>-109.20577756000006</v>
+        <v>-103.06078486000011</v>
       </c>
       <c r="AJ13" s="12">
         <f t="shared" si="13"/>
-        <v>-119.77051698040019</v>
+        <v>-113.31827464540014</v>
       </c>
       <c r="AK13" s="12">
         <f t="shared" si="13"/>
-        <v>-130.89473515399618</v>
+        <v>-124.11988070224612</v>
       </c>
       <c r="AL13" s="12">
         <f t="shared" si="13"/>
-        <v>-142.60676074990477</v>
+        <v>-135.49316357556705</v>
       </c>
       <c r="AM13" s="12">
         <f t="shared" si="13"/>
-        <v>-154.93628353965551</v>
+        <v>-147.46700650660097</v>
       </c>
       <c r="AN13" s="12">
         <f t="shared" si="13"/>
-        <v>-167.91441368651468</v>
+        <v>-160.0716728018073</v>
       </c>
       <c r="AO13" s="12">
         <f t="shared" si="13"/>
-        <v>-181.57374300137474</v>
+        <v>-173.33886507243204</v>
       </c>
       <c r="AP13" s="12">
         <f t="shared" si="13"/>
-        <v>-195.94840815905928</v>
+        <v>-187.30178633366947</v>
       </c>
     </row>
     <row r="14" spans="1:145" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2735,457 +2737,457 @@
         <f t="shared" ref="AF14:AP14" si="16">SUM(AF12:AF13)</f>
         <v>359</v>
       </c>
-      <c r="AG14" s="10">
+      <c r="AG14" s="11">
         <f t="shared" si="16"/>
-        <v>338.33279999999996</v>
+        <v>318.47010000000017</v>
       </c>
       <c r="AH14" s="10">
         <f t="shared" si="16"/>
-        <v>373.1299260000003</v>
+        <v>352.2740910000004</v>
       </c>
       <c r="AI14" s="10">
         <f t="shared" si="16"/>
-        <v>387.18412044000019</v>
+        <v>365.39732814000035</v>
       </c>
       <c r="AJ14" s="10">
         <f t="shared" si="16"/>
-        <v>424.64092383960065</v>
+        <v>401.76479192460044</v>
       </c>
       <c r="AK14" s="10">
         <f t="shared" si="16"/>
-        <v>464.08133372780458</v>
+        <v>440.06139521705444</v>
       </c>
       <c r="AL14" s="10">
         <f t="shared" si="16"/>
-        <v>505.60578811329867</v>
+        <v>480.38485267701043</v>
       </c>
       <c r="AM14" s="10">
         <f t="shared" si="16"/>
-        <v>549.31955073150584</v>
+        <v>522.83756852340343</v>
       </c>
       <c r="AN14" s="10">
         <f t="shared" si="16"/>
-        <v>595.33292125218838</v>
+        <v>567.52683993368044</v>
       </c>
       <c r="AO14" s="10">
         <f t="shared" si="16"/>
-        <v>643.7614524594195</v>
+        <v>614.56506707498625</v>
       </c>
       <c r="AP14" s="10">
         <f t="shared" si="16"/>
-        <v>694.72617438211932</v>
+        <v>664.06996972846446</v>
       </c>
       <c r="AQ14" s="10">
         <f>AP14*(1+$AS$18)</f>
-        <v>687.77891263829815</v>
+        <v>657.42927003117984</v>
       </c>
       <c r="AR14" s="10">
         <f t="shared" ref="AR14:DC14" si="17">AQ14*(1+$AS$18)</f>
-        <v>680.90112351191522</v>
+        <v>650.854977330868</v>
       </c>
       <c r="AS14" s="10">
         <f>AR14*(1+$AS$18)</f>
-        <v>674.092112276796</v>
+        <v>644.34642755755931</v>
       </c>
       <c r="AT14" s="10">
         <f t="shared" si="17"/>
-        <v>667.35119115402802</v>
+        <v>637.90296328198372</v>
       </c>
       <c r="AU14" s="10">
         <f t="shared" si="17"/>
-        <v>660.67767924248778</v>
+        <v>631.52393364916384</v>
       </c>
       <c r="AV14" s="10">
         <f t="shared" si="17"/>
-        <v>654.07090245006293</v>
+        <v>625.20869431267215</v>
       </c>
       <c r="AW14" s="10">
         <f t="shared" si="17"/>
-        <v>647.53019342556229</v>
+        <v>618.9566073695454</v>
       </c>
       <c r="AX14" s="10">
         <f t="shared" si="17"/>
-        <v>641.05489149130665</v>
+        <v>612.76704129584994</v>
       </c>
       <c r="AY14" s="10">
         <f t="shared" si="17"/>
-        <v>634.64434257639357</v>
+        <v>606.6393708828914</v>
       </c>
       <c r="AZ14" s="10">
         <f t="shared" si="17"/>
-        <v>628.29789915062963</v>
+        <v>600.57297717406243</v>
       </c>
       <c r="BA14" s="10">
         <f t="shared" si="17"/>
-        <v>622.01492015912333</v>
+        <v>594.56724740232175</v>
       </c>
       <c r="BB14" s="10">
         <f t="shared" si="17"/>
-        <v>615.79477095753214</v>
+        <v>588.62157492829851</v>
       </c>
       <c r="BC14" s="10">
         <f t="shared" si="17"/>
-        <v>609.63682324795684</v>
+        <v>582.73535917901552</v>
       </c>
       <c r="BD14" s="10">
         <f t="shared" si="17"/>
-        <v>603.54045501547728</v>
+        <v>576.90800558722538</v>
       </c>
       <c r="BE14" s="10">
         <f t="shared" si="17"/>
-        <v>597.50505046532248</v>
+        <v>571.13892553135315</v>
       </c>
       <c r="BF14" s="10">
         <f t="shared" si="17"/>
-        <v>591.52999996066922</v>
+        <v>565.42753627603963</v>
       </c>
       <c r="BG14" s="10">
         <f t="shared" si="17"/>
-        <v>585.61469996106257</v>
+        <v>559.77326091327927</v>
       </c>
       <c r="BH14" s="10">
         <f t="shared" si="17"/>
-        <v>579.75855296145198</v>
+        <v>554.1755283041465</v>
       </c>
       <c r="BI14" s="10">
         <f t="shared" si="17"/>
-        <v>573.9609674318375</v>
+        <v>548.63377302110507</v>
       </c>
       <c r="BJ14" s="10">
         <f t="shared" si="17"/>
-        <v>568.22135775751917</v>
+        <v>543.14743529089401</v>
       </c>
       <c r="BK14" s="10">
         <f t="shared" si="17"/>
-        <v>562.53914417994395</v>
+        <v>537.71596093798507</v>
       </c>
       <c r="BL14" s="10">
         <f t="shared" si="17"/>
-        <v>556.91375273814447</v>
+        <v>532.3388013286052</v>
       </c>
       <c r="BM14" s="10">
         <f t="shared" si="17"/>
-        <v>551.34461521076298</v>
+        <v>527.01541331531917</v>
       </c>
       <c r="BN14" s="10">
         <f t="shared" si="17"/>
-        <v>545.83116905865529</v>
+        <v>521.74525918216602</v>
       </c>
       <c r="BO14" s="10">
         <f t="shared" si="17"/>
-        <v>540.37285736806871</v>
+        <v>516.52780659034431</v>
       </c>
       <c r="BP14" s="10">
         <f t="shared" si="17"/>
-        <v>534.96912879438798</v>
+        <v>511.36252852444085</v>
       </c>
       <c r="BQ14" s="10">
         <f t="shared" si="17"/>
-        <v>529.61943750644411</v>
+        <v>506.24890323919641</v>
       </c>
       <c r="BR14" s="10">
         <f t="shared" si="17"/>
-        <v>524.32324313137963</v>
+        <v>501.18641420680444</v>
       </c>
       <c r="BS14" s="10">
         <f t="shared" si="17"/>
-        <v>519.08001070006583</v>
+        <v>496.17455006473642</v>
       </c>
       <c r="BT14" s="10">
         <f t="shared" si="17"/>
-        <v>513.88921059306517</v>
+        <v>491.21280456408903</v>
       </c>
       <c r="BU14" s="10">
         <f t="shared" si="17"/>
-        <v>508.75031848713451</v>
+        <v>486.30067651844814</v>
       </c>
       <c r="BV14" s="10">
         <f t="shared" si="17"/>
-        <v>503.66281530226314</v>
+        <v>481.43766975326366</v>
       </c>
       <c r="BW14" s="10">
         <f t="shared" si="17"/>
-        <v>498.62618714924048</v>
+        <v>476.62329305573104</v>
       </c>
       <c r="BX14" s="10">
         <f t="shared" si="17"/>
-        <v>493.63992527774809</v>
+        <v>471.85706012517375</v>
       </c>
       <c r="BY14" s="10">
         <f t="shared" si="17"/>
-        <v>488.70352602497059</v>
+        <v>467.13848952392198</v>
       </c>
       <c r="BZ14" s="10">
         <f t="shared" si="17"/>
-        <v>483.81649076472087</v>
+        <v>462.46710462868276</v>
       </c>
       <c r="CA14" s="10">
         <f t="shared" si="17"/>
-        <v>478.97832585707363</v>
+        <v>457.84243358239593</v>
       </c>
       <c r="CB14" s="10">
         <f t="shared" si="17"/>
-        <v>474.18854259850286</v>
+        <v>453.26400924657196</v>
       </c>
       <c r="CC14" s="10">
         <f t="shared" si="17"/>
-        <v>469.4466571725178</v>
+        <v>448.73136915410623</v>
       </c>
       <c r="CD14" s="10">
         <f t="shared" si="17"/>
-        <v>464.75219060079263</v>
+        <v>444.24405546256514</v>
       </c>
       <c r="CE14" s="10">
         <f t="shared" si="17"/>
-        <v>460.10466869478472</v>
+        <v>439.80161490793949</v>
       </c>
       <c r="CF14" s="10">
         <f t="shared" si="17"/>
-        <v>455.5036220078369</v>
+        <v>435.40359875886008</v>
       </c>
       <c r="CG14" s="10">
         <f t="shared" si="17"/>
-        <v>450.94858578775853</v>
+        <v>431.0495627712715</v>
       </c>
       <c r="CH14" s="10">
         <f t="shared" si="17"/>
-        <v>446.43909992988097</v>
+        <v>426.73906714355877</v>
       </c>
       <c r="CI14" s="10">
         <f t="shared" si="17"/>
-        <v>441.97470893058215</v>
+        <v>422.47167647212319</v>
       </c>
       <c r="CJ14" s="10">
         <f t="shared" si="17"/>
-        <v>437.55496184127634</v>
+        <v>418.24695970740197</v>
       </c>
       <c r="CK14" s="10">
         <f t="shared" si="17"/>
-        <v>433.17941222286356</v>
+        <v>414.06449011032794</v>
       </c>
       <c r="CL14" s="10">
         <f t="shared" si="17"/>
-        <v>428.84761810063492</v>
+        <v>409.92384520922468</v>
       </c>
       <c r="CM14" s="10">
         <f t="shared" si="17"/>
-        <v>424.55914191962859</v>
+        <v>405.82460675713241</v>
       </c>
       <c r="CN14" s="10">
         <f t="shared" si="17"/>
-        <v>420.31355050043231</v>
+        <v>401.76636068956111</v>
       </c>
       <c r="CO14" s="10">
         <f t="shared" si="17"/>
-        <v>416.11041499542796</v>
+        <v>397.7486970826655</v>
       </c>
       <c r="CP14" s="10">
         <f t="shared" si="17"/>
-        <v>411.94931084547369</v>
+        <v>393.77121011183885</v>
       </c>
       <c r="CQ14" s="10">
         <f t="shared" si="17"/>
-        <v>407.82981773701897</v>
+        <v>389.83349801072046</v>
       </c>
       <c r="CR14" s="10">
         <f t="shared" si="17"/>
-        <v>403.75151955964878</v>
+        <v>385.93516303061324</v>
       </c>
       <c r="CS14" s="10">
         <f t="shared" si="17"/>
-        <v>399.7140043640523</v>
+        <v>382.07581140030709</v>
       </c>
       <c r="CT14" s="10">
         <f t="shared" si="17"/>
-        <v>395.71686432041179</v>
+        <v>378.25505328630402</v>
       </c>
       <c r="CU14" s="10">
         <f t="shared" si="17"/>
-        <v>391.75969567720767</v>
+        <v>374.47250275344095</v>
       </c>
       <c r="CV14" s="10">
         <f t="shared" si="17"/>
-        <v>387.84209872043562</v>
+        <v>370.72777772590655</v>
       </c>
       <c r="CW14" s="10">
         <f t="shared" si="17"/>
-        <v>383.96367773323124</v>
+        <v>367.02049994864745</v>
       </c>
       <c r="CX14" s="10">
         <f t="shared" si="17"/>
-        <v>380.12404095589892</v>
+        <v>363.35029494916097</v>
       </c>
       <c r="CY14" s="10">
         <f t="shared" si="17"/>
-        <v>376.32280054633992</v>
+        <v>359.71679199966934</v>
       </c>
       <c r="CZ14" s="10">
         <f t="shared" si="17"/>
-        <v>372.5595725408765</v>
+        <v>356.11962407967263</v>
       </c>
       <c r="DA14" s="10">
         <f t="shared" si="17"/>
-        <v>368.83397681546774</v>
+        <v>352.5584278388759</v>
       </c>
       <c r="DB14" s="10">
         <f t="shared" si="17"/>
-        <v>365.14563704731307</v>
+        <v>349.03284356048715</v>
       </c>
       <c r="DC14" s="10">
         <f t="shared" si="17"/>
-        <v>361.49418067683996</v>
+        <v>345.5425151248823</v>
       </c>
       <c r="DD14" s="10">
         <f t="shared" ref="DD14:EO14" si="18">DC14*(1+$AS$18)</f>
-        <v>357.87923887007156</v>
+        <v>342.08708997363345</v>
       </c>
       <c r="DE14" s="10">
         <f t="shared" si="18"/>
-        <v>354.30044648137084</v>
+        <v>338.66621907389714</v>
       </c>
       <c r="DF14" s="10">
         <f t="shared" si="18"/>
-        <v>350.75744201655715</v>
+        <v>335.27955688315814</v>
       </c>
       <c r="DG14" s="10">
         <f t="shared" si="18"/>
-        <v>347.2498675963916</v>
+        <v>331.92676131432654</v>
       </c>
       <c r="DH14" s="10">
         <f t="shared" si="18"/>
-        <v>343.7773689204277</v>
+        <v>328.60749370118327</v>
       </c>
       <c r="DI14" s="10">
         <f t="shared" si="18"/>
-        <v>340.33959523122343</v>
+        <v>325.32141876417143</v>
       </c>
       <c r="DJ14" s="10">
         <f t="shared" si="18"/>
-        <v>336.9361992789112</v>
+        <v>322.06820457652969</v>
       </c>
       <c r="DK14" s="10">
         <f t="shared" si="18"/>
-        <v>333.56683728612211</v>
+        <v>318.84752253076442</v>
       </c>
       <c r="DL14" s="10">
         <f t="shared" si="18"/>
-        <v>330.23116891326089</v>
+        <v>315.6590473054568</v>
       </c>
       <c r="DM14" s="10">
         <f t="shared" si="18"/>
-        <v>326.92885722412825</v>
+        <v>312.50245683240223</v>
       </c>
       <c r="DN14" s="10">
         <f t="shared" si="18"/>
-        <v>323.65956865188696</v>
+        <v>309.37743226407821</v>
       </c>
       <c r="DO14" s="10">
         <f t="shared" si="18"/>
-        <v>320.4229729653681</v>
+        <v>306.28365794143741</v>
       </c>
       <c r="DP14" s="10">
         <f t="shared" si="18"/>
-        <v>317.21874323571444</v>
+        <v>303.22082136202306</v>
       </c>
       <c r="DQ14" s="10">
         <f t="shared" si="18"/>
-        <v>314.04655580335731</v>
+        <v>300.18861314840285</v>
       </c>
       <c r="DR14" s="10">
         <f t="shared" si="18"/>
-        <v>310.90609024532375</v>
+        <v>297.18672701691884</v>
       </c>
       <c r="DS14" s="10">
         <f t="shared" si="18"/>
-        <v>307.79702934287053</v>
+        <v>294.21485974674965</v>
       </c>
       <c r="DT14" s="10">
         <f t="shared" si="18"/>
-        <v>304.7190590494418</v>
+        <v>291.27271114928215</v>
       </c>
       <c r="DU14" s="10">
         <f t="shared" si="18"/>
-        <v>301.67186845894736</v>
+        <v>288.35998403778933</v>
       </c>
       <c r="DV14" s="10">
         <f t="shared" si="18"/>
-        <v>298.65514977435788</v>
+        <v>285.47638419741145</v>
       </c>
       <c r="DW14" s="10">
         <f t="shared" si="18"/>
-        <v>295.66859827661432</v>
+        <v>282.62162035543736</v>
       </c>
       <c r="DX14" s="10">
         <f t="shared" si="18"/>
-        <v>292.71191229384817</v>
+        <v>279.79540415188296</v>
       </c>
       <c r="DY14" s="10">
         <f t="shared" si="18"/>
-        <v>289.78479317090967</v>
+        <v>276.99745011036413</v>
       </c>
       <c r="DZ14" s="10">
         <f t="shared" si="18"/>
-        <v>286.88694523920054</v>
+        <v>274.22747560926047</v>
       </c>
       <c r="EA14" s="10">
         <f t="shared" si="18"/>
-        <v>284.01807578680854</v>
+        <v>271.48520085316784</v>
       </c>
       <c r="EB14" s="10">
         <f t="shared" si="18"/>
-        <v>281.17789502894044</v>
+        <v>268.77034884463615</v>
       </c>
       <c r="EC14" s="10">
         <f t="shared" si="18"/>
-        <v>278.36611607865103</v>
+        <v>266.0826453561898</v>
       </c>
       <c r="ED14" s="10">
         <f t="shared" si="18"/>
-        <v>275.58245491786454</v>
+        <v>263.42181890262788</v>
       </c>
       <c r="EE14" s="10">
         <f t="shared" si="18"/>
-        <v>272.82663036868587</v>
+        <v>260.78760071360159</v>
       </c>
       <c r="EF14" s="10">
         <f t="shared" si="18"/>
-        <v>270.09836406499903</v>
+        <v>258.17972470646555</v>
       </c>
       <c r="EG14" s="10">
         <f t="shared" si="18"/>
-        <v>267.39738042434902</v>
+        <v>255.59792745940089</v>
       </c>
       <c r="EH14" s="10">
         <f t="shared" si="18"/>
-        <v>264.72340662010555</v>
+        <v>253.04194818480687</v>
       </c>
       <c r="EI14" s="10">
         <f t="shared" si="18"/>
-        <v>262.07617255390448</v>
+        <v>250.5115287029588</v>
       </c>
       <c r="EJ14" s="10">
         <f t="shared" si="18"/>
-        <v>259.45541082836542</v>
+        <v>248.00641341592922</v>
       </c>
       <c r="EK14" s="10">
         <f t="shared" si="18"/>
-        <v>256.86085672008176</v>
+        <v>245.52634928176991</v>
       </c>
       <c r="EL14" s="10">
         <f t="shared" si="18"/>
-        <v>254.29224815288094</v>
+        <v>243.07108578895222</v>
       </c>
       <c r="EM14" s="10">
         <f t="shared" si="18"/>
-        <v>251.74932567135212</v>
+        <v>240.64037493106269</v>
       </c>
       <c r="EN14" s="10">
         <f t="shared" si="18"/>
-        <v>249.2318324146386</v>
+        <v>238.23397118175205</v>
       </c>
       <c r="EO14" s="10">
         <f t="shared" si="18"/>
-        <v>246.73951409049221</v>
+        <v>235.85163146993452</v>
       </c>
     </row>
     <row r="15" spans="1:145" x14ac:dyDescent="0.25">
@@ -3270,7 +3272,7 @@
       <c r="AF15" s="25">
         <v>103.80063699999999</v>
       </c>
-      <c r="AG15" s="25">
+      <c r="AG15" s="28">
         <v>103.80063699999999</v>
       </c>
       <c r="AH15" s="25">
@@ -3409,45 +3411,45 @@
         <f t="shared" si="21"/>
         <v>3.4585529566644184</v>
       </c>
-      <c r="AG16" s="15">
+      <c r="AG16" s="14">
         <f t="shared" ref="AG16:AP16" si="22">AG14/AG15</f>
-        <v>3.2594482055057137</v>
+        <v>3.0680938884797033</v>
       </c>
       <c r="AH16" s="15">
         <f t="shared" si="22"/>
-        <v>3.5946785760091271</v>
+        <v>3.3937565431318153</v>
       </c>
       <c r="AI16" s="15">
         <f t="shared" si="22"/>
-        <v>3.730074608694359</v>
+        <v>3.5201838707406043</v>
       </c>
       <c r="AJ16" s="15">
         <f t="shared" si="22"/>
-        <v>4.0909279182901415</v>
+        <v>3.8705426434386956</v>
       </c>
       <c r="AK16" s="15">
         <f t="shared" si="22"/>
-        <v>4.4708909997132738</v>
+        <v>4.239486461119256</v>
       </c>
       <c r="AL16" s="15">
         <f t="shared" si="22"/>
-        <v>4.8709314578994221</v>
+        <v>4.6279566923756974</v>
       </c>
       <c r="AM16" s="15">
         <f t="shared" si="22"/>
-        <v>5.2920633881226173</v>
+        <v>5.0369398843227087</v>
       </c>
       <c r="AN16" s="15">
         <f t="shared" si="22"/>
-        <v>5.7353494011042381</v>
+        <v>5.4674697221143305</v>
       </c>
       <c r="AO16" s="15">
         <f t="shared" si="22"/>
-        <v>6.2019027152927739</v>
+        <v>5.9206290523533713</v>
       </c>
       <c r="AP16" s="15">
         <f t="shared" si="22"/>
-        <v>6.6928893161042868</v>
+        <v>6.3975519700179149</v>
       </c>
     </row>
     <row r="17" spans="3:45" x14ac:dyDescent="0.25">
@@ -3562,45 +3564,45 @@
         <f t="shared" ref="AF18:AP18" si="26">(AF4-AE4)/AE4</f>
         <v>-2.2953328232593728E-3</v>
       </c>
-      <c r="AG18" s="17">
+      <c r="AG18" s="16">
         <f t="shared" si="26"/>
-        <v>9.9999999999999725E-3</v>
+        <v>0</v>
       </c>
       <c r="AH18" s="17">
         <f>(AH4-AG4)/AG4</f>
-        <v>5.0000000000000128E-2</v>
+        <v>5.0000000000000093E-2</v>
       </c>
       <c r="AI18" s="17">
         <f t="shared" si="26"/>
-        <v>4.9999999999999947E-2</v>
+        <v>5.0000000000000024E-2</v>
       </c>
       <c r="AJ18" s="17">
         <f t="shared" si="26"/>
-        <v>5.0000000000000148E-2</v>
+        <v>5.0000000000000072E-2</v>
       </c>
       <c r="AK18" s="17">
         <f t="shared" si="26"/>
-        <v>5.0000000000000037E-2</v>
+        <v>0.05</v>
       </c>
       <c r="AL18" s="17">
         <f t="shared" si="26"/>
-        <v>5.0000000000000114E-2</v>
+        <v>0.05</v>
       </c>
       <c r="AM18" s="17">
         <f t="shared" si="26"/>
-        <v>4.9999999999999961E-2</v>
+        <v>5.000000000000001E-2</v>
       </c>
       <c r="AN18" s="17">
         <f t="shared" si="26"/>
-        <v>5.0000000000000086E-2</v>
+        <v>0.05</v>
       </c>
       <c r="AO18" s="17">
         <f t="shared" si="26"/>
-        <v>5.0000000000000072E-2</v>
+        <v>5.0000000000000107E-2</v>
       </c>
       <c r="AP18" s="17">
         <f t="shared" si="26"/>
-        <v>5.0000000000000051E-2</v>
+        <v>4.9999999999999982E-2</v>
       </c>
       <c r="AR18" s="1" t="s">
         <v>87</v>
@@ -3716,52 +3718,52 @@
         <f>AF10/AF4</f>
         <v>0.12116564417177914</v>
       </c>
-      <c r="AG19" s="19">
+      <c r="AG19" s="20">
         <f t="shared" si="31"/>
-        <v>0.10978153030026928</v>
+        <v>0.10436988752556244</v>
       </c>
       <c r="AH19" s="19">
         <f t="shared" si="31"/>
-        <v>0.11530707628168609</v>
+        <v>0.10995068896679337</v>
       </c>
       <c r="AI19" s="19">
         <f t="shared" si="31"/>
-        <v>0.11395256795409524</v>
+        <v>0.1086158788123294</v>
       </c>
       <c r="AJ19" s="19">
         <f t="shared" si="31"/>
-        <v>0.11902525654776627</v>
+        <v>0.11373929429193703</v>
       </c>
       <c r="AK19" s="19">
         <f t="shared" si="31"/>
-        <v>0.12388595747813344</v>
+        <v>0.11864860223160791</v>
       </c>
       <c r="AL19" s="19">
         <f t="shared" si="31"/>
-        <v>0.12854367710105852</v>
+        <v>0.12335289905076208</v>
       </c>
       <c r="AM19" s="19">
         <f t="shared" si="31"/>
-        <v>0.13300698199607039</v>
+        <v>0.12786083699472411</v>
       </c>
       <c r="AN19" s="19">
         <f t="shared" si="31"/>
-        <v>0.13728401850931068</v>
+        <v>0.13218064387309675</v>
       </c>
       <c r="AO19" s="19">
         <f t="shared" si="31"/>
-        <v>0.14138253132162668</v>
+        <v>0.13632014181353591</v>
       </c>
       <c r="AP19" s="19">
         <f t="shared" si="31"/>
-        <v>0.14530988108551698</v>
+        <v>0.14028676507506518</v>
       </c>
       <c r="AR19" s="23" t="s">
         <v>88</v>
       </c>
       <c r="AS19" s="24">
         <f>NPV(AS17,AF14:EO14)</f>
-        <v>6547.5720215258207</v>
+        <v>6253.053618475129</v>
       </c>
     </row>
     <row r="20" spans="3:45" x14ac:dyDescent="0.25">
@@ -3855,33 +3857,33 @@
         <f>(AF6-AE6)/AE6</f>
         <v>2.2463496817671284E-2</v>
       </c>
-      <c r="AG20" s="19">
+      <c r="AG20" s="20">
         <f t="shared" ref="AG20:AP20" si="39">(AG6-AF6)/AF6</f>
-        <v>9.9999999999999794E-3</v>
+        <v>4.9999999999999064E-3</v>
       </c>
       <c r="AH20" s="19">
         <f t="shared" si="39"/>
-        <v>5.0000000000000024E-2</v>
+        <v>5.0000000000000051E-2</v>
       </c>
       <c r="AI20" s="19">
         <f t="shared" si="39"/>
-        <v>5.9999999999999977E-2</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AJ20" s="19">
         <f t="shared" si="39"/>
-        <v>4.9999999999999982E-2</v>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AK20" s="19">
         <f t="shared" si="39"/>
-        <v>5.00000000000001E-2</v>
+        <v>5.0000000000000024E-2</v>
       </c>
       <c r="AL20" s="19">
         <f t="shared" si="39"/>
-        <v>4.9999999999999996E-2</v>
+        <v>5.0000000000000051E-2</v>
       </c>
       <c r="AM20" s="19">
         <f t="shared" si="39"/>
-        <v>5.0000000000000051E-2</v>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN20" s="19">
         <f t="shared" si="39"/>
@@ -3889,11 +3891,11 @@
       </c>
       <c r="AO20" s="19">
         <f t="shared" si="39"/>
-        <v>5.0000000000000107E-2</v>
+        <v>5.00000000000001E-2</v>
       </c>
       <c r="AP20" s="19">
         <f t="shared" si="39"/>
-        <v>5.0000000000000135E-2</v>
+        <v>5.000000000000001E-2</v>
       </c>
       <c r="AR20" s="1" t="s">
         <v>45</v>
@@ -3941,7 +3943,7 @@
         <v>0.82393232998597377</v>
       </c>
       <c r="AF21" s="19"/>
-      <c r="AG21" s="19"/>
+      <c r="AG21" s="20"/>
       <c r="AH21" s="19"/>
       <c r="AI21" s="19"/>
       <c r="AJ21" s="19"/>
@@ -3956,7 +3958,7 @@
       </c>
       <c r="AS21" s="26">
         <f>AS19/AS20</f>
-        <v>63.88996801463653</v>
+        <v>61.016113204216964</v>
       </c>
     </row>
     <row r="22" spans="3:45" x14ac:dyDescent="0.25">
@@ -3976,7 +3978,7 @@
       </c>
       <c r="AS22" s="27">
         <f>(AS21-B4)/B4</f>
-        <v>0.41977706699192291</v>
+        <v>0.418979376842255</v>
       </c>
     </row>
     <row r="23" spans="3:45" x14ac:dyDescent="0.25">
@@ -7984,15 +7986,15 @@
       </c>
       <c r="F6" s="30">
         <f>Modell!$B$9/Modell!AG10</f>
-        <v>9.7710052217816337</v>
+        <v>9.8784144184964244</v>
       </c>
       <c r="G6" s="30">
         <f>Modell!$B$9/Modell!AH10</f>
-        <v>8.8597866993386045</v>
+        <v>8.930488242179571</v>
       </c>
       <c r="H6" s="30">
         <f>Modell!$B$9/Modell!AI10</f>
-        <v>8.5381899230350538</v>
+        <v>8.6097499500451509</v>
       </c>
     </row>
     <row r="7" spans="5:8" ht="92" x14ac:dyDescent="1">
@@ -8001,15 +8003,15 @@
       </c>
       <c r="F7" s="30">
         <f>Modell!$B$4/Modell!AG16</f>
-        <v>13.806017817367989</v>
+        <v>14.015216470871199</v>
       </c>
       <c r="G7" s="30">
         <f>Modell!$B$4/Modell!AH16</f>
-        <v>12.518504519522232</v>
+        <v>12.670325479599335</v>
       </c>
       <c r="H7" s="30">
         <f>Modell!$B$4/Modell!AI16</f>
-        <v>12.064101853381262</v>
+        <v>12.215271013940905</v>
       </c>
     </row>
   </sheetData>
@@ -8255,7 +8257,7 @@
     <row r="6" spans="1:16367" x14ac:dyDescent="0.25">
       <c r="A6" s="27">
         <f>X22</f>
-        <v>-0.15130556572554038</v>
+        <v>-0.11183140599184459</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>35</v>
@@ -25927,7 +25929,7 @@
       </c>
       <c r="X22" s="27">
         <f>(X21-Modell!B4)/Modell!B4</f>
-        <v>-0.15130556572554038</v>
+        <v>-0.11183140599184459</v>
       </c>
     </row>
   </sheetData>
